--- a/app/templates/informes/EquiArena/Template_EquiArena.xlsx
+++ b/app/templates/informes/EquiArena/Template_EquiArena.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\6.1 JUNIO INICIA 15-06-25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16039C29-0C4A-4E1C-8012-ED7D1F99C089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5491EC75-F5BF-4341-9F34-FB11E3A17F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="556" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="556" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO" sheetId="97" r:id="rId1"/>
@@ -141,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="178">
   <si>
     <t>:</t>
   </si>
@@ -407,12 +407,6 @@
     <t>Equivalente de arena de los suelos y agregados finos</t>
   </si>
   <si>
-    <t>- Los resultados corresponden sólo a los ensayos realizados sobre la muestra proporcionada por el cliente.</t>
-  </si>
-  <si>
-    <t>- Prohibida la reproducción total o parcial del presente informe de ensayo sin la autorización escrita de Geofal S.A.C.</t>
-  </si>
-  <si>
     <t>Equivalente arena</t>
   </si>
   <si>
@@ -521,12 +515,6 @@
     <t>Nota:</t>
   </si>
   <si>
-    <t>- Los datos de identificación de la muestra son proporcionados por el cliente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Los resultados de los ensayos no deben ser utilizados como una certificación de conformidad con normas de productos o como certificado del sistema de calidad de Geofal SAC. </t>
-  </si>
-  <si>
     <t>Observaciones:</t>
   </si>
   <si>
@@ -581,19 +569,10 @@
     <t>ASTM  D2419-22</t>
   </si>
   <si>
-    <t>- Este informe de ensayo, al estar en el marco de la acreditación del INACAL - DA, se encuentra dentro del ámbito de reconocimiento multilateral/mutuo de los miembros firmantes de IAAC e ILAC.</t>
-  </si>
-  <si>
     <t>TIPO DE MUESTRA</t>
   </si>
   <si>
     <t>RECEPCIÓN N°</t>
-  </si>
-  <si>
-    <t>Versión: 07 (04-01-2024)</t>
-  </si>
-  <si>
-    <t>Procedimiento A</t>
   </si>
   <si>
     <r>
@@ -726,52 +705,28 @@
     <t>Balanza 0.1 g</t>
   </si>
   <si>
-    <t>EQP-0046</t>
-  </si>
-  <si>
     <t>Horno 110ºC</t>
   </si>
   <si>
-    <t>EQP-0049</t>
-  </si>
-  <si>
     <t>Equivalente de arena</t>
   </si>
   <si>
-    <t>EQP-0028</t>
-  </si>
-  <si>
     <t>Agitador de EA</t>
   </si>
   <si>
-    <t>EQP-0047</t>
-  </si>
-  <si>
     <t>Termómetro</t>
   </si>
   <si>
-    <t>INS-0153</t>
-  </si>
-  <si>
     <t>Tamiz No. 4</t>
   </si>
   <si>
-    <t>INS-0053</t>
-  </si>
-  <si>
     <t>Cronometro</t>
   </si>
   <si>
-    <t>EQP-0077</t>
-  </si>
-  <si>
     <t>Versión: 05 (15-04-2025)</t>
   </si>
   <si>
     <t>Prohibido resproducir sin  autorización</t>
-  </si>
-  <si>
-    <t>WEB: www.geofal.com.pe   E-MAIL: laboratorio@geofal.com.pe / geofal.sac@gmail.com                                                                                                                         Av. Marañon 763, Los Olivos-Lima / Teléfono  01 522-1851</t>
   </si>
   <si>
     <t>F. EMISIÓN</t>
@@ -867,6 +822,30 @@
   </si>
   <si>
     <t>Factor de precision EQUIVALENTE ARENA</t>
+  </si>
+  <si>
+    <t>WEB: www.geofal.com.pe   E-MAIL: laboratorio@geofal.com.pe                                                                                                                                                                 Av. Marañon 763, Los Olivos-Lima / Teléfono  01 522-1851</t>
+  </si>
+  <si>
+    <t>- El cliente es responsable de los datos de identificación de los puntos de ensayo brindados.</t>
+  </si>
+  <si>
+    <t>- Los resultados expresados se refieren únicamente al ensayo realizado en dicho momento y en las condiciones especificadas en este documento, por lo que GEOFAL S.A.C. no será responsable por los ensayos realizados con la presente muestra en condiciones distintas a las aquí señaladas.</t>
+  </si>
+  <si>
+    <t>- GEOFAL S.A.C. no se hace responsable por el uso incorrecto o inadecuado del presente informe.</t>
+  </si>
+  <si>
+    <t>- Los resultados de los ensayos realizados no deben ser utilizados como una certificación de conformidad con normas de producto o como certificado del sistema de calidad de la entidad que lo produce.</t>
+  </si>
+  <si>
+    <t>- De conformidad con lo dispuesto por el artículo 1321 del Código Civil, queda establecido que en ningún caso la responsabilidad de GEOFAL S.A.C. será mayor al valor del servicio prestado.</t>
+  </si>
+  <si>
+    <t>Versión: 08 (15-06-2026)</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -891,7 +870,7 @@
     <numFmt numFmtId="178" formatCode="&quot;FORMATO F-LEM-P-SU-11.01&quot;"/>
     <numFmt numFmtId="179" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="46" x14ac:knownFonts="1">
+  <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1154,6 +1133,19 @@
       <vertAlign val="subscript"/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1668,12 +1660,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="465">
+  <cellXfs count="529">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1747,23 +1739,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1786,24 +1762,6 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1816,9 +1774,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -1829,47 +1784,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1886,17 +1803,8 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1908,9 +1816,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1944,26 +1849,9 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1971,34 +1859,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2010,12 +1871,6 @@
     <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="4" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2262,44 +2117,11 @@
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="4" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="38" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2366,16 +2188,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2400,44 +2212,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="174" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2464,14 +2238,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -2738,6 +2504,9 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="1" fontId="43" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -2819,19 +2588,362 @@
     <xf numFmtId="174" fontId="24" fillId="2" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="174" fontId="9" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2929,6 +3041,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="1" fontId="44" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="44" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="44" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="1"/>
@@ -2969,19 +3090,114 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3001,15 +3217,23 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3028,43 +3252,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3072,23 +3259,20 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="174" fontId="3" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3412,7 +3596,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="119672192"/>
@@ -3449,7 +3633,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="119670272"/>
@@ -3488,7 +3672,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4044,7 +4228,7 @@
       <xdr:col>22</xdr:col>
       <xdr:colOff>347436</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>18745</xdr:rowOff>
+      <xdr:rowOff>49225</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4464,7 +4648,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -4523,7 +4707,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -4642,7 +4826,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -4693,7 +4877,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -4745,7 +4929,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -4777,7 +4961,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -5484,887 +5668,875 @@
   <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="271" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="271" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" style="271" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" style="271" customWidth="1"/>
-    <col min="5" max="5" width="8.109375" style="271" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="271" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" style="271" customWidth="1"/>
-    <col min="8" max="10" width="13" style="271" customWidth="1"/>
-    <col min="11" max="11" width="6.44140625" style="271" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" style="271" customWidth="1"/>
-    <col min="13" max="14" width="10.6640625" style="271" customWidth="1"/>
-    <col min="15" max="16384" width="10.33203125" style="271"/>
+    <col min="1" max="1" width="6.88671875" style="199" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="199" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" style="199" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="199" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" style="199" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="199" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" style="199" customWidth="1"/>
+    <col min="8" max="10" width="13" style="199" customWidth="1"/>
+    <col min="11" max="11" width="6.44140625" style="199" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" style="199" customWidth="1"/>
+    <col min="13" max="14" width="10.6640625" style="199" customWidth="1"/>
+    <col min="15" max="16384" width="10.33203125" style="199"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="267"/>
-      <c r="B1" s="268"/>
-      <c r="C1" s="268"/>
-      <c r="D1" s="268"/>
-      <c r="E1" s="269"/>
-      <c r="F1" s="269"/>
-      <c r="G1" s="269"/>
-      <c r="H1" s="269"/>
-      <c r="I1" s="269"/>
-      <c r="J1" s="270"/>
+      <c r="A1" s="195"/>
+      <c r="B1" s="196"/>
+      <c r="C1" s="196"/>
+      <c r="D1" s="196"/>
+      <c r="E1" s="197"/>
+      <c r="F1" s="197"/>
+      <c r="G1" s="197"/>
+      <c r="H1" s="197"/>
+      <c r="I1" s="197"/>
+      <c r="J1" s="198"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="272"/>
-      <c r="B2" s="273"/>
-      <c r="C2" s="273"/>
-      <c r="D2" s="273"/>
-      <c r="E2" s="274"/>
-      <c r="F2" s="274"/>
-      <c r="G2" s="274"/>
-      <c r="H2" s="274"/>
-      <c r="I2" s="274"/>
-      <c r="J2" s="275"/>
-      <c r="M2" s="350" t="s">
+      <c r="A2" s="200"/>
+      <c r="B2" s="201"/>
+      <c r="C2" s="201"/>
+      <c r="D2" s="201"/>
+      <c r="E2" s="202"/>
+      <c r="F2" s="202"/>
+      <c r="G2" s="202"/>
+      <c r="H2" s="202"/>
+      <c r="I2" s="202"/>
+      <c r="J2" s="203"/>
+      <c r="M2" s="279" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="351"/>
+      <c r="N2" s="280"/>
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="272"/>
-      <c r="B3" s="273"/>
-      <c r="C3" s="273"/>
-      <c r="D3" s="273"/>
-      <c r="E3" s="274"/>
-      <c r="F3" s="274"/>
-      <c r="G3" s="274"/>
-      <c r="H3" s="274"/>
-      <c r="I3" s="274"/>
-      <c r="J3" s="275"/>
-      <c r="M3" s="350" t="s">
+      <c r="A3" s="200"/>
+      <c r="B3" s="201"/>
+      <c r="C3" s="201"/>
+      <c r="D3" s="201"/>
+      <c r="E3" s="202"/>
+      <c r="F3" s="202"/>
+      <c r="G3" s="202"/>
+      <c r="H3" s="202"/>
+      <c r="I3" s="202"/>
+      <c r="J3" s="203"/>
+      <c r="M3" s="279" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="352"/>
+      <c r="N3" s="281"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="272"/>
-      <c r="B4" s="273"/>
-      <c r="C4" s="273"/>
-      <c r="D4" s="273"/>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
-      <c r="G4" s="274"/>
-      <c r="H4" s="274"/>
-      <c r="I4" s="274"/>
-      <c r="J4" s="275"/>
-      <c r="M4" s="350" t="s">
+      <c r="A4" s="200"/>
+      <c r="B4" s="201"/>
+      <c r="C4" s="201"/>
+      <c r="D4" s="201"/>
+      <c r="E4" s="202"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="202"/>
+      <c r="H4" s="202"/>
+      <c r="I4" s="202"/>
+      <c r="J4" s="203"/>
+      <c r="M4" s="279" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="352"/>
+      <c r="N4" s="281"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="276"/>
-      <c r="B5" s="277"/>
-      <c r="C5" s="277"/>
-      <c r="D5" s="277"/>
-      <c r="E5" s="277"/>
-      <c r="F5" s="277"/>
-      <c r="G5" s="277"/>
-      <c r="H5" s="277"/>
-      <c r="I5" s="277"/>
-      <c r="J5" s="278"/>
-      <c r="M5" s="350" t="s">
+      <c r="A5" s="204"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="205"/>
+      <c r="D5" s="205"/>
+      <c r="E5" s="205"/>
+      <c r="F5" s="205"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="205"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="206"/>
+      <c r="M5" s="279" t="s">
         <v>23</v>
       </c>
-      <c r="N5" s="352"/>
+      <c r="N5" s="281"/>
     </row>
     <row r="6" spans="1:14" ht="5.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="279"/>
-      <c r="B6" s="279"/>
-      <c r="C6" s="279"/>
-      <c r="D6" s="279"/>
-      <c r="E6" s="279"/>
-      <c r="F6" s="279"/>
-      <c r="G6" s="279"/>
-      <c r="H6" s="279"/>
-      <c r="I6" s="279"/>
-      <c r="J6" s="279"/>
-      <c r="M6" s="353"/>
-      <c r="N6" s="354"/>
+      <c r="A6" s="207"/>
+      <c r="B6" s="207"/>
+      <c r="C6" s="207"/>
+      <c r="D6" s="207"/>
+      <c r="E6" s="207"/>
+      <c r="F6" s="207"/>
+      <c r="G6" s="207"/>
+      <c r="H6" s="207"/>
+      <c r="I6" s="207"/>
+      <c r="J6" s="207"/>
+      <c r="M6" s="282"/>
+      <c r="N6" s="283"/>
     </row>
     <row r="7" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="369" t="s">
+      <c r="A7" s="409" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="369"/>
-      <c r="C7" s="369"/>
-      <c r="D7" s="369"/>
-      <c r="E7" s="369"/>
-      <c r="F7" s="369"/>
-      <c r="G7" s="369"/>
-      <c r="H7" s="369"/>
-      <c r="I7" s="369"/>
-      <c r="J7" s="369"/>
-      <c r="M7" s="350" t="s">
+      <c r="B7" s="409"/>
+      <c r="C7" s="409"/>
+      <c r="D7" s="409"/>
+      <c r="E7" s="409"/>
+      <c r="F7" s="409"/>
+      <c r="G7" s="409"/>
+      <c r="H7" s="409"/>
+      <c r="I7" s="409"/>
+      <c r="J7" s="409"/>
+      <c r="M7" s="279" t="s">
+        <v>119</v>
+      </c>
+      <c r="N7" s="283"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="410" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="410"/>
+      <c r="C8" s="410"/>
+      <c r="D8" s="410"/>
+      <c r="E8" s="410"/>
+      <c r="F8" s="410"/>
+      <c r="G8" s="410"/>
+      <c r="H8" s="410"/>
+      <c r="I8" s="410"/>
+      <c r="J8" s="410"/>
+      <c r="M8" s="279" t="s">
+        <v>157</v>
+      </c>
+      <c r="N8" s="284"/>
+    </row>
+    <row r="9" spans="1:14" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="208"/>
+      <c r="B9" s="208"/>
+      <c r="C9" s="208"/>
+      <c r="D9" s="208"/>
+      <c r="E9" s="208"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
+      <c r="I9" s="208"/>
+      <c r="J9" s="208"/>
+      <c r="M9" s="279" t="s">
+        <v>158</v>
+      </c>
+      <c r="N9" s="283"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="411" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="411"/>
+      <c r="D10" s="411" t="s">
         <v>124</v>
       </c>
-      <c r="N7" s="354"/>
-    </row>
-    <row r="8" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="370" t="s">
+      <c r="E10" s="411"/>
+      <c r="F10" s="411" t="s">
+        <v>125</v>
+      </c>
+      <c r="G10" s="411"/>
+      <c r="H10" s="411" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" s="411"/>
+      <c r="J10" s="209"/>
+      <c r="K10" s="210"/>
+      <c r="L10" s="210"/>
+      <c r="M10" s="282"/>
+      <c r="N10" s="283"/>
+    </row>
+    <row r="11" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="211"/>
+      <c r="B11" s="411"/>
+      <c r="C11" s="411"/>
+      <c r="D11" s="411"/>
+      <c r="E11" s="411"/>
+      <c r="F11" s="411"/>
+      <c r="G11" s="411"/>
+      <c r="H11" s="411"/>
+      <c r="I11" s="411"/>
+      <c r="J11" s="212"/>
+      <c r="K11" s="210"/>
+      <c r="L11" s="210"/>
+      <c r="M11" s="279" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" s="283"/>
+    </row>
+    <row r="12" spans="1:14" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="211"/>
+      <c r="B12" s="211"/>
+      <c r="C12" s="213"/>
+      <c r="D12" s="214"/>
+      <c r="E12" s="214"/>
+      <c r="F12" s="214"/>
+      <c r="G12" s="214"/>
+      <c r="H12" s="214"/>
+      <c r="I12" s="214"/>
+      <c r="J12" s="215"/>
+      <c r="K12" s="210"/>
+      <c r="L12" s="210"/>
+      <c r="M12" s="279" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" s="284"/>
+    </row>
+    <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="412" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="413"/>
+      <c r="C13" s="413"/>
+      <c r="D13" s="413"/>
+      <c r="E13" s="413"/>
+      <c r="F13" s="413"/>
+      <c r="G13" s="413"/>
+      <c r="H13" s="413"/>
+      <c r="I13" s="413"/>
+      <c r="J13" s="414"/>
+      <c r="K13" s="210"/>
+      <c r="L13" s="210"/>
+      <c r="M13" s="279" t="s">
+        <v>25</v>
+      </c>
+      <c r="N13" s="284"/>
+    </row>
+    <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="406" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="407"/>
+      <c r="C14" s="407"/>
+      <c r="D14" s="407"/>
+      <c r="E14" s="407"/>
+      <c r="F14" s="407"/>
+      <c r="G14" s="407"/>
+      <c r="H14" s="407"/>
+      <c r="I14" s="407"/>
+      <c r="J14" s="408"/>
+      <c r="K14" s="210"/>
+      <c r="L14" s="210"/>
+      <c r="M14" s="282"/>
+      <c r="N14" s="283"/>
+    </row>
+    <row r="15" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="216"/>
+      <c r="B15" s="217"/>
+      <c r="C15" s="218"/>
+      <c r="D15" s="219"/>
+      <c r="E15" s="219"/>
+      <c r="F15" s="219"/>
+      <c r="G15" s="219"/>
+      <c r="H15" s="219"/>
+      <c r="I15" s="219"/>
+      <c r="J15" s="220"/>
+      <c r="K15" s="210"/>
+      <c r="L15" s="210"/>
+      <c r="M15" s="279" t="s">
+        <v>159</v>
+      </c>
+      <c r="N15" s="285"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="221"/>
+      <c r="B16" s="415" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="415"/>
+      <c r="D16" s="415"/>
+      <c r="E16" s="222"/>
+      <c r="F16" s="416" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16" s="416"/>
+      <c r="H16" s="222"/>
+      <c r="I16" s="417" t="s">
+        <v>128</v>
+      </c>
+      <c r="J16" s="420"/>
+      <c r="K16" s="210"/>
+      <c r="L16" s="210"/>
+      <c r="M16" s="279" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="285"/>
+    </row>
+    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="221"/>
+      <c r="B17" s="423"/>
+      <c r="C17" s="424"/>
+      <c r="D17" s="425"/>
+      <c r="E17" s="223"/>
+      <c r="F17" s="423"/>
+      <c r="G17" s="425"/>
+      <c r="H17" s="222"/>
+      <c r="I17" s="418"/>
+      <c r="J17" s="421"/>
+      <c r="K17" s="210"/>
+      <c r="L17" s="210"/>
+      <c r="M17" s="279" t="s">
+        <v>160</v>
+      </c>
+      <c r="N17" s="286"/>
+    </row>
+    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="223"/>
+      <c r="F18" s="223"/>
+      <c r="G18" s="223"/>
+      <c r="H18" s="222"/>
+      <c r="I18" s="419"/>
+      <c r="J18" s="422"/>
+      <c r="L18" s="210"/>
+      <c r="M18" s="224"/>
+    </row>
+    <row r="19" spans="1:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="225"/>
+      <c r="B19" s="223"/>
+      <c r="C19" s="223"/>
+      <c r="D19" s="222"/>
+      <c r="E19" s="223"/>
+      <c r="F19" s="212"/>
+      <c r="G19" s="223"/>
+      <c r="H19" s="222"/>
+      <c r="I19" s="223"/>
+      <c r="J19" s="226"/>
+      <c r="L19" s="210"/>
+      <c r="M19" s="224"/>
+    </row>
+    <row r="20" spans="1:14" s="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="227"/>
+      <c r="B20" s="426" t="s">
         <v>129</v>
       </c>
-      <c r="B8" s="370"/>
-      <c r="C8" s="370"/>
-      <c r="D8" s="370"/>
-      <c r="E8" s="370"/>
-      <c r="F8" s="370"/>
-      <c r="G8" s="370"/>
-      <c r="H8" s="370"/>
-      <c r="I8" s="370"/>
-      <c r="J8" s="370"/>
-      <c r="M8" s="350" t="s">
-        <v>172</v>
-      </c>
-      <c r="N8" s="355"/>
-    </row>
-    <row r="9" spans="1:14" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="280"/>
-      <c r="B9" s="280"/>
-      <c r="C9" s="280"/>
-      <c r="D9" s="280"/>
-      <c r="E9" s="280"/>
-      <c r="F9" s="280"/>
-      <c r="G9" s="280"/>
-      <c r="H9" s="280"/>
-      <c r="I9" s="280"/>
-      <c r="J9" s="280"/>
-      <c r="M9" s="350" t="s">
-        <v>173</v>
-      </c>
-      <c r="N9" s="354"/>
-    </row>
-    <row r="10" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="371" t="s">
+      <c r="C20" s="426"/>
+      <c r="D20" s="428"/>
+      <c r="F20" s="229" t="s">
         <v>130</v>
       </c>
-      <c r="C10" s="371"/>
-      <c r="D10" s="371" t="s">
+      <c r="G20" s="229"/>
+      <c r="H20" s="229"/>
+      <c r="I20" s="230"/>
+      <c r="J20" s="226"/>
+      <c r="L20" s="231"/>
+      <c r="M20" s="224"/>
+    </row>
+    <row r="21" spans="1:14" s="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="232"/>
+      <c r="B21" s="427"/>
+      <c r="C21" s="427"/>
+      <c r="D21" s="429"/>
+      <c r="F21" s="423"/>
+      <c r="G21" s="424"/>
+      <c r="H21" s="425"/>
+      <c r="I21" s="230"/>
+      <c r="J21" s="226"/>
+      <c r="L21" s="231"/>
+      <c r="M21" s="224"/>
+    </row>
+    <row r="22" spans="1:14" s="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="232"/>
+      <c r="B22" s="230"/>
+      <c r="C22" s="230"/>
+      <c r="D22" s="222"/>
+      <c r="I22" s="230"/>
+      <c r="J22" s="226"/>
+      <c r="L22" s="231"/>
+      <c r="M22" s="224"/>
+    </row>
+    <row r="23" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="233"/>
+      <c r="B23" s="234"/>
+      <c r="C23" s="234"/>
+      <c r="D23" s="234"/>
+      <c r="E23" s="234"/>
+      <c r="F23" s="234"/>
+      <c r="G23" s="234"/>
+      <c r="H23" s="234"/>
+      <c r="I23" s="234"/>
+      <c r="J23" s="235"/>
+      <c r="L23" s="236"/>
+    </row>
+    <row r="24" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="67"/>
+      <c r="B24" s="67"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="210"/>
+      <c r="L24" s="237"/>
+    </row>
+    <row r="25" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="238" t="s">
         <v>131</v>
       </c>
-      <c r="E10" s="371"/>
-      <c r="F10" s="371" t="s">
+      <c r="B25" s="239" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="240"/>
+      <c r="D25" s="240"/>
+      <c r="E25" s="240"/>
+      <c r="F25" s="240"/>
+      <c r="G25" s="241"/>
+      <c r="H25" s="242" t="s">
         <v>132</v>
       </c>
-      <c r="G10" s="371"/>
-      <c r="H10" s="371" t="s">
+      <c r="I25" s="242" t="s">
         <v>133</v>
       </c>
-      <c r="I10" s="371"/>
-      <c r="J10" s="281"/>
-      <c r="K10" s="282"/>
-      <c r="L10" s="282"/>
-      <c r="M10" s="353"/>
-      <c r="N10" s="354"/>
-    </row>
-    <row r="11" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="283"/>
-      <c r="B11" s="371"/>
-      <c r="C11" s="371"/>
-      <c r="D11" s="371"/>
-      <c r="E11" s="371"/>
-      <c r="F11" s="371"/>
-      <c r="G11" s="371"/>
-      <c r="H11" s="371"/>
-      <c r="I11" s="371"/>
-      <c r="J11" s="284"/>
-      <c r="K11" s="282"/>
-      <c r="L11" s="282"/>
-      <c r="M11" s="350" t="s">
-        <v>32</v>
-      </c>
-      <c r="N11" s="354"/>
-    </row>
-    <row r="12" spans="1:14" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="283"/>
-      <c r="B12" s="283"/>
-      <c r="C12" s="285"/>
-      <c r="D12" s="286"/>
-      <c r="E12" s="286"/>
-      <c r="F12" s="286"/>
-      <c r="G12" s="286"/>
-      <c r="H12" s="286"/>
-      <c r="I12" s="286"/>
-      <c r="J12" s="287"/>
-      <c r="K12" s="282"/>
-      <c r="L12" s="282"/>
-      <c r="M12" s="350" t="s">
-        <v>24</v>
-      </c>
-      <c r="N12" s="355"/>
-    </row>
-    <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="372" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="373"/>
-      <c r="C13" s="373"/>
-      <c r="D13" s="373"/>
-      <c r="E13" s="373"/>
-      <c r="F13" s="373"/>
-      <c r="G13" s="373"/>
-      <c r="H13" s="373"/>
-      <c r="I13" s="373"/>
-      <c r="J13" s="374"/>
-      <c r="K13" s="282"/>
-      <c r="L13" s="282"/>
-      <c r="M13" s="350" t="s">
-        <v>25</v>
-      </c>
-      <c r="N13" s="355"/>
-    </row>
-    <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="366" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" s="367"/>
-      <c r="C14" s="367"/>
-      <c r="D14" s="367"/>
-      <c r="E14" s="367"/>
-      <c r="F14" s="367"/>
-      <c r="G14" s="367"/>
-      <c r="H14" s="367"/>
-      <c r="I14" s="367"/>
-      <c r="J14" s="368"/>
-      <c r="K14" s="282"/>
-      <c r="L14" s="282"/>
-      <c r="M14" s="353"/>
-      <c r="N14" s="354"/>
-    </row>
-    <row r="15" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="288"/>
-      <c r="B15" s="289"/>
-      <c r="C15" s="290"/>
-      <c r="D15" s="291"/>
-      <c r="E15" s="291"/>
-      <c r="F15" s="291"/>
-      <c r="G15" s="291"/>
-      <c r="H15" s="291"/>
-      <c r="I15" s="291"/>
-      <c r="J15" s="292"/>
-      <c r="K15" s="282"/>
-      <c r="L15" s="282"/>
-      <c r="M15" s="350" t="s">
-        <v>174</v>
-      </c>
-      <c r="N15" s="356"/>
-    </row>
-    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="293"/>
-      <c r="B16" s="375" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="375"/>
-      <c r="D16" s="375"/>
-      <c r="E16" s="294"/>
-      <c r="F16" s="376" t="s">
+      <c r="J25" s="243" t="s">
         <v>134</v>
       </c>
-      <c r="G16" s="376"/>
-      <c r="H16" s="294"/>
-      <c r="I16" s="377" t="s">
+      <c r="K25" s="244"/>
+      <c r="L25" s="245"/>
+    </row>
+    <row r="26" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="246" t="s">
         <v>135</v>
       </c>
-      <c r="J16" s="380"/>
-      <c r="K16" s="282"/>
-      <c r="L16" s="282"/>
-      <c r="M16" s="350" t="s">
-        <v>27</v>
-      </c>
-      <c r="N16" s="356"/>
-    </row>
-    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="293"/>
-      <c r="B17" s="383"/>
-      <c r="C17" s="384"/>
-      <c r="D17" s="385"/>
-      <c r="E17" s="295"/>
-      <c r="F17" s="383"/>
-      <c r="G17" s="385"/>
-      <c r="H17" s="294"/>
-      <c r="I17" s="378"/>
-      <c r="J17" s="381"/>
-      <c r="K17" s="282"/>
-      <c r="L17" s="282"/>
-      <c r="M17" s="350" t="s">
-        <v>175</v>
-      </c>
-      <c r="N17" s="357"/>
-    </row>
-    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E18" s="295"/>
-      <c r="F18" s="295"/>
-      <c r="G18" s="295"/>
-      <c r="H18" s="294"/>
-      <c r="I18" s="379"/>
-      <c r="J18" s="382"/>
-      <c r="L18" s="282"/>
-      <c r="M18" s="296"/>
-    </row>
-    <row r="19" spans="1:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="297"/>
-      <c r="B19" s="295"/>
-      <c r="C19" s="295"/>
-      <c r="D19" s="294"/>
-      <c r="E19" s="295"/>
-      <c r="F19" s="284"/>
-      <c r="G19" s="295"/>
-      <c r="H19" s="294"/>
-      <c r="I19" s="295"/>
-      <c r="J19" s="298"/>
-      <c r="L19" s="282"/>
-      <c r="M19" s="296"/>
-    </row>
-    <row r="20" spans="1:14" s="300" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="299"/>
-      <c r="B20" s="386" t="s">
+      <c r="B26" s="247" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="248"/>
+      <c r="D26" s="248"/>
+      <c r="E26" s="249"/>
+      <c r="F26" s="249"/>
+      <c r="G26" s="250" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" s="251"/>
+      <c r="I26" s="251"/>
+      <c r="J26" s="251"/>
+      <c r="K26" s="252"/>
+      <c r="N26" s="253"/>
+    </row>
+    <row r="27" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="246" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="386"/>
-      <c r="D20" s="388"/>
-      <c r="F20" s="301" t="s">
+      <c r="B27" s="247" t="s">
         <v>137</v>
       </c>
-      <c r="G20" s="301"/>
-      <c r="H20" s="301"/>
-      <c r="I20" s="302"/>
-      <c r="J20" s="298"/>
-      <c r="L20" s="303"/>
-      <c r="M20" s="296"/>
-    </row>
-    <row r="21" spans="1:14" s="300" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="304"/>
-      <c r="B21" s="387"/>
-      <c r="C21" s="387"/>
-      <c r="D21" s="389"/>
-      <c r="F21" s="383"/>
-      <c r="G21" s="384"/>
-      <c r="H21" s="385"/>
-      <c r="I21" s="302"/>
-      <c r="J21" s="298"/>
-      <c r="L21" s="303"/>
-      <c r="M21" s="296"/>
-    </row>
-    <row r="22" spans="1:14" s="300" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="304"/>
-      <c r="B22" s="302"/>
-      <c r="C22" s="302"/>
-      <c r="D22" s="294"/>
-      <c r="I22" s="302"/>
-      <c r="J22" s="298"/>
-      <c r="L22" s="303"/>
-      <c r="M22" s="296"/>
-    </row>
-    <row r="23" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="305"/>
-      <c r="B23" s="306"/>
-      <c r="C23" s="306"/>
-      <c r="D23" s="306"/>
-      <c r="E23" s="306"/>
-      <c r="F23" s="306"/>
-      <c r="G23" s="306"/>
-      <c r="H23" s="306"/>
-      <c r="I23" s="306"/>
-      <c r="J23" s="307"/>
-      <c r="L23" s="308"/>
-    </row>
-    <row r="24" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="101"/>
-      <c r="B24" s="101"/>
-      <c r="J24" s="101"/>
-      <c r="K24" s="282"/>
-      <c r="L24" s="309"/>
-    </row>
-    <row r="25" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="310" t="s">
+      <c r="C27" s="248"/>
+      <c r="D27" s="248"/>
+      <c r="E27" s="249"/>
+      <c r="F27" s="249"/>
+      <c r="G27" s="250" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" s="254"/>
+      <c r="I27" s="254"/>
+      <c r="J27" s="254"/>
+      <c r="K27" s="255"/>
+      <c r="L27" s="253"/>
+    </row>
+    <row r="28" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="246" t="s">
         <v>138</v>
       </c>
-      <c r="B25" s="311" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="312"/>
-      <c r="D25" s="312"/>
-      <c r="E25" s="312"/>
-      <c r="F25" s="312"/>
-      <c r="G25" s="313"/>
-      <c r="H25" s="314" t="s">
+      <c r="B28" s="247" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="248"/>
+      <c r="D28" s="248"/>
+      <c r="E28" s="249"/>
+      <c r="F28" s="249"/>
+      <c r="G28" s="250" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="256"/>
+      <c r="I28" s="256"/>
+      <c r="J28" s="256"/>
+      <c r="K28" s="257"/>
+      <c r="L28" s="253"/>
+    </row>
+    <row r="29" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="246" t="s">
         <v>139</v>
       </c>
-      <c r="I25" s="314" t="s">
+      <c r="B29" s="247" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="248"/>
+      <c r="D29" s="248"/>
+      <c r="E29" s="249"/>
+      <c r="F29" s="249"/>
+      <c r="G29" s="250" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29" s="256"/>
+      <c r="I29" s="256"/>
+      <c r="J29" s="256"/>
+      <c r="K29" s="257"/>
+      <c r="L29" s="236"/>
+    </row>
+    <row r="30" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="246" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="247" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="248"/>
+      <c r="D30" s="248"/>
+      <c r="E30" s="249"/>
+      <c r="F30" s="249"/>
+      <c r="G30" s="250" t="s">
+        <v>78</v>
+      </c>
+      <c r="H30" s="254"/>
+      <c r="I30" s="254"/>
+      <c r="J30" s="254"/>
+      <c r="K30" s="257"/>
+      <c r="L30" s="210"/>
+    </row>
+    <row r="31" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="246" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="247" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="248"/>
+      <c r="D31" s="248"/>
+      <c r="E31" s="249"/>
+      <c r="F31" s="249"/>
+      <c r="G31" s="250" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="254"/>
+      <c r="I31" s="254"/>
+      <c r="J31" s="254"/>
+      <c r="K31" s="257"/>
+      <c r="L31" s="210"/>
+    </row>
+    <row r="32" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="246" t="s">
         <v>140</v>
       </c>
-      <c r="J25" s="315" t="s">
+      <c r="B32" s="247" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="248"/>
+      <c r="D32" s="248"/>
+      <c r="E32" s="249"/>
+      <c r="F32" s="249"/>
+      <c r="G32" s="250" t="s">
+        <v>79</v>
+      </c>
+      <c r="H32" s="256"/>
+      <c r="I32" s="256"/>
+      <c r="J32" s="256"/>
+      <c r="K32" s="258"/>
+      <c r="L32" s="210"/>
+    </row>
+    <row r="33" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="246" t="s">
         <v>141</v>
       </c>
-      <c r="K25" s="316"/>
-      <c r="L25" s="317"/>
-    </row>
-    <row r="26" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="318" t="s">
+      <c r="B33" s="259" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="248"/>
+      <c r="D33" s="248"/>
+      <c r="E33" s="260"/>
+      <c r="F33" s="260"/>
+      <c r="G33" s="250" t="s">
+        <v>66</v>
+      </c>
+      <c r="H33" s="261"/>
+      <c r="I33" s="261"/>
+      <c r="J33" s="261"/>
+      <c r="K33" s="262"/>
+      <c r="L33" s="210"/>
+    </row>
+    <row r="34" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="246" t="s">
         <v>142</v>
       </c>
-      <c r="B26" s="319" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="320"/>
-      <c r="D26" s="320"/>
-      <c r="E26" s="321"/>
-      <c r="F26" s="321"/>
-      <c r="G26" s="322" t="s">
-        <v>80</v>
-      </c>
-      <c r="H26" s="323"/>
-      <c r="I26" s="323"/>
-      <c r="J26" s="323"/>
-      <c r="K26" s="324"/>
-      <c r="N26" s="325"/>
-    </row>
-    <row r="27" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="318" t="s">
+      <c r="B34" s="259" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="248"/>
+      <c r="D34" s="248"/>
+      <c r="E34" s="263"/>
+      <c r="F34" s="263"/>
+      <c r="G34" s="250" t="s">
+        <v>66</v>
+      </c>
+      <c r="H34" s="261"/>
+      <c r="I34" s="261"/>
+      <c r="J34" s="261"/>
+      <c r="K34" s="264"/>
+      <c r="L34" s="210"/>
+    </row>
+    <row r="35" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="246" t="s">
         <v>143</v>
       </c>
-      <c r="B27" s="319" t="s">
+      <c r="B35" s="259" t="s">
         <v>144</v>
       </c>
-      <c r="C27" s="320"/>
-      <c r="D27" s="320"/>
-      <c r="E27" s="321"/>
-      <c r="F27" s="321"/>
-      <c r="G27" s="322" t="s">
-        <v>80</v>
-      </c>
-      <c r="H27" s="326"/>
-      <c r="I27" s="326"/>
-      <c r="J27" s="326"/>
-      <c r="K27" s="327"/>
-      <c r="L27" s="325"/>
-    </row>
-    <row r="28" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="318" t="s">
+      <c r="C35" s="248"/>
+      <c r="D35" s="248"/>
+      <c r="E35" s="263"/>
+      <c r="F35" s="263"/>
+      <c r="G35" s="250" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="265"/>
+      <c r="I35" s="265"/>
+      <c r="J35" s="265"/>
+      <c r="K35" s="210"/>
+      <c r="L35" s="210"/>
+    </row>
+    <row r="36" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="246" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="319" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" s="320"/>
-      <c r="D28" s="320"/>
-      <c r="E28" s="321"/>
-      <c r="F28" s="321"/>
-      <c r="G28" s="322" t="s">
-        <v>80</v>
-      </c>
-      <c r="H28" s="328"/>
-      <c r="I28" s="328"/>
-      <c r="J28" s="328"/>
-      <c r="K28" s="329"/>
-      <c r="L28" s="325"/>
-    </row>
-    <row r="29" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="318" t="s">
+      <c r="B36" s="266" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="248"/>
+      <c r="D36" s="248"/>
+      <c r="E36" s="263"/>
+      <c r="F36" s="263"/>
+      <c r="G36" s="250" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="430">
+        <v>31</v>
+      </c>
+      <c r="I36" s="431"/>
+      <c r="J36" s="432"/>
+      <c r="K36" s="210"/>
+      <c r="L36" s="210"/>
+    </row>
+    <row r="37" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="267"/>
+      <c r="B37" s="267"/>
+      <c r="C37" s="268"/>
+      <c r="D37" s="269"/>
+      <c r="E37" s="269"/>
+      <c r="F37" s="269"/>
+      <c r="G37" s="269"/>
+      <c r="H37" s="269"/>
+      <c r="I37" s="269"/>
+      <c r="J37" s="270"/>
+      <c r="K37" s="210"/>
+      <c r="L37" s="210"/>
+    </row>
+    <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="433" t="s">
         <v>146</v>
       </c>
-      <c r="B29" s="319" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" s="320"/>
-      <c r="D29" s="320"/>
-      <c r="E29" s="321"/>
-      <c r="F29" s="321"/>
-      <c r="G29" s="322" t="s">
-        <v>85</v>
-      </c>
-      <c r="H29" s="328"/>
-      <c r="I29" s="328"/>
-      <c r="J29" s="328"/>
-      <c r="K29" s="329"/>
-      <c r="L29" s="308"/>
-    </row>
-    <row r="30" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="318" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="319" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="320"/>
-      <c r="D30" s="320"/>
-      <c r="E30" s="321"/>
-      <c r="F30" s="321"/>
-      <c r="G30" s="322" t="s">
-        <v>80</v>
-      </c>
-      <c r="H30" s="326"/>
-      <c r="I30" s="326"/>
-      <c r="J30" s="326"/>
-      <c r="K30" s="329"/>
-      <c r="L30" s="282"/>
-    </row>
-    <row r="31" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="318" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="319" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="320"/>
-      <c r="D31" s="320"/>
-      <c r="E31" s="321"/>
-      <c r="F31" s="321"/>
-      <c r="G31" s="322" t="s">
-        <v>80</v>
-      </c>
-      <c r="H31" s="326"/>
-      <c r="I31" s="326"/>
-      <c r="J31" s="326"/>
-      <c r="K31" s="329"/>
-      <c r="L31" s="282"/>
-    </row>
-    <row r="32" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="318" t="s">
+      <c r="B38" s="434"/>
+      <c r="C38" s="435"/>
+      <c r="D38" s="433" t="s">
         <v>147</v>
       </c>
-      <c r="B32" s="319" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="320"/>
-      <c r="D32" s="320"/>
-      <c r="E32" s="321"/>
-      <c r="F32" s="321"/>
-      <c r="G32" s="322" t="s">
-        <v>81</v>
-      </c>
-      <c r="H32" s="328"/>
-      <c r="I32" s="328"/>
-      <c r="J32" s="328"/>
-      <c r="K32" s="330"/>
-      <c r="L32" s="282"/>
-    </row>
-    <row r="33" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="318" t="s">
+      <c r="E38" s="435"/>
+      <c r="F38" s="271" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" s="272"/>
+      <c r="H38" s="272"/>
+      <c r="I38" s="272"/>
+      <c r="J38" s="273"/>
+      <c r="K38" s="210"/>
+      <c r="L38" s="210"/>
+    </row>
+    <row r="39" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="436" t="s">
         <v>148</v>
       </c>
-      <c r="B33" s="331" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="320"/>
-      <c r="D33" s="320"/>
-      <c r="E33" s="332"/>
-      <c r="F33" s="332"/>
-      <c r="G33" s="322" t="s">
-        <v>66</v>
-      </c>
-      <c r="H33" s="333"/>
-      <c r="I33" s="333"/>
-      <c r="J33" s="333"/>
-      <c r="K33" s="334"/>
-      <c r="L33" s="282"/>
-    </row>
-    <row r="34" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="318" t="s">
+      <c r="B39" s="437"/>
+      <c r="C39" s="438"/>
+      <c r="D39" s="436"/>
+      <c r="E39" s="438"/>
+      <c r="F39" s="233"/>
+      <c r="G39" s="234"/>
+      <c r="H39" s="234"/>
+      <c r="I39" s="234"/>
+      <c r="J39" s="235"/>
+      <c r="K39" s="210"/>
+      <c r="L39" s="210"/>
+    </row>
+    <row r="40" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="436" t="s">
         <v>149</v>
       </c>
-      <c r="B34" s="331" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" s="320"/>
-      <c r="D34" s="320"/>
-      <c r="E34" s="335"/>
-      <c r="F34" s="335"/>
-      <c r="G34" s="322" t="s">
-        <v>66</v>
-      </c>
-      <c r="H34" s="333"/>
-      <c r="I34" s="333"/>
-      <c r="J34" s="333"/>
-      <c r="K34" s="336"/>
-      <c r="L34" s="282"/>
-    </row>
-    <row r="35" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="318" t="s">
+      <c r="B40" s="437"/>
+      <c r="C40" s="438"/>
+      <c r="D40" s="436"/>
+      <c r="E40" s="438"/>
+      <c r="F40" s="274"/>
+      <c r="G40" s="272"/>
+      <c r="H40" s="272"/>
+      <c r="I40" s="272"/>
+      <c r="J40" s="272"/>
+      <c r="K40" s="210"/>
+      <c r="L40" s="210"/>
+    </row>
+    <row r="41" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="436" t="s">
         <v>150</v>
       </c>
-      <c r="B35" s="331" t="s">
+      <c r="B41" s="437"/>
+      <c r="C41" s="438"/>
+      <c r="D41" s="436"/>
+      <c r="E41" s="438"/>
+      <c r="F41" s="221"/>
+      <c r="K41" s="210"/>
+      <c r="L41" s="210"/>
+    </row>
+    <row r="42" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="440" t="s">
         <v>151</v>
       </c>
-      <c r="C35" s="320"/>
-      <c r="D35" s="320"/>
-      <c r="E35" s="335"/>
-      <c r="F35" s="335"/>
-      <c r="G35" s="322" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="208"/>
-      <c r="I35" s="208"/>
-      <c r="J35" s="208"/>
-      <c r="K35" s="282"/>
-      <c r="L35" s="282"/>
-    </row>
-    <row r="36" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="318" t="s">
+      <c r="B42" s="441"/>
+      <c r="C42" s="442"/>
+      <c r="D42" s="436"/>
+      <c r="E42" s="438"/>
+      <c r="F42" s="221"/>
+      <c r="K42" s="210"/>
+      <c r="L42" s="210"/>
+    </row>
+    <row r="43" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="440" t="s">
         <v>152</v>
       </c>
-      <c r="B36" s="337" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="320"/>
-      <c r="D36" s="320"/>
-      <c r="E36" s="335"/>
-      <c r="F36" s="335"/>
-      <c r="G36" s="322" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36" s="425"/>
-      <c r="I36" s="426"/>
-      <c r="J36" s="427"/>
-      <c r="K36" s="282"/>
-      <c r="L36" s="282"/>
-    </row>
-    <row r="37" spans="1:12" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="338"/>
-      <c r="B37" s="338"/>
-      <c r="C37" s="339"/>
-      <c r="D37" s="340"/>
-      <c r="E37" s="340"/>
-      <c r="F37" s="340"/>
-      <c r="G37" s="340"/>
-      <c r="H37" s="340"/>
-      <c r="I37" s="340"/>
-      <c r="J37" s="341"/>
-      <c r="K37" s="282"/>
-      <c r="L37" s="282"/>
-    </row>
-    <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="390" t="s">
+      <c r="B43" s="441"/>
+      <c r="C43" s="442"/>
+      <c r="D43" s="436"/>
+      <c r="E43" s="438"/>
+      <c r="F43" s="221"/>
+      <c r="K43" s="210"/>
+      <c r="L43" s="210"/>
+    </row>
+    <row r="44" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="436" t="s">
         <v>153</v>
       </c>
-      <c r="B38" s="391"/>
-      <c r="C38" s="392"/>
-      <c r="D38" s="390" t="s">
+      <c r="B44" s="437"/>
+      <c r="C44" s="438"/>
+      <c r="D44" s="436"/>
+      <c r="E44" s="438"/>
+      <c r="F44" s="221"/>
+      <c r="K44" s="210"/>
+      <c r="L44" s="210"/>
+    </row>
+    <row r="45" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="436" t="s">
         <v>154</v>
       </c>
-      <c r="E38" s="392"/>
-      <c r="F38" s="342" t="s">
-        <v>104</v>
-      </c>
-      <c r="G38" s="343"/>
-      <c r="H38" s="343"/>
-      <c r="I38" s="343"/>
-      <c r="J38" s="344"/>
-      <c r="K38" s="282"/>
-      <c r="L38" s="282"/>
-    </row>
-    <row r="39" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="393" t="s">
+      <c r="B45" s="437"/>
+      <c r="C45" s="438"/>
+      <c r="D45" s="436"/>
+      <c r="E45" s="438"/>
+      <c r="F45" s="221"/>
+      <c r="K45" s="210"/>
+      <c r="L45" s="210"/>
+    </row>
+    <row r="46" spans="1:12" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="275"/>
+      <c r="B46" s="275"/>
+      <c r="C46" s="270"/>
+      <c r="D46" s="270"/>
+      <c r="E46" s="270"/>
+      <c r="F46" s="270"/>
+      <c r="G46" s="270"/>
+      <c r="H46" s="270"/>
+      <c r="I46" s="270"/>
+      <c r="J46" s="270"/>
+      <c r="K46" s="210"/>
+      <c r="L46" s="210"/>
+    </row>
+    <row r="47" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="276"/>
+      <c r="B47" s="276"/>
+      <c r="C47" s="270"/>
+      <c r="J47" s="270"/>
+      <c r="K47" s="210"/>
+      <c r="L47" s="210"/>
+    </row>
+    <row r="48" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="276"/>
+      <c r="B48" s="276"/>
+      <c r="C48" s="270"/>
+      <c r="J48" s="270"/>
+      <c r="K48" s="210"/>
+      <c r="L48" s="210"/>
+    </row>
+    <row r="49" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="276"/>
+      <c r="B49" s="276"/>
+      <c r="C49" s="270"/>
+      <c r="J49" s="270"/>
+      <c r="K49" s="210"/>
+      <c r="L49" s="210"/>
+    </row>
+    <row r="50" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="277"/>
+      <c r="B50" s="277"/>
+      <c r="C50" s="270"/>
+      <c r="D50" s="270"/>
+      <c r="E50" s="270"/>
+      <c r="F50" s="270"/>
+      <c r="G50" s="270"/>
+      <c r="H50" s="270"/>
+      <c r="I50" s="270"/>
+      <c r="J50" s="270"/>
+      <c r="K50" s="210"/>
+      <c r="L50" s="210"/>
+    </row>
+    <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="278" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51" s="278"/>
+      <c r="C51" s="270"/>
+      <c r="D51" s="270"/>
+      <c r="E51" s="270"/>
+      <c r="F51" s="270"/>
+      <c r="G51" s="270"/>
+      <c r="H51" s="270"/>
+      <c r="I51" s="270"/>
+      <c r="J51" s="270"/>
+      <c r="K51" s="210"/>
+      <c r="L51" s="210"/>
+    </row>
+    <row r="52" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="278" t="s">
         <v>155</v>
       </c>
-      <c r="B39" s="394"/>
-      <c r="C39" s="395"/>
-      <c r="D39" s="393" t="s">
+      <c r="B52" s="278"/>
+      <c r="C52" s="270"/>
+      <c r="D52" s="270"/>
+      <c r="E52" s="270"/>
+      <c r="F52" s="255" t="s">
         <v>156</v>
       </c>
-      <c r="E39" s="395"/>
-      <c r="F39" s="305"/>
-      <c r="G39" s="306"/>
-      <c r="H39" s="306"/>
-      <c r="I39" s="306"/>
-      <c r="J39" s="307"/>
-      <c r="K39" s="282"/>
-      <c r="L39" s="282"/>
-    </row>
-    <row r="40" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="393" t="s">
-        <v>157</v>
-      </c>
-      <c r="B40" s="394"/>
-      <c r="C40" s="395"/>
-      <c r="D40" s="393" t="s">
-        <v>158</v>
-      </c>
-      <c r="E40" s="395"/>
-      <c r="F40" s="345"/>
-      <c r="G40" s="343"/>
-      <c r="H40" s="343"/>
-      <c r="I40" s="343"/>
-      <c r="J40" s="343"/>
-      <c r="K40" s="282"/>
-      <c r="L40" s="282"/>
-    </row>
-    <row r="41" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="393" t="s">
-        <v>159</v>
-      </c>
-      <c r="B41" s="394"/>
-      <c r="C41" s="395"/>
-      <c r="D41" s="393" t="s">
-        <v>160</v>
-      </c>
-      <c r="E41" s="395"/>
-      <c r="F41" s="293"/>
-      <c r="K41" s="282"/>
-      <c r="L41" s="282"/>
-    </row>
-    <row r="42" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="397" t="s">
-        <v>161</v>
-      </c>
-      <c r="B42" s="398"/>
-      <c r="C42" s="399"/>
-      <c r="D42" s="393" t="s">
-        <v>162</v>
-      </c>
-      <c r="E42" s="395"/>
-      <c r="F42" s="293"/>
-      <c r="K42" s="282"/>
-      <c r="L42" s="282"/>
-    </row>
-    <row r="43" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="397" t="s">
-        <v>163</v>
-      </c>
-      <c r="B43" s="398"/>
-      <c r="C43" s="399"/>
-      <c r="D43" s="393" t="s">
-        <v>164</v>
-      </c>
-      <c r="E43" s="395"/>
-      <c r="F43" s="293"/>
-      <c r="K43" s="282"/>
-      <c r="L43" s="282"/>
-    </row>
-    <row r="44" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="393" t="s">
-        <v>165</v>
-      </c>
-      <c r="B44" s="394"/>
-      <c r="C44" s="395"/>
-      <c r="D44" s="393" t="s">
-        <v>166</v>
-      </c>
-      <c r="E44" s="395"/>
-      <c r="F44" s="293"/>
-      <c r="K44" s="282"/>
-      <c r="L44" s="282"/>
-    </row>
-    <row r="45" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="393" t="s">
-        <v>167</v>
-      </c>
-      <c r="B45" s="394"/>
-      <c r="C45" s="395"/>
-      <c r="D45" s="393" t="s">
-        <v>168</v>
-      </c>
-      <c r="E45" s="395"/>
-      <c r="F45" s="293"/>
-      <c r="K45" s="282"/>
-      <c r="L45" s="282"/>
-    </row>
-    <row r="46" spans="1:12" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="346"/>
-      <c r="B46" s="346"/>
-      <c r="C46" s="341"/>
-      <c r="D46" s="341"/>
-      <c r="E46" s="341"/>
-      <c r="F46" s="341"/>
-      <c r="G46" s="341"/>
-      <c r="H46" s="341"/>
-      <c r="I46" s="341"/>
-      <c r="J46" s="341"/>
-      <c r="K46" s="282"/>
-      <c r="L46" s="282"/>
-    </row>
-    <row r="47" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="347"/>
-      <c r="B47" s="347"/>
-      <c r="C47" s="341"/>
-      <c r="J47" s="341"/>
-      <c r="K47" s="282"/>
-      <c r="L47" s="282"/>
-    </row>
-    <row r="48" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="347"/>
-      <c r="B48" s="347"/>
-      <c r="C48" s="341"/>
-      <c r="J48" s="341"/>
-      <c r="K48" s="282"/>
-      <c r="L48" s="282"/>
-    </row>
-    <row r="49" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="347"/>
-      <c r="B49" s="347"/>
-      <c r="C49" s="341"/>
-      <c r="J49" s="341"/>
-      <c r="K49" s="282"/>
-      <c r="L49" s="282"/>
-    </row>
-    <row r="50" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="348"/>
-      <c r="B50" s="348"/>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
-      <c r="G50" s="341"/>
-      <c r="H50" s="341"/>
-      <c r="I50" s="341"/>
-      <c r="J50" s="341"/>
-      <c r="K50" s="282"/>
-      <c r="L50" s="282"/>
-    </row>
-    <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="349" t="s">
-        <v>18</v>
-      </c>
-      <c r="B51" s="349"/>
-      <c r="C51" s="341"/>
-      <c r="D51" s="341"/>
-      <c r="E51" s="341"/>
-      <c r="F51" s="341"/>
-      <c r="G51" s="341"/>
-      <c r="H51" s="341"/>
-      <c r="I51" s="341"/>
-      <c r="J51" s="341"/>
-      <c r="K51" s="282"/>
-      <c r="L51" s="282"/>
-    </row>
-    <row r="52" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="349" t="s">
-        <v>169</v>
-      </c>
-      <c r="B52" s="349"/>
-      <c r="C52" s="341"/>
-      <c r="D52" s="341"/>
-      <c r="E52" s="341"/>
-      <c r="F52" s="327" t="s">
-        <v>170</v>
-      </c>
-      <c r="G52" s="341"/>
-      <c r="H52" s="341"/>
-      <c r="I52" s="341"/>
-      <c r="J52" s="341"/>
-      <c r="K52" s="282"/>
-      <c r="L52" s="282"/>
+      <c r="G52" s="270"/>
+      <c r="H52" s="270"/>
+      <c r="I52" s="270"/>
+      <c r="J52" s="270"/>
+      <c r="K52" s="210"/>
+      <c r="L52" s="210"/>
     </row>
     <row r="53" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="396" t="s">
-        <v>171</v>
-      </c>
-      <c r="B54" s="396"/>
-      <c r="C54" s="396"/>
-      <c r="D54" s="396"/>
-      <c r="E54" s="396"/>
-      <c r="F54" s="396"/>
-      <c r="G54" s="396"/>
-      <c r="H54" s="396"/>
-      <c r="I54" s="396"/>
-      <c r="J54" s="396"/>
+      <c r="A54" s="439" t="s">
+        <v>170</v>
+      </c>
+      <c r="B54" s="439"/>
+      <c r="C54" s="439"/>
+      <c r="D54" s="439"/>
+      <c r="E54" s="439"/>
+      <c r="F54" s="439"/>
+      <c r="G54" s="439"/>
+      <c r="H54" s="439"/>
+      <c r="I54" s="439"/>
+      <c r="J54" s="439"/>
     </row>
     <row r="55" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6431,995 +6603,1022 @@
   <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="28" customWidth="1"/>
-    <col min="2" max="2" width="2.109375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="4.5546875" style="28" customWidth="1"/>
-    <col min="4" max="4" width="1.6640625" style="28" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" style="28" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" style="28" customWidth="1"/>
-    <col min="7" max="7" width="8.109375" style="28" customWidth="1"/>
-    <col min="8" max="8" width="6.5546875" style="28" customWidth="1"/>
-    <col min="9" max="11" width="10.5546875" style="28" customWidth="1"/>
-    <col min="12" max="12" width="1.5546875" style="28" customWidth="1"/>
-    <col min="13" max="13" width="13.5546875" style="28" customWidth="1"/>
-    <col min="14" max="14" width="6.44140625" style="28" customWidth="1"/>
-    <col min="15" max="15" width="8.5546875" style="28" customWidth="1"/>
-    <col min="16" max="16" width="8" style="28" customWidth="1"/>
-    <col min="17" max="17" width="13.33203125" style="28" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="10.33203125" style="28"/>
+    <col min="1" max="1" width="11.33203125" style="296" customWidth="1"/>
+    <col min="2" max="2" width="2.109375" style="296" customWidth="1"/>
+    <col min="3" max="3" width="4.5546875" style="296" customWidth="1"/>
+    <col min="4" max="4" width="1.6640625" style="296" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" style="296" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="296" customWidth="1"/>
+    <col min="7" max="7" width="8.109375" style="296" customWidth="1"/>
+    <col min="8" max="8" width="6.5546875" style="296" customWidth="1"/>
+    <col min="9" max="11" width="10.5546875" style="296" customWidth="1"/>
+    <col min="12" max="12" width="1.5546875" style="296" customWidth="1"/>
+    <col min="13" max="13" width="13.5546875" style="296" customWidth="1"/>
+    <col min="14" max="14" width="6.44140625" style="296" customWidth="1"/>
+    <col min="15" max="15" width="8.5546875" style="296" customWidth="1"/>
+    <col min="16" max="16" width="8" style="296" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" style="296" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="10.33203125" style="296"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50"/>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
+      <c r="A1" s="293"/>
+      <c r="B1" s="293"/>
+      <c r="C1" s="293"/>
+      <c r="D1" s="293"/>
+      <c r="E1" s="293"/>
+      <c r="F1" s="294"/>
+      <c r="G1" s="294"/>
+      <c r="H1" s="294"/>
+      <c r="I1" s="294"/>
+      <c r="J1" s="294"/>
+      <c r="K1" s="295"/>
+      <c r="L1" s="295"/>
+      <c r="M1" s="295"/>
     </row>
     <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="400" t="s">
+      <c r="A2" s="443" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="400"/>
-      <c r="C2" s="400"/>
-      <c r="D2" s="400"/>
-      <c r="E2" s="400"/>
-      <c r="F2" s="400"/>
-      <c r="G2" s="400"/>
-      <c r="H2" s="400"/>
-      <c r="I2" s="400"/>
-      <c r="J2" s="400"/>
-      <c r="K2" s="400"/>
-      <c r="L2" s="400"/>
-      <c r="M2" s="400"/>
+      <c r="B2" s="443"/>
+      <c r="C2" s="443"/>
+      <c r="D2" s="443"/>
+      <c r="E2" s="443"/>
+      <c r="F2" s="443"/>
+      <c r="G2" s="443"/>
+      <c r="H2" s="443"/>
+      <c r="I2" s="443"/>
+      <c r="J2" s="443"/>
+      <c r="K2" s="443"/>
+      <c r="L2" s="443"/>
+      <c r="M2" s="443"/>
     </row>
     <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="401">
+      <c r="A3" s="444">
         <v>0</v>
       </c>
-      <c r="B3" s="401"/>
-      <c r="C3" s="401"/>
-      <c r="D3" s="401"/>
-      <c r="E3" s="401"/>
-      <c r="F3" s="401"/>
-      <c r="G3" s="401"/>
-      <c r="H3" s="401"/>
-      <c r="I3" s="401"/>
-      <c r="J3" s="401"/>
-      <c r="K3" s="401"/>
-      <c r="L3" s="401"/>
-      <c r="M3" s="401"/>
+      <c r="B3" s="444"/>
+      <c r="C3" s="444"/>
+      <c r="D3" s="444"/>
+      <c r="E3" s="444"/>
+      <c r="F3" s="444"/>
+      <c r="G3" s="444"/>
+      <c r="H3" s="444"/>
+      <c r="I3" s="444"/>
+      <c r="J3" s="444"/>
+      <c r="K3" s="444"/>
+      <c r="L3" s="444"/>
+      <c r="M3" s="444"/>
     </row>
     <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="297" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="412">
+      <c r="C5" s="455">
         <f>+FORMATO!N2</f>
         <v>0</v>
       </c>
-      <c r="D5" s="412"/>
-      <c r="E5" s="412"/>
-      <c r="F5" s="412"/>
-      <c r="G5" s="412"/>
-      <c r="H5" s="412"/>
-      <c r="I5" s="412"/>
-      <c r="J5" s="412"/>
-      <c r="K5" s="55" t="s">
+      <c r="D5" s="455"/>
+      <c r="E5" s="455"/>
+      <c r="F5" s="455"/>
+      <c r="G5" s="455"/>
+      <c r="H5" s="455"/>
+      <c r="I5" s="455"/>
+      <c r="J5" s="455"/>
+      <c r="K5" s="299" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="56" t="s">
+      <c r="L5" s="300" t="s">
         <v>0</v>
       </c>
-      <c r="M5" s="59" t="s">
+      <c r="M5" s="301" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="297" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="412">
+      <c r="C6" s="455">
         <f>+FORMATO!N3</f>
         <v>0</v>
       </c>
-      <c r="D6" s="412"/>
-      <c r="E6" s="412"/>
-      <c r="F6" s="412"/>
-      <c r="G6" s="412"/>
-      <c r="H6" s="412"/>
-      <c r="I6" s="412"/>
-      <c r="J6" s="412"/>
-      <c r="K6" s="57" t="s">
-        <v>124</v>
-      </c>
-      <c r="L6" s="54" t="s">
+      <c r="D6" s="455"/>
+      <c r="E6" s="455"/>
+      <c r="F6" s="455"/>
+      <c r="G6" s="455"/>
+      <c r="H6" s="455"/>
+      <c r="I6" s="455"/>
+      <c r="J6" s="455"/>
+      <c r="K6" s="279" t="s">
+        <v>119</v>
+      </c>
+      <c r="L6" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="M6" s="265">
+      <c r="M6" s="302">
         <f>+FORMATO!N7</f>
         <v>0</v>
       </c>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
+      <c r="N6" s="303"/>
+      <c r="O6" s="303"/>
+      <c r="P6" s="303"/>
     </row>
     <row r="7" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="297" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="412">
+      <c r="C7" s="455">
         <f>+FORMATO!N4</f>
         <v>0</v>
       </c>
-      <c r="D7" s="412"/>
-      <c r="E7" s="412"/>
-      <c r="F7" s="412"/>
-      <c r="G7" s="412"/>
-      <c r="H7" s="412"/>
-      <c r="I7" s="412"/>
-      <c r="J7" s="412"/>
-      <c r="K7" s="365" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" s="54" t="s">
+      <c r="D7" s="455"/>
+      <c r="E7" s="455"/>
+      <c r="F7" s="455"/>
+      <c r="G7" s="455"/>
+      <c r="H7" s="455"/>
+      <c r="I7" s="455"/>
+      <c r="J7" s="455"/>
+      <c r="K7" s="279" t="s">
+        <v>158</v>
+      </c>
+      <c r="L7" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="M7" s="244">
-        <f>+FORMATO!N8</f>
+      <c r="M7" s="302">
+        <f>+FORMATO!N9</f>
         <v>0</v>
       </c>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-    </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="N7" s="303"/>
+      <c r="O7" s="303"/>
+      <c r="P7" s="303"/>
+    </row>
+    <row r="8" spans="1:16" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="297" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="412">
+      <c r="C8" s="455">
         <f>+FORMATO!N5</f>
         <v>0</v>
       </c>
-      <c r="D8" s="412"/>
-      <c r="E8" s="412"/>
-      <c r="F8" s="412"/>
-      <c r="G8" s="412"/>
-      <c r="H8" s="412"/>
-      <c r="I8" s="412"/>
-      <c r="J8" s="412"/>
-      <c r="K8" s="412"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
+      <c r="D8" s="455"/>
+      <c r="E8" s="455"/>
+      <c r="F8" s="455"/>
+      <c r="G8" s="455"/>
+      <c r="H8" s="455"/>
+      <c r="I8" s="455"/>
+      <c r="J8" s="455"/>
+      <c r="K8" s="304" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="298" t="s">
+        <v>0</v>
+      </c>
+      <c r="M8" s="305">
+        <f>+FORMATO!N9</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="303"/>
+      <c r="O8" s="303"/>
+      <c r="P8" s="303"/>
     </row>
     <row r="9" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="204" t="s">
-        <v>105</v>
-      </c>
-      <c r="B9" s="96"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="57"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
+      <c r="A9" s="306" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="307"/>
+      <c r="C9" s="307"/>
+      <c r="D9" s="298"/>
+      <c r="E9" s="308"/>
+      <c r="F9" s="308"/>
+      <c r="G9" s="308"/>
+      <c r="H9" s="308"/>
+      <c r="I9" s="308"/>
+      <c r="J9" s="309"/>
+      <c r="K9" s="279"/>
+      <c r="L9" s="298"/>
+      <c r="M9" s="310"/>
+      <c r="N9" s="303"/>
+      <c r="O9" s="303"/>
+      <c r="P9" s="303"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="404" t="s">
+      <c r="A10" s="447" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="405"/>
-      <c r="C10" s="405"/>
-      <c r="D10" s="405"/>
-      <c r="E10" s="405"/>
-      <c r="F10" s="405"/>
-      <c r="G10" s="405"/>
-      <c r="H10" s="405"/>
-      <c r="I10" s="405"/>
-      <c r="J10" s="405"/>
-      <c r="K10" s="405"/>
-      <c r="L10" s="405"/>
-      <c r="M10" s="406"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="30"/>
+      <c r="B10" s="448"/>
+      <c r="C10" s="448"/>
+      <c r="D10" s="448"/>
+      <c r="E10" s="448"/>
+      <c r="F10" s="448"/>
+      <c r="G10" s="448"/>
+      <c r="H10" s="448"/>
+      <c r="I10" s="448"/>
+      <c r="J10" s="448"/>
+      <c r="K10" s="448"/>
+      <c r="L10" s="448"/>
+      <c r="M10" s="449"/>
+      <c r="N10" s="303"/>
+      <c r="O10" s="303"/>
+      <c r="P10" s="303"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="407" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11" s="408"/>
-      <c r="C11" s="408"/>
-      <c r="D11" s="408"/>
-      <c r="E11" s="408"/>
-      <c r="F11" s="408"/>
-      <c r="G11" s="408"/>
-      <c r="H11" s="408"/>
-      <c r="I11" s="408"/>
-      <c r="J11" s="408"/>
-      <c r="K11" s="408"/>
-      <c r="L11" s="408"/>
-      <c r="M11" s="409"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
+      <c r="A11" s="450" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="451"/>
+      <c r="C11" s="451"/>
+      <c r="D11" s="451"/>
+      <c r="E11" s="451"/>
+      <c r="F11" s="451"/>
+      <c r="G11" s="451"/>
+      <c r="H11" s="451"/>
+      <c r="I11" s="451"/>
+      <c r="J11" s="451"/>
+      <c r="K11" s="451"/>
+      <c r="L11" s="451"/>
+      <c r="M11" s="452"/>
+      <c r="N11" s="303"/>
+      <c r="O11" s="303"/>
+      <c r="P11" s="303"/>
     </row>
     <row r="12" spans="1:16" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="34"/>
-      <c r="B12" s="97"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="37"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30"/>
+      <c r="A12" s="311"/>
+      <c r="B12" s="312"/>
+      <c r="C12" s="312"/>
+      <c r="D12" s="313"/>
+      <c r="E12" s="314"/>
+      <c r="F12" s="315"/>
+      <c r="G12" s="314"/>
+      <c r="H12" s="314"/>
+      <c r="I12" s="314"/>
+      <c r="J12" s="314"/>
+      <c r="K12" s="316"/>
+      <c r="L12" s="313"/>
+      <c r="M12" s="317"/>
+      <c r="N12" s="303"/>
+      <c r="O12" s="303"/>
+      <c r="P12" s="303"/>
     </row>
     <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="410" t="s">
+      <c r="A13" s="453" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="411"/>
-      <c r="C13" s="411"/>
-      <c r="D13" s="411"/>
-      <c r="E13" s="411"/>
-      <c r="F13" s="245"/>
-      <c r="G13" s="245"/>
-      <c r="H13" s="245"/>
-      <c r="I13" s="245"/>
-      <c r="J13" s="246"/>
-      <c r="K13" s="246"/>
-      <c r="L13" s="246"/>
-      <c r="M13" s="39"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="30"/>
+      <c r="B13" s="454"/>
+      <c r="C13" s="454"/>
+      <c r="D13" s="454"/>
+      <c r="E13" s="454"/>
+      <c r="F13" s="318"/>
+      <c r="G13" s="318"/>
+      <c r="H13" s="318"/>
+      <c r="I13" s="318"/>
+      <c r="J13" s="319"/>
+      <c r="K13" s="319"/>
+      <c r="L13" s="319"/>
+      <c r="M13" s="320"/>
+      <c r="O13" s="303"/>
+      <c r="P13" s="303"/>
     </row>
     <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="61" t="s">
+      <c r="A14" s="321" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="247"/>
-      <c r="C14" s="247"/>
-      <c r="D14" s="248" t="s">
+      <c r="B14" s="322"/>
+      <c r="C14" s="322"/>
+      <c r="D14" s="323" t="s">
         <v>0</v>
       </c>
-      <c r="E14" s="364">
+      <c r="E14" s="324">
         <f>+FORMATO!N15</f>
         <v>0</v>
       </c>
-      <c r="F14" s="248"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="249" t="s">
+      <c r="F14" s="323"/>
+      <c r="G14" s="325"/>
+      <c r="H14" s="326"/>
+      <c r="I14" s="326"/>
+      <c r="J14" s="327"/>
+      <c r="K14" s="328" t="s">
         <v>32</v>
       </c>
-      <c r="L14" s="250" t="s">
+      <c r="L14" s="329" t="s">
         <v>0</v>
       </c>
-      <c r="M14" s="266">
+      <c r="M14" s="330">
         <f>+FORMATO!N11</f>
         <v>0</v>
       </c>
-      <c r="O14" s="30"/>
+      <c r="O14" s="303"/>
     </row>
     <row r="15" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="321" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="247"/>
-      <c r="C15" s="247"/>
-      <c r="D15" s="248" t="s">
+      <c r="B15" s="322"/>
+      <c r="C15" s="322"/>
+      <c r="D15" s="323" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="364">
+      <c r="E15" s="324">
         <f>+FORMATO!N16</f>
         <v>0</v>
       </c>
-      <c r="F15" s="248"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="249" t="s">
+      <c r="F15" s="323"/>
+      <c r="G15" s="325"/>
+      <c r="H15" s="326"/>
+      <c r="I15" s="326"/>
+      <c r="J15" s="327"/>
+      <c r="K15" s="328" t="s">
         <v>24</v>
       </c>
-      <c r="L15" s="250" t="s">
+      <c r="L15" s="329" t="s">
         <v>0</v>
       </c>
-      <c r="M15" s="251">
+      <c r="M15" s="331">
         <f>+FORMATO!N12</f>
         <v>0</v>
       </c>
-      <c r="O15" s="30"/>
-      <c r="P15" s="30"/>
+      <c r="O15" s="303"/>
+      <c r="P15" s="303"/>
     </row>
     <row r="16" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="61" t="s">
-        <v>123</v>
-      </c>
-      <c r="B16" s="247"/>
-      <c r="C16" s="247"/>
-      <c r="D16" s="248" t="s">
+      <c r="A16" s="321" t="s">
+        <v>118</v>
+      </c>
+      <c r="B16" s="322"/>
+      <c r="C16" s="322"/>
+      <c r="D16" s="323" t="s">
         <v>0</v>
       </c>
-      <c r="E16" s="364">
+      <c r="E16" s="324">
         <f>+FORMATO!N17</f>
         <v>0</v>
       </c>
-      <c r="F16" s="248"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="63"/>
-      <c r="K16" s="249" t="s">
+      <c r="F16" s="323"/>
+      <c r="G16" s="325"/>
+      <c r="H16" s="326"/>
+      <c r="I16" s="326"/>
+      <c r="J16" s="327"/>
+      <c r="K16" s="328" t="s">
         <v>25</v>
       </c>
-      <c r="L16" s="250" t="s">
+      <c r="L16" s="329" t="s">
         <v>0</v>
       </c>
-      <c r="M16" s="251">
+      <c r="M16" s="331">
         <f>+FORMATO!N13</f>
         <v>0</v>
       </c>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
+      <c r="O16" s="303"/>
+      <c r="P16" s="303"/>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="332" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="41" t="s">
+      <c r="B17" s="333"/>
+      <c r="C17" s="333"/>
+      <c r="D17" s="334" t="s">
         <v>0</v>
       </c>
-      <c r="E17" s="209" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="252"/>
-      <c r="L17" s="253"/>
-      <c r="M17" s="254"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
+      <c r="E17" s="335" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="336"/>
+      <c r="G17" s="336"/>
+      <c r="H17" s="336"/>
+      <c r="I17" s="336"/>
+      <c r="J17" s="337"/>
+      <c r="K17" s="338"/>
+      <c r="L17" s="339"/>
+      <c r="M17" s="340"/>
+      <c r="O17" s="303"/>
+      <c r="P17" s="303"/>
     </row>
     <row r="18" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="65"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="402"/>
-      <c r="E18" s="402"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="403"/>
-      <c r="L18" s="403"/>
-      <c r="M18" s="77"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="44"/>
-      <c r="P18" s="44"/>
+      <c r="A18" s="341"/>
+      <c r="B18" s="342"/>
+      <c r="C18" s="342"/>
+      <c r="D18" s="445"/>
+      <c r="E18" s="445"/>
+      <c r="F18" s="342"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="343"/>
+      <c r="J18" s="343"/>
+      <c r="K18" s="446"/>
+      <c r="L18" s="446"/>
+      <c r="M18" s="344"/>
+      <c r="N18" s="303"/>
+      <c r="O18" s="345"/>
+      <c r="P18" s="345"/>
     </row>
     <row r="19" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="99"/>
-      <c r="B19" s="100"/>
-      <c r="C19" s="100"/>
-      <c r="D19" s="413" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="414"/>
-      <c r="F19" s="414"/>
-      <c r="G19" s="414"/>
-      <c r="H19" s="415"/>
-      <c r="I19" s="430" t="s">
-        <v>74</v>
-      </c>
-      <c r="J19" s="430"/>
-      <c r="K19" s="431"/>
-      <c r="L19" s="101"/>
-      <c r="M19" s="102"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="44"/>
-      <c r="P19" s="44"/>
+      <c r="A19" s="346"/>
+      <c r="B19" s="347"/>
+      <c r="C19" s="347"/>
+      <c r="D19" s="456" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="457"/>
+      <c r="F19" s="457"/>
+      <c r="G19" s="457"/>
+      <c r="H19" s="458"/>
+      <c r="I19" s="474" t="s">
+        <v>72</v>
+      </c>
+      <c r="J19" s="474"/>
+      <c r="K19" s="475"/>
+      <c r="L19" s="348"/>
+      <c r="M19" s="349"/>
+      <c r="N19" s="303"/>
+      <c r="O19" s="345"/>
+      <c r="P19" s="345"/>
     </row>
     <row r="20" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="67"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="416"/>
-      <c r="E20" s="417"/>
-      <c r="F20" s="417"/>
-      <c r="G20" s="417"/>
-      <c r="H20" s="418"/>
-      <c r="I20" s="113">
+      <c r="A20" s="350"/>
+      <c r="B20" s="295"/>
+      <c r="C20" s="295"/>
+      <c r="D20" s="459"/>
+      <c r="E20" s="460"/>
+      <c r="F20" s="460"/>
+      <c r="G20" s="460"/>
+      <c r="H20" s="461"/>
+      <c r="I20" s="351">
         <v>1</v>
       </c>
-      <c r="J20" s="92">
+      <c r="J20" s="352">
         <v>2</v>
       </c>
-      <c r="K20" s="92">
+      <c r="K20" s="352">
         <v>3</v>
       </c>
-      <c r="L20" s="114"/>
-      <c r="M20" s="78"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="45"/>
-      <c r="P20" s="46"/>
+      <c r="L20" s="353"/>
+      <c r="M20" s="354"/>
+      <c r="N20" s="303"/>
+      <c r="O20" s="355"/>
+      <c r="P20" s="356"/>
     </row>
     <row r="21" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="67"/>
-      <c r="B21" s="52"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="68" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="69"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="112" t="s">
+      <c r="A21" s="350"/>
+      <c r="B21" s="295"/>
+      <c r="C21" s="295"/>
+      <c r="D21" s="357" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="358"/>
+      <c r="F21" s="359"/>
+      <c r="G21" s="359"/>
+      <c r="H21" s="360" t="s">
         <v>66</v>
       </c>
-      <c r="I21" s="207">
+      <c r="I21" s="77">
         <f>+Datos!G13</f>
         <v>0</v>
       </c>
-      <c r="J21" s="207">
+      <c r="J21" s="77">
         <f>+Datos!H13</f>
         <v>0</v>
       </c>
-      <c r="K21" s="207">
+      <c r="K21" s="77">
         <f>+Datos!I13</f>
         <v>0</v>
       </c>
-      <c r="L21" s="80"/>
-      <c r="M21" s="79"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="30"/>
-      <c r="P21" s="30"/>
+      <c r="L21" s="361"/>
+      <c r="M21" s="362"/>
+      <c r="N21" s="303"/>
+      <c r="O21" s="303"/>
+      <c r="P21" s="303"/>
     </row>
     <row r="22" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="67"/>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="68" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" s="69"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="112" t="s">
+      <c r="A22" s="350"/>
+      <c r="B22" s="295"/>
+      <c r="C22" s="295"/>
+      <c r="D22" s="357" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="358"/>
+      <c r="F22" s="363"/>
+      <c r="G22" s="363"/>
+      <c r="H22" s="360" t="s">
         <v>66</v>
       </c>
-      <c r="I22" s="207">
+      <c r="I22" s="77">
         <f>+Datos!G14</f>
         <v>0</v>
       </c>
-      <c r="J22" s="207">
+      <c r="J22" s="77">
         <f>+Datos!H14</f>
         <v>0</v>
       </c>
-      <c r="K22" s="207">
+      <c r="K22" s="77">
         <f>+Datos!I14</f>
         <v>0</v>
       </c>
-      <c r="L22" s="424"/>
-      <c r="M22" s="423"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="47"/>
-      <c r="P22" s="30"/>
+      <c r="L22" s="468"/>
+      <c r="M22" s="467"/>
+      <c r="N22" s="303"/>
+      <c r="O22" s="364"/>
+      <c r="P22" s="303"/>
     </row>
     <row r="23" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="67"/>
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="68" t="s">
-        <v>70</v>
-      </c>
-      <c r="E23" s="69"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="112" t="s">
+      <c r="A23" s="350"/>
+      <c r="B23" s="295"/>
+      <c r="C23" s="295"/>
+      <c r="D23" s="357" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="358"/>
+      <c r="F23" s="363"/>
+      <c r="G23" s="363"/>
+      <c r="H23" s="360" t="s">
         <v>1</v>
       </c>
-      <c r="I23" s="208" t="e">
+      <c r="I23" s="365" t="e">
         <f>+Datos!G15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J23" s="208" t="e">
+      <c r="J23" s="365" t="e">
         <f>+Datos!H15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K23" s="208" t="e">
+      <c r="K23" s="365" t="e">
         <f>+Datos!I15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L23" s="422"/>
-      <c r="M23" s="423"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="47"/>
+      <c r="L23" s="466"/>
+      <c r="M23" s="467"/>
+      <c r="N23" s="303"/>
+      <c r="O23" s="303"/>
+      <c r="P23" s="364"/>
     </row>
     <row r="24" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="72"/>
-      <c r="B24" s="84"/>
-      <c r="C24" s="84"/>
-      <c r="D24" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="69"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="112" t="s">
+      <c r="A24" s="366"/>
+      <c r="B24" s="367"/>
+      <c r="C24" s="367"/>
+      <c r="D24" s="368" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="358"/>
+      <c r="F24" s="363"/>
+      <c r="G24" s="363"/>
+      <c r="H24" s="360" t="s">
         <v>1</v>
       </c>
-      <c r="I24" s="425" t="e">
+      <c r="I24" s="469" t="e">
         <f>+Datos!G16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J24" s="426"/>
-      <c r="K24" s="427"/>
-      <c r="L24" s="81"/>
-      <c r="M24" s="79"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
-      <c r="P24" s="30"/>
+      <c r="J24" s="470"/>
+      <c r="K24" s="471"/>
+      <c r="L24" s="369"/>
+      <c r="M24" s="362"/>
+      <c r="N24" s="303"/>
+      <c r="O24" s="303"/>
+      <c r="P24" s="303"/>
     </row>
     <row r="25" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="74"/>
-      <c r="B25" s="75"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="76"/>
-      <c r="M25" s="82"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="30"/>
-      <c r="P25" s="30"/>
-      <c r="Q25" s="49"/>
+      <c r="A25" s="370"/>
+      <c r="B25" s="371"/>
+      <c r="C25" s="371"/>
+      <c r="D25" s="371"/>
+      <c r="E25" s="372"/>
+      <c r="F25" s="372"/>
+      <c r="G25" s="372"/>
+      <c r="H25" s="372"/>
+      <c r="I25" s="373"/>
+      <c r="J25" s="373"/>
+      <c r="K25" s="373"/>
+      <c r="L25" s="372"/>
+      <c r="M25" s="374"/>
+      <c r="N25" s="303"/>
+      <c r="O25" s="303"/>
+      <c r="P25" s="303"/>
+      <c r="Q25" s="375"/>
     </row>
     <row r="26" spans="1:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="103"/>
-      <c r="B26" s="104"/>
-      <c r="C26" s="104"/>
-      <c r="D26" s="104"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="105"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="107"/>
-      <c r="J26" s="107"/>
-      <c r="K26" s="107"/>
-      <c r="L26" s="107"/>
-      <c r="M26" s="108"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
+      <c r="A26" s="376"/>
+      <c r="B26" s="377"/>
+      <c r="C26" s="377"/>
+      <c r="D26" s="377"/>
+      <c r="E26" s="378"/>
+      <c r="F26" s="379"/>
+      <c r="G26" s="378"/>
+      <c r="H26" s="378"/>
+      <c r="I26" s="380"/>
+      <c r="J26" s="380"/>
+      <c r="K26" s="380"/>
+      <c r="L26" s="380"/>
+      <c r="M26" s="381"/>
+      <c r="N26" s="303"/>
+      <c r="O26" s="303"/>
+      <c r="P26" s="303"/>
     </row>
     <row r="27" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="115" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="83"/>
-      <c r="C27" s="83"/>
-      <c r="D27" s="84"/>
-      <c r="E27" s="81"/>
-      <c r="M27" s="109"/>
+      <c r="A27" s="382" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="383"/>
+      <c r="C27" s="383"/>
+      <c r="D27" s="367"/>
+      <c r="E27" s="369"/>
+      <c r="M27" s="384"/>
     </row>
     <row r="28" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="116" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28" s="85"/>
-      <c r="C28" s="85"/>
-      <c r="D28" s="84"/>
-      <c r="E28" s="81"/>
-      <c r="F28" s="428" t="s">
-        <v>126</v>
-      </c>
-      <c r="G28" s="429"/>
-      <c r="M28" s="109"/>
+      <c r="A28" s="385" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="386"/>
+      <c r="C28" s="386"/>
+      <c r="D28" s="367"/>
+      <c r="E28" s="369"/>
+      <c r="F28" s="472" t="s">
+        <v>177</v>
+      </c>
+      <c r="G28" s="473"/>
+      <c r="M28" s="384"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="234" t="s">
-        <v>116</v>
-      </c>
-      <c r="B29" s="85"/>
-      <c r="C29" s="85"/>
-      <c r="D29" s="84"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="233"/>
-      <c r="G29" s="233"/>
-      <c r="M29" s="109"/>
+      <c r="A29" s="387" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="386"/>
+      <c r="C29" s="386"/>
+      <c r="D29" s="367"/>
+      <c r="E29" s="369"/>
+      <c r="F29" s="388"/>
+      <c r="G29" s="388"/>
+      <c r="M29" s="384"/>
     </row>
     <row r="30" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="235" t="s">
-        <v>119</v>
-      </c>
-      <c r="B30" s="85"/>
-      <c r="C30" s="85"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="419">
+      <c r="A30" s="389" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="386"/>
+      <c r="C30" s="386"/>
+      <c r="D30" s="367"/>
+      <c r="E30" s="369"/>
+      <c r="F30" s="462">
         <f>+Datos!E25</f>
         <v>0</v>
       </c>
-      <c r="G30" s="420"/>
-      <c r="M30" s="109"/>
+      <c r="G30" s="463"/>
+      <c r="M30" s="384"/>
     </row>
     <row r="31" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="235" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" s="85"/>
-      <c r="C31" s="85"/>
-      <c r="D31" s="84"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="419">
+      <c r="A31" s="389" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="386"/>
+      <c r="C31" s="386"/>
+      <c r="D31" s="367"/>
+      <c r="E31" s="369"/>
+      <c r="F31" s="462">
         <f>+Datos!E26</f>
         <v>0</v>
       </c>
-      <c r="G31" s="420"/>
-      <c r="M31" s="109"/>
+      <c r="G31" s="463"/>
+      <c r="M31" s="384"/>
     </row>
     <row r="32" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="110"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="42"/>
-      <c r="M32" s="111"/>
+      <c r="A32" s="390"/>
+      <c r="B32" s="336"/>
+      <c r="C32" s="336"/>
+      <c r="D32" s="336"/>
+      <c r="E32" s="336"/>
+      <c r="F32" s="336"/>
+      <c r="G32" s="336"/>
+      <c r="H32" s="336"/>
+      <c r="I32" s="336"/>
+      <c r="J32" s="336"/>
+      <c r="K32" s="336"/>
+      <c r="L32" s="336"/>
+      <c r="M32" s="391"/>
     </row>
     <row r="33" spans="1:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="83" t="s">
-        <v>101</v>
-      </c>
-      <c r="B34" s="197"/>
-      <c r="C34" s="197"/>
-      <c r="D34" s="198"/>
-      <c r="E34" s="198"/>
-      <c r="F34" s="198"/>
-      <c r="G34" s="198"/>
-      <c r="H34" s="198"/>
-      <c r="I34" s="198"/>
-      <c r="J34" s="199"/>
-      <c r="K34" s="199"/>
-      <c r="L34" s="199"/>
-      <c r="M34" s="199"/>
+      <c r="A34" s="383" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="392"/>
+      <c r="C34" s="392"/>
+      <c r="D34" s="172"/>
+      <c r="E34" s="172"/>
+      <c r="F34" s="172"/>
+      <c r="G34" s="172"/>
+      <c r="H34" s="172"/>
+      <c r="I34" s="172"/>
+      <c r="J34" s="393"/>
+      <c r="K34" s="393"/>
+      <c r="L34" s="393"/>
+      <c r="M34" s="393"/>
     </row>
     <row r="35" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="95" t="s">
+      <c r="A35" s="476" t="s">
+        <v>171</v>
+      </c>
+      <c r="B35" s="476"/>
+      <c r="C35" s="476"/>
+      <c r="D35" s="476"/>
+      <c r="E35" s="476"/>
+      <c r="F35" s="476"/>
+      <c r="G35" s="476"/>
+      <c r="H35" s="476"/>
+      <c r="I35" s="476"/>
+      <c r="J35" s="476"/>
+      <c r="K35" s="476"/>
+      <c r="L35" s="476"/>
+      <c r="M35" s="476"/>
+    </row>
+    <row r="36" spans="1:16" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="465" t="s">
+        <v>172</v>
+      </c>
+      <c r="B36" s="465"/>
+      <c r="C36" s="465"/>
+      <c r="D36" s="465"/>
+      <c r="E36" s="465"/>
+      <c r="F36" s="465"/>
+      <c r="G36" s="465"/>
+      <c r="H36" s="465"/>
+      <c r="I36" s="465"/>
+      <c r="J36" s="465"/>
+      <c r="K36" s="465"/>
+      <c r="L36" s="465"/>
+      <c r="M36" s="465"/>
+    </row>
+    <row r="37" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="465" t="s">
+        <v>173</v>
+      </c>
+      <c r="B37" s="465"/>
+      <c r="C37" s="465"/>
+      <c r="D37" s="465"/>
+      <c r="E37" s="465"/>
+      <c r="F37" s="465"/>
+      <c r="G37" s="465"/>
+      <c r="H37" s="465"/>
+      <c r="I37" s="465"/>
+      <c r="J37" s="465"/>
+      <c r="K37" s="465"/>
+      <c r="L37" s="465"/>
+      <c r="M37" s="465"/>
+      <c r="N37" s="303"/>
+      <c r="O37" s="303"/>
+      <c r="P37" s="303"/>
+    </row>
+    <row r="38" spans="1:16" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="465" t="s">
+        <v>174</v>
+      </c>
+      <c r="B38" s="465"/>
+      <c r="C38" s="465"/>
+      <c r="D38" s="465"/>
+      <c r="E38" s="465"/>
+      <c r="F38" s="465"/>
+      <c r="G38" s="465"/>
+      <c r="H38" s="465"/>
+      <c r="I38" s="465"/>
+      <c r="J38" s="465"/>
+      <c r="K38" s="465"/>
+      <c r="L38" s="465"/>
+      <c r="M38" s="465"/>
+      <c r="N38" s="303"/>
+      <c r="O38" s="303"/>
+      <c r="P38" s="303"/>
+    </row>
+    <row r="39" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="464" t="s">
+        <v>175</v>
+      </c>
+      <c r="B39" s="464"/>
+      <c r="C39" s="464"/>
+      <c r="D39" s="464"/>
+      <c r="E39" s="464"/>
+      <c r="F39" s="464"/>
+      <c r="G39" s="464"/>
+      <c r="H39" s="464"/>
+      <c r="I39" s="464"/>
+      <c r="J39" s="464"/>
+      <c r="K39" s="464"/>
+      <c r="L39" s="464"/>
+      <c r="M39" s="464"/>
+      <c r="N39" s="303"/>
+      <c r="O39" s="303"/>
+      <c r="P39" s="303"/>
+    </row>
+    <row r="40" spans="1:16" ht="4.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="394"/>
+      <c r="B40" s="394"/>
+      <c r="C40" s="394"/>
+      <c r="N40" s="303"/>
+      <c r="O40" s="303"/>
+      <c r="P40" s="303"/>
+    </row>
+    <row r="41" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="395" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="396"/>
+      <c r="C41" s="397" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" s="397"/>
+      <c r="E41" s="398" t="s">
         <v>102</v>
       </c>
-      <c r="B35" s="197"/>
-      <c r="C35" s="197"/>
-      <c r="D35" s="198"/>
-      <c r="E35" s="198"/>
-      <c r="F35" s="198"/>
-      <c r="G35" s="198"/>
-      <c r="H35" s="198"/>
-      <c r="I35" s="198"/>
-      <c r="J35" s="199"/>
-      <c r="K35" s="199"/>
-      <c r="L35" s="199"/>
-      <c r="M35" s="199"/>
-    </row>
-    <row r="36" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="95" t="s">
-        <v>68</v>
-      </c>
-      <c r="B36" s="95"/>
-      <c r="C36" s="95"/>
-    </row>
-    <row r="37" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="421" t="s">
-        <v>103</v>
-      </c>
-      <c r="B37" s="421"/>
-      <c r="C37" s="421"/>
-      <c r="D37" s="421"/>
-      <c r="E37" s="421"/>
-      <c r="F37" s="421"/>
-      <c r="G37" s="421"/>
-      <c r="H37" s="421"/>
-      <c r="I37" s="421"/>
-      <c r="J37" s="421"/>
-      <c r="K37" s="421"/>
-      <c r="L37" s="421"/>
-      <c r="M37" s="421"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-    </row>
-    <row r="38" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="95" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" s="95"/>
-      <c r="C38" s="95"/>
-      <c r="N38" s="30"/>
-      <c r="O38" s="30"/>
-      <c r="P38" s="30"/>
-    </row>
-    <row r="39" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="421" t="s">
-        <v>122</v>
-      </c>
-      <c r="B39" s="421"/>
-      <c r="C39" s="421"/>
-      <c r="D39" s="421"/>
-      <c r="E39" s="421"/>
-      <c r="F39" s="421"/>
-      <c r="G39" s="421"/>
-      <c r="H39" s="421"/>
-      <c r="I39" s="421"/>
-      <c r="J39" s="421"/>
-      <c r="K39" s="421"/>
-      <c r="L39" s="421"/>
-      <c r="M39" s="421"/>
-      <c r="N39" s="30"/>
-      <c r="O39" s="30"/>
-      <c r="P39" s="30"/>
-    </row>
-    <row r="40" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="95"/>
-      <c r="B40" s="95"/>
-      <c r="C40" s="95"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-    </row>
-    <row r="41" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="200" t="s">
-        <v>104</v>
-      </c>
-      <c r="B41" s="201"/>
-      <c r="C41" s="203" t="s">
-        <v>97</v>
-      </c>
-      <c r="D41" s="203"/>
-      <c r="E41" s="210" t="s">
-        <v>106</v>
-      </c>
-      <c r="F41" s="210"/>
-      <c r="G41" s="210"/>
-      <c r="H41" s="210"/>
-      <c r="I41" s="210"/>
-      <c r="J41" s="210"/>
-      <c r="K41" s="210"/>
-      <c r="L41" s="210"/>
-      <c r="M41" s="210"/>
-      <c r="N41" s="30"/>
-      <c r="O41" s="30"/>
-      <c r="P41" s="30"/>
+      <c r="F41" s="398"/>
+      <c r="G41" s="398"/>
+      <c r="H41" s="398"/>
+      <c r="I41" s="398"/>
+      <c r="J41" s="398"/>
+      <c r="K41" s="398"/>
+      <c r="L41" s="398"/>
+      <c r="M41" s="398"/>
+      <c r="N41" s="303"/>
+      <c r="O41" s="303"/>
+      <c r="P41" s="303"/>
     </row>
     <row r="42" spans="1:16" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="40"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="63"/>
-      <c r="F42" s="63"/>
-      <c r="G42" s="63"/>
-      <c r="H42" s="63"/>
-      <c r="I42" s="63"/>
-      <c r="J42" s="63"/>
-      <c r="K42" s="63"/>
-      <c r="L42" s="202"/>
-      <c r="M42" s="202"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="30"/>
-      <c r="P42" s="30"/>
+      <c r="A42" s="325"/>
+      <c r="B42" s="325"/>
+      <c r="C42" s="325"/>
+      <c r="D42" s="325"/>
+      <c r="E42" s="327"/>
+      <c r="F42" s="327"/>
+      <c r="G42" s="327"/>
+      <c r="H42" s="327"/>
+      <c r="I42" s="327"/>
+      <c r="J42" s="327"/>
+      <c r="K42" s="327"/>
+      <c r="L42" s="399"/>
+      <c r="M42" s="399"/>
+      <c r="N42" s="303"/>
+      <c r="O42" s="303"/>
+      <c r="P42" s="303"/>
     </row>
     <row r="43" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="95"/>
-      <c r="C43" s="95"/>
-      <c r="D43" s="87"/>
-      <c r="E43" s="87"/>
-      <c r="F43" s="87"/>
-      <c r="G43" s="87"/>
-      <c r="H43" s="87"/>
-      <c r="I43" s="87"/>
-      <c r="J43" s="87"/>
-      <c r="K43" s="87"/>
-      <c r="L43" s="86"/>
-      <c r="M43" s="89"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
+      <c r="B43" s="394"/>
+      <c r="C43" s="394"/>
+      <c r="D43" s="400"/>
+      <c r="E43" s="400"/>
+      <c r="F43" s="400"/>
+      <c r="G43" s="400"/>
+      <c r="H43" s="400"/>
+      <c r="I43" s="400"/>
+      <c r="J43" s="400"/>
+      <c r="K43" s="400"/>
+      <c r="L43" s="401"/>
+      <c r="M43" s="402"/>
+      <c r="N43" s="303"/>
+      <c r="O43" s="303"/>
+      <c r="P43" s="303"/>
     </row>
     <row r="44" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="95"/>
-      <c r="C44" s="95"/>
-      <c r="D44" s="87"/>
-      <c r="E44" s="87"/>
-      <c r="F44" s="87"/>
-      <c r="G44" s="87"/>
-      <c r="H44" s="87"/>
-      <c r="I44" s="87"/>
-      <c r="J44" s="87"/>
-      <c r="K44" s="87"/>
-      <c r="L44" s="86"/>
-      <c r="M44" s="86"/>
-      <c r="N44" s="30"/>
-      <c r="O44" s="30"/>
-      <c r="P44" s="30"/>
+      <c r="B44" s="394"/>
+      <c r="C44" s="394"/>
+      <c r="D44" s="400"/>
+      <c r="E44" s="400"/>
+      <c r="F44" s="400"/>
+      <c r="G44" s="400"/>
+      <c r="H44" s="400"/>
+      <c r="I44" s="400"/>
+      <c r="J44" s="400"/>
+      <c r="K44" s="400"/>
+      <c r="L44" s="401"/>
+      <c r="M44" s="401"/>
+      <c r="N44" s="303"/>
+      <c r="O44" s="303"/>
+      <c r="P44" s="303"/>
     </row>
     <row r="45" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="90"/>
-      <c r="C45" s="90"/>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
-      <c r="F45" s="94"/>
-      <c r="G45" s="94"/>
-      <c r="H45" s="94"/>
-      <c r="I45" s="94"/>
-      <c r="J45" s="94"/>
-      <c r="K45" s="94"/>
-      <c r="L45" s="94"/>
-      <c r="M45" s="94"/>
-      <c r="N45" s="30"/>
-      <c r="O45" s="30"/>
-      <c r="P45" s="30"/>
+      <c r="B45" s="403"/>
+      <c r="C45" s="403"/>
+      <c r="D45" s="404"/>
+      <c r="E45" s="404"/>
+      <c r="F45" s="404"/>
+      <c r="G45" s="404"/>
+      <c r="H45" s="404"/>
+      <c r="I45" s="404"/>
+      <c r="J45" s="404"/>
+      <c r="K45" s="404"/>
+      <c r="L45" s="404"/>
+      <c r="M45" s="404"/>
+      <c r="N45" s="303"/>
+      <c r="O45" s="303"/>
+      <c r="P45" s="303"/>
     </row>
     <row r="46" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="90" t="s">
+      <c r="A46" s="403" t="s">
         <v>18</v>
       </c>
-      <c r="B46" s="90"/>
-      <c r="C46" s="90"/>
-      <c r="D46" s="50"/>
-      <c r="E46" s="50"/>
-      <c r="F46" s="50"/>
-      <c r="G46" s="50"/>
-      <c r="H46" s="50"/>
-      <c r="I46" s="50"/>
-      <c r="J46" s="91"/>
-      <c r="K46" s="91"/>
-      <c r="L46" s="91"/>
-      <c r="M46" s="91"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
+      <c r="B46" s="403"/>
+      <c r="C46" s="403"/>
+      <c r="D46" s="293"/>
+      <c r="E46" s="293"/>
+      <c r="F46" s="293"/>
+      <c r="G46" s="293"/>
+      <c r="H46" s="293"/>
+      <c r="I46" s="293"/>
+      <c r="J46" s="405"/>
+      <c r="K46" s="405"/>
+      <c r="L46" s="405"/>
+      <c r="M46" s="405"/>
+      <c r="N46" s="303"/>
+      <c r="O46" s="303"/>
+      <c r="P46" s="303"/>
     </row>
     <row r="47" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="90" t="s">
-        <v>125</v>
-      </c>
-      <c r="B47" s="90"/>
-      <c r="C47" s="90"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="52"/>
-      <c r="H47" s="52"/>
-      <c r="I47" s="52"/>
-      <c r="J47" s="52"/>
-      <c r="K47" s="52"/>
-      <c r="L47" s="52"/>
-      <c r="M47" s="89" t="s">
-        <v>78</v>
-      </c>
-      <c r="N47" s="30"/>
-      <c r="O47" s="30"/>
-      <c r="P47" s="30"/>
+      <c r="A47" s="403" t="s">
+        <v>176</v>
+      </c>
+      <c r="B47" s="403"/>
+      <c r="C47" s="403"/>
+      <c r="D47" s="295"/>
+      <c r="E47" s="295"/>
+      <c r="F47" s="295"/>
+      <c r="G47" s="295"/>
+      <c r="H47" s="295"/>
+      <c r="I47" s="295"/>
+      <c r="J47" s="295"/>
+      <c r="K47" s="295"/>
+      <c r="L47" s="295"/>
+      <c r="M47" s="402" t="s">
+        <v>76</v>
+      </c>
+      <c r="N47" s="303"/>
+      <c r="O47" s="303"/>
+      <c r="P47" s="303"/>
     </row>
     <row r="48" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="52"/>
-      <c r="B48" s="52"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
-      <c r="G48" s="52"/>
-      <c r="H48" s="52"/>
-      <c r="I48" s="52"/>
-      <c r="J48" s="52"/>
-      <c r="K48" s="52"/>
-      <c r="L48" s="52"/>
-      <c r="M48" s="52"/>
-      <c r="N48" s="30"/>
-      <c r="O48" s="30"/>
-      <c r="P48" s="30"/>
+      <c r="A48" s="295"/>
+      <c r="B48" s="295"/>
+      <c r="C48" s="295"/>
+      <c r="D48" s="295"/>
+      <c r="E48" s="295"/>
+      <c r="F48" s="295"/>
+      <c r="G48" s="295"/>
+      <c r="H48" s="295"/>
+      <c r="I48" s="295"/>
+      <c r="J48" s="295"/>
+      <c r="K48" s="295"/>
+      <c r="L48" s="295"/>
+      <c r="M48" s="295"/>
+      <c r="N48" s="303"/>
+      <c r="O48" s="303"/>
+      <c r="P48" s="303"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="52"/>
-      <c r="B49" s="52"/>
-      <c r="C49" s="52"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="52"/>
-      <c r="G49" s="52"/>
-      <c r="H49" s="52"/>
-      <c r="I49" s="52"/>
-      <c r="J49" s="52"/>
-      <c r="K49" s="52"/>
-      <c r="L49" s="52"/>
-      <c r="M49" s="52"/>
+      <c r="A49" s="295"/>
+      <c r="B49" s="295"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="295"/>
+      <c r="G49" s="295"/>
+      <c r="H49" s="295"/>
+      <c r="I49" s="295"/>
+      <c r="J49" s="295"/>
+      <c r="K49" s="295"/>
+      <c r="L49" s="295"/>
+      <c r="M49" s="295"/>
     </row>
     <row r="50" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="52"/>
-      <c r="B50" s="52"/>
-      <c r="C50" s="52"/>
-      <c r="D50" s="86"/>
-      <c r="E50" s="86"/>
-      <c r="F50" s="86"/>
-      <c r="G50" s="86"/>
-      <c r="H50" s="86"/>
-      <c r="I50" s="86"/>
-      <c r="J50" s="52"/>
-      <c r="K50" s="52"/>
-      <c r="L50" s="52"/>
-      <c r="M50" s="52"/>
+      <c r="A50" s="295"/>
+      <c r="B50" s="295"/>
+      <c r="C50" s="295"/>
+      <c r="D50" s="401"/>
+      <c r="E50" s="401"/>
+      <c r="F50" s="401"/>
+      <c r="G50" s="401"/>
+      <c r="H50" s="401"/>
+      <c r="I50" s="401"/>
+      <c r="J50" s="295"/>
+      <c r="K50" s="295"/>
+      <c r="L50" s="295"/>
+      <c r="M50" s="295"/>
     </row>
     <row r="51" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="WauiPDsZIqA6a2EeZ8bupg0bubohlpIXLICRmrMQzlAaPN/8tQ1aq7sfd13dFgca0c7X8Qu7SCDaNzkIHUChYw==" saltValue="xaaWzzb996uuE2w3GeHZ6g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="M9pFxN1vCZ6AssimQy9CSjlzNMYwxkYAI/oYy7gjk/sW0GpV64Tmh24pQaoksmla/+3jmuHbJXffSgoAOfB+NQ==" saltValue="aZQAvccvHvYOr/L9Ag76PA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="E12" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="E7:E9 C7:D8" name="Rango3_3_1_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="C5:E6" name="Rango3_3_1_1_1_1_1_2_1_1"/>
   </protectedRanges>
-  <mergeCells count="21">
+  <mergeCells count="24">
     <mergeCell ref="D19:H20"/>
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
@@ -7430,6 +7629,9 @@
     <mergeCell ref="I24:K24"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A35:M35"/>
+    <mergeCell ref="A36:M36"/>
+    <mergeCell ref="A38:M38"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A3:M3"/>
     <mergeCell ref="D18:E18"/>
@@ -7440,7 +7642,7 @@
     <mergeCell ref="C5:J5"/>
     <mergeCell ref="C6:J6"/>
     <mergeCell ref="C7:J7"/>
-    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="C8:J8"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F28:G28" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -7475,735 +7677,735 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="404" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="405"/>
-      <c r="C1" s="405"/>
-      <c r="D1" s="405"/>
-      <c r="E1" s="405"/>
-      <c r="F1" s="405"/>
-      <c r="G1" s="405"/>
-      <c r="H1" s="405"/>
-      <c r="I1" s="405"/>
-      <c r="J1" s="405"/>
-      <c r="K1" s="406"/>
-      <c r="L1" s="243" t="s">
-        <v>120</v>
-      </c>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
+      <c r="A1" s="477" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="478"/>
+      <c r="C1" s="478"/>
+      <c r="D1" s="478"/>
+      <c r="E1" s="478"/>
+      <c r="F1" s="478"/>
+      <c r="G1" s="478"/>
+      <c r="H1" s="478"/>
+      <c r="I1" s="478"/>
+      <c r="J1" s="478"/>
+      <c r="K1" s="479"/>
+      <c r="L1" s="184" t="s">
+        <v>116</v>
+      </c>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="407" t="s">
-        <v>121</v>
-      </c>
-      <c r="B2" s="408"/>
-      <c r="C2" s="408"/>
-      <c r="D2" s="408"/>
-      <c r="E2" s="408"/>
-      <c r="F2" s="408"/>
-      <c r="G2" s="408"/>
-      <c r="H2" s="408"/>
-      <c r="I2" s="408"/>
-      <c r="J2" s="408"/>
-      <c r="K2" s="409"/>
-      <c r="L2" s="255"/>
-      <c r="M2" s="30">
+      <c r="A2" s="480" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="481"/>
+      <c r="C2" s="481"/>
+      <c r="D2" s="481"/>
+      <c r="E2" s="481"/>
+      <c r="F2" s="481"/>
+      <c r="G2" s="481"/>
+      <c r="H2" s="481"/>
+      <c r="I2" s="481"/>
+      <c r="J2" s="481"/>
+      <c r="K2" s="482"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="29">
         <f>+FORMATO!H11</f>
         <v>0</v>
       </c>
-      <c r="N2" s="30"/>
+      <c r="N2" s="29"/>
     </row>
     <row r="3" spans="1:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
     </row>
     <row r="4" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="99"/>
-      <c r="B4" s="413" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="414"/>
-      <c r="D4" s="414"/>
-      <c r="E4" s="414"/>
-      <c r="F4" s="415"/>
-      <c r="G4" s="430" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="430"/>
-      <c r="I4" s="431"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
+      <c r="A4" s="66"/>
+      <c r="B4" s="489" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="490"/>
+      <c r="D4" s="490"/>
+      <c r="E4" s="490"/>
+      <c r="F4" s="491"/>
+      <c r="G4" s="495" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="495"/>
+      <c r="I4" s="496"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
     </row>
     <row r="5" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="67"/>
-      <c r="B5" s="416"/>
-      <c r="C5" s="417"/>
-      <c r="D5" s="417"/>
-      <c r="E5" s="417"/>
-      <c r="F5" s="418"/>
-      <c r="G5" s="113">
+      <c r="A5" s="43"/>
+      <c r="B5" s="492"/>
+      <c r="C5" s="493"/>
+      <c r="D5" s="493"/>
+      <c r="E5" s="493"/>
+      <c r="F5" s="494"/>
+      <c r="G5" s="71">
         <v>1</v>
       </c>
-      <c r="H5" s="92">
+      <c r="H5" s="64">
         <v>2</v>
       </c>
-      <c r="I5" s="92">
+      <c r="I5" s="64">
         <v>3</v>
       </c>
-      <c r="J5" s="114"/>
-      <c r="K5" s="78"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="46"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="37"/>
     </row>
     <row r="6" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="67"/>
-      <c r="B6" s="117" t="s">
+      <c r="A6" s="43"/>
+      <c r="B6" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="120" t="s">
-        <v>80</v>
-      </c>
-      <c r="G6" s="221">
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="165">
         <v>0.42083333333333334</v>
       </c>
-      <c r="H6" s="221">
+      <c r="H6" s="165">
         <f>+G6+0.0025</f>
         <v>0.42333333333333334</v>
       </c>
-      <c r="I6" s="221">
+      <c r="I6" s="165">
         <f>+G6+0.0045</f>
         <v>0.42533333333333334</v>
       </c>
-      <c r="J6" s="114"/>
-      <c r="K6" s="122">
+      <c r="J6" s="72"/>
+      <c r="K6" s="78">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="46"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="37"/>
     </row>
     <row r="7" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="67"/>
-      <c r="B7" s="117" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="119"/>
-      <c r="F7" s="120" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="212">
+      <c r="A7" s="43"/>
+      <c r="B7" s="73" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="156">
         <f>G6+K7</f>
         <v>0.42777777777777776</v>
       </c>
-      <c r="H7" s="212">
+      <c r="H7" s="156">
         <f>H6+K7</f>
         <v>0.43027777777777776</v>
       </c>
-      <c r="I7" s="212">
+      <c r="I7" s="156">
         <f>I6+K7</f>
         <v>0.43227777777777776</v>
       </c>
-      <c r="J7" s="114"/>
-      <c r="K7" s="123">
+      <c r="J7" s="72"/>
+      <c r="K7" s="79">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="L7" s="30"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="46"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="37"/>
     </row>
     <row r="8" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="67"/>
-      <c r="B8" s="117" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="120" t="s">
-        <v>80</v>
-      </c>
-      <c r="G8" s="213">
+      <c r="A8" s="43"/>
+      <c r="B8" s="73" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="157">
         <f>+FORMATO!H28</f>
         <v>0</v>
       </c>
-      <c r="H8" s="213">
+      <c r="H8" s="157">
         <f>+FORMATO!I28</f>
         <v>0</v>
       </c>
-      <c r="I8" s="213">
+      <c r="I8" s="157">
         <f>+FORMATO!J28</f>
         <v>0</v>
       </c>
-      <c r="J8" s="114"/>
-      <c r="K8" s="124">
+      <c r="J8" s="72"/>
+      <c r="K8" s="80">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="46"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="37"/>
     </row>
     <row r="9" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="67"/>
-      <c r="B9" s="117" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="120" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" s="213">
+      <c r="A9" s="43"/>
+      <c r="B9" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="74"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="76" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="157">
         <f>+FORMATO!H29</f>
         <v>0</v>
       </c>
-      <c r="H9" s="213">
+      <c r="H9" s="157">
         <f>+FORMATO!I29</f>
         <v>0</v>
       </c>
-      <c r="I9" s="213">
+      <c r="I9" s="157">
         <f>+FORMATO!J29</f>
         <v>0</v>
       </c>
-      <c r="J9" s="114"/>
-      <c r="K9" s="78"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="46"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="37"/>
     </row>
     <row r="10" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="67"/>
-      <c r="B10" s="117" t="s">
+      <c r="A10" s="43"/>
+      <c r="B10" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="118"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="120" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="212">
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="156">
         <f>G7+K6</f>
         <v>0.42916666666666664</v>
       </c>
-      <c r="H10" s="212">
+      <c r="H10" s="156">
         <f>H7+K6</f>
         <v>0.43166666666666664</v>
       </c>
-      <c r="I10" s="212">
+      <c r="I10" s="156">
         <f>I7+K6</f>
         <v>0.43366666666666664</v>
       </c>
-      <c r="J10" s="114"/>
-      <c r="K10" s="78"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="46"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="37"/>
     </row>
     <row r="11" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="67"/>
-      <c r="B11" s="117" t="s">
+      <c r="A11" s="43"/>
+      <c r="B11" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="118"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="120" t="s">
-        <v>80</v>
-      </c>
-      <c r="G11" s="212">
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="156">
         <f>IF(G10=0,0,G10+K8)</f>
         <v>0.44305555555555554</v>
       </c>
-      <c r="H11" s="212">
+      <c r="H11" s="156">
         <f>IF(H10=0,0,H10+K8)</f>
         <v>0.44555555555555554</v>
       </c>
-      <c r="I11" s="212">
+      <c r="I11" s="156">
         <f>IF(I10=0,0,I10+K8)</f>
         <v>0.44755555555555554</v>
       </c>
-      <c r="J11" s="114"/>
-      <c r="K11" s="78"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="46"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="37"/>
     </row>
     <row r="12" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="67"/>
-      <c r="B12" s="117" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="118"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="120" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" s="213">
+      <c r="A12" s="43"/>
+      <c r="B12" s="73" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="157">
         <f>+FORMATO!H32</f>
         <v>0</v>
       </c>
-      <c r="H12" s="213">
+      <c r="H12" s="157">
         <f>+FORMATO!I32</f>
         <v>0</v>
       </c>
-      <c r="I12" s="213">
+      <c r="I12" s="157">
         <f>+FORMATO!J32</f>
         <v>0</v>
       </c>
-      <c r="J12" s="114"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="46"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="37"/>
     </row>
     <row r="13" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="67"/>
-      <c r="B13" s="68" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="69"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="112" t="s">
+      <c r="A13" s="43"/>
+      <c r="B13" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="45"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="211">
+      <c r="G13" s="155">
         <f>+FORMATO!H33</f>
         <v>0</v>
       </c>
-      <c r="H13" s="211">
+      <c r="H13" s="155">
         <f>+FORMATO!I33</f>
         <v>0</v>
       </c>
-      <c r="I13" s="211">
+      <c r="I13" s="155">
         <f>+FORMATO!J33</f>
         <v>0</v>
       </c>
-      <c r="J13" s="80"/>
-      <c r="K13" s="79"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="46"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="52"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="37"/>
     </row>
     <row r="14" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="67"/>
-      <c r="B14" s="68" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="69"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="112" t="s">
+      <c r="A14" s="43"/>
+      <c r="B14" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="45"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="211">
+      <c r="G14" s="155">
         <f>+FORMATO!H34</f>
         <v>0</v>
       </c>
-      <c r="H14" s="211">
+      <c r="H14" s="155">
         <f>+FORMATO!I34</f>
         <v>0</v>
       </c>
-      <c r="I14" s="211">
+      <c r="I14" s="155">
         <f>+FORMATO!J34</f>
         <v>0</v>
       </c>
-      <c r="J14" s="424"/>
-      <c r="K14" s="423"/>
-      <c r="M14" s="45"/>
-      <c r="N14" s="46"/>
+      <c r="J14" s="497"/>
+      <c r="K14" s="498"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="37"/>
     </row>
     <row r="15" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="67"/>
-      <c r="B15" s="117" t="s">
+      <c r="A15" s="43"/>
+      <c r="B15" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="220" t="s">
+      <c r="C15" s="74"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="164" t="s">
         <v>1</v>
       </c>
-      <c r="G15" s="213" t="e">
+      <c r="G15" s="157" t="e">
         <f>+ROUNDUP(G14/G13*100,0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H15" s="213" t="e">
+      <c r="H15" s="157" t="e">
         <f t="shared" ref="H15:I15" si="0">+ROUNDUP(H14/H13*100,0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I15" s="213" t="e">
+      <c r="I15" s="157" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J15" s="134"/>
-      <c r="K15" s="133"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="46"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="89"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="37"/>
     </row>
     <row r="16" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="72"/>
-      <c r="B16" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="69"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="112" t="s">
+      <c r="A16" s="48"/>
+      <c r="B16" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="45"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="G16" s="425" t="e">
+      <c r="G16" s="499" t="e">
         <f>ROUNDUP((AVERAGE(G15:I15)),0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H16" s="426"/>
-      <c r="I16" s="427"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="79"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="46"/>
+      <c r="H16" s="500"/>
+      <c r="I16" s="501"/>
+      <c r="J16" s="54"/>
+      <c r="K16" s="52"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="37"/>
     </row>
     <row r="17" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="72"/>
-      <c r="B17" s="84"/>
-      <c r="C17" s="81"/>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="126"/>
-      <c r="J17" s="81"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="45"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="49"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="82"/>
+      <c r="J17" s="54"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="39"/>
     </row>
     <row r="18" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="129"/>
-      <c r="C18" s="214"/>
-      <c r="D18" s="434" t="s">
+      <c r="A18" s="85"/>
+      <c r="C18" s="158"/>
+      <c r="D18" s="485" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" s="486"/>
+      <c r="F18" s="486"/>
+      <c r="G18" s="486"/>
+      <c r="H18" s="486"/>
+      <c r="I18" s="83"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="86"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+    </row>
+    <row r="19" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="85"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="483" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="484"/>
+      <c r="F19" s="483" t="s">
         <v>87</v>
       </c>
-      <c r="E18" s="435"/>
-      <c r="F18" s="435"/>
-      <c r="G18" s="435"/>
-      <c r="H18" s="435"/>
-      <c r="I18" s="127"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="130"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-    </row>
-    <row r="19" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="129"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="432" t="s">
+      <c r="G19" s="484"/>
+      <c r="H19" s="487" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="433"/>
-      <c r="F19" s="432" t="s">
+      <c r="I19" s="83"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="86"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+    </row>
+    <row r="20" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="85"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="159" t="s">
         <v>89</v>
       </c>
-      <c r="G19" s="433"/>
-      <c r="H19" s="436" t="s">
+      <c r="E20" s="159" t="s">
         <v>90</v>
       </c>
-      <c r="I19" s="127"/>
-      <c r="J19" s="86"/>
-      <c r="K19" s="130"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-    </row>
-    <row r="20" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="129"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="215" t="s">
+      <c r="F20" s="159" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" s="159" t="s">
+        <v>90</v>
+      </c>
+      <c r="H20" s="488"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+    </row>
+    <row r="21" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="85"/>
+      <c r="C21" s="84" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="215" t="s">
-        <v>92</v>
-      </c>
-      <c r="F20" s="215" t="s">
-        <v>91</v>
-      </c>
-      <c r="G20" s="215" t="s">
-        <v>92</v>
-      </c>
-      <c r="H20" s="437"/>
-      <c r="I20" s="127"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="130"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-    </row>
-    <row r="21" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="129"/>
-      <c r="C21" s="128" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" s="216" t="e">
+      <c r="D21" s="160" t="e">
         <f>+STDEV(MAX(G15:I15),MIN(G15:I15))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E21" s="217" t="e">
+      <c r="E21" s="161" t="e">
         <f>D21*2.8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F21" s="218">
+      <c r="F21" s="162">
         <v>2.9</v>
       </c>
-      <c r="G21" s="218">
+      <c r="G21" s="162">
         <v>8.1999999999999993</v>
       </c>
-      <c r="H21" s="219" t="e">
+      <c r="H21" s="163" t="e">
         <f>IF(E21&lt;G21, "cumple", "no cumple")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I21" s="87"/>
-      <c r="J21" s="86"/>
-      <c r="K21" s="130"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="86"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
     </row>
     <row r="22" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="129"/>
-      <c r="B22" s="87"/>
-      <c r="C22" s="128" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="216" t="e">
+      <c r="A22" s="85"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="84" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" s="160" t="e">
         <f>+STDEV(MAX(G15:I15),MIN(G15:I15))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E22" s="217" t="e">
+      <c r="E22" s="161" t="e">
         <f>D22*2.8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F22" s="125">
+      <c r="F22" s="81">
         <v>1.5</v>
       </c>
-      <c r="G22" s="218">
+      <c r="G22" s="162">
         <v>4.2</v>
       </c>
-      <c r="H22" s="219" t="e">
+      <c r="H22" s="163" t="e">
         <f>IF(E22&lt;G22, "cumple", "no cumple")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I22" s="87"/>
-      <c r="J22" s="86"/>
-      <c r="K22" s="130"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="86"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
     </row>
     <row r="23" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="129"/>
-      <c r="B23" s="87"/>
-      <c r="C23" s="236"/>
-      <c r="D23" s="237"/>
-      <c r="E23" s="238"/>
-      <c r="F23" s="239"/>
-      <c r="G23" s="240"/>
-      <c r="H23" s="241"/>
-      <c r="I23" s="87"/>
-      <c r="J23" s="86"/>
-      <c r="K23" s="130"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
+      <c r="A23" s="85"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="177"/>
+      <c r="D23" s="178"/>
+      <c r="E23" s="179"/>
+      <c r="F23" s="180"/>
+      <c r="G23" s="181"/>
+      <c r="H23" s="182"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="86"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
     </row>
     <row r="24" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="129"/>
-      <c r="B24" s="87"/>
-      <c r="C24" s="83" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" s="237"/>
-      <c r="E24" s="238"/>
-      <c r="F24" s="239"/>
-      <c r="G24" s="240"/>
-      <c r="H24" s="241"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="86"/>
-      <c r="K24" s="130"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
+      <c r="A24" s="85"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="178"/>
+      <c r="E24" s="179"/>
+      <c r="F24" s="180"/>
+      <c r="G24" s="181"/>
+      <c r="H24" s="182"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
     </row>
     <row r="25" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="129"/>
-      <c r="B25" s="87"/>
-      <c r="C25" s="85" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" s="237"/>
-      <c r="E25" s="264">
+      <c r="A25" s="85"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" s="178"/>
+      <c r="E25" s="194">
         <v>0</v>
       </c>
-      <c r="F25" s="239"/>
-      <c r="G25" s="240"/>
-      <c r="H25" s="241"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="130"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
+      <c r="F25" s="180"/>
+      <c r="G25" s="181"/>
+      <c r="H25" s="182"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="86"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
     </row>
     <row r="26" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="129"/>
-      <c r="B26" s="87"/>
-      <c r="C26" s="85" t="s">
-        <v>117</v>
-      </c>
-      <c r="D26" s="237"/>
-      <c r="E26" s="242">
+      <c r="A26" s="85"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="178"/>
+      <c r="E26" s="183">
         <v>0</v>
       </c>
-      <c r="F26" s="239"/>
-      <c r="G26" s="240"/>
-      <c r="H26" s="241"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="130"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
+      <c r="F26" s="180"/>
+      <c r="G26" s="181"/>
+      <c r="H26" s="182"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="58"/>
+      <c r="K26" s="86"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
     </row>
     <row r="27" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="110"/>
-      <c r="B27" s="131"/>
-      <c r="C27" s="131"/>
-      <c r="D27" s="131"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="131"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="131"/>
-      <c r="I27" s="131"/>
-      <c r="J27" s="131"/>
-      <c r="K27" s="132"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="30"/>
+      <c r="A27" s="69"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="87"/>
+      <c r="H27" s="87"/>
+      <c r="I27" s="87"/>
+      <c r="J27" s="87"/>
+      <c r="K27" s="88"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
     </row>
     <row r="28" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="88"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="93"/>
-      <c r="N28" s="30"/>
+      <c r="A28" s="60"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="29"/>
     </row>
     <row r="29" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="90"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="91"/>
-      <c r="I29" s="91"/>
-      <c r="J29" s="91"/>
-      <c r="K29" s="91"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
+      <c r="A29" s="62"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="63"/>
+      <c r="K29" s="63"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
     </row>
     <row r="30" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="90"/>
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="89"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="30"/>
+      <c r="A30" s="62"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
     </row>
     <row r="31" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="52"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="52"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
+      <c r="A32" s="41"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
     </row>
     <row r="33" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="52"/>
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="86"/>
-      <c r="G33" s="86"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="52"/>
-      <c r="K33" s="52"/>
+      <c r="A33" s="41"/>
+      <c r="B33" s="58"/>
+      <c r="C33" s="58"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="58"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
     </row>
     <row r="34" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -8258,73 +8460,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="452"/>
-      <c r="B1" s="452"/>
-      <c r="C1" s="443" t="s">
+      <c r="A1" s="516"/>
+      <c r="B1" s="516"/>
+      <c r="C1" s="507" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="444"/>
-      <c r="E1" s="444"/>
-      <c r="F1" s="444"/>
-      <c r="G1" s="444"/>
-      <c r="H1" s="445"/>
-      <c r="I1" s="153" t="s">
+      <c r="D1" s="508"/>
+      <c r="E1" s="508"/>
+      <c r="F1" s="508"/>
+      <c r="G1" s="508"/>
+      <c r="H1" s="509"/>
+      <c r="I1" s="109" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="153" t="s">
+      <c r="J1" s="109" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="452"/>
-      <c r="B2" s="452"/>
-      <c r="C2" s="446"/>
-      <c r="D2" s="447"/>
-      <c r="E2" s="447"/>
-      <c r="F2" s="447"/>
-      <c r="G2" s="447"/>
-      <c r="H2" s="448"/>
-      <c r="I2" s="153" t="s">
+      <c r="A2" s="516"/>
+      <c r="B2" s="516"/>
+      <c r="C2" s="510"/>
+      <c r="D2" s="511"/>
+      <c r="E2" s="511"/>
+      <c r="F2" s="511"/>
+      <c r="G2" s="511"/>
+      <c r="H2" s="512"/>
+      <c r="I2" s="109" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="154">
+      <c r="J2" s="110">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="452"/>
-      <c r="B3" s="452"/>
-      <c r="C3" s="446"/>
-      <c r="D3" s="447"/>
-      <c r="E3" s="447"/>
-      <c r="F3" s="447"/>
-      <c r="G3" s="447"/>
-      <c r="H3" s="448"/>
-      <c r="I3" s="153" t="s">
+      <c r="A3" s="516"/>
+      <c r="B3" s="516"/>
+      <c r="C3" s="510"/>
+      <c r="D3" s="511"/>
+      <c r="E3" s="511"/>
+      <c r="F3" s="511"/>
+      <c r="G3" s="511"/>
+      <c r="H3" s="512"/>
+      <c r="I3" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="360">
+      <c r="J3" s="289">
         <v>46146</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="452"/>
-      <c r="B4" s="452"/>
-      <c r="C4" s="449"/>
-      <c r="D4" s="450"/>
-      <c r="E4" s="450"/>
-      <c r="F4" s="450"/>
-      <c r="G4" s="450"/>
-      <c r="H4" s="451"/>
-      <c r="I4" s="153" t="s">
+      <c r="A4" s="516"/>
+      <c r="B4" s="516"/>
+      <c r="C4" s="513"/>
+      <c r="D4" s="514"/>
+      <c r="E4" s="514"/>
+      <c r="F4" s="514"/>
+      <c r="G4" s="514"/>
+      <c r="H4" s="515"/>
+      <c r="I4" s="109" t="s">
         <v>52</v>
       </c>
-      <c r="J4" s="153" t="s">
+      <c r="J4" s="109" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="226" t="s">
+      <c r="A6" s="170" t="s">
         <v>50</v>
       </c>
       <c r="B6" s="19" t="s">
@@ -8340,11 +8542,11 @@
       <c r="J6" s="16"/>
     </row>
     <row r="7" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="226" t="s">
+      <c r="A7" s="170" t="s">
         <v>49</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -8356,11 +8558,11 @@
       <c r="J7" s="16"/>
     </row>
     <row r="8" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="226" t="s">
+      <c r="A8" s="170" t="s">
         <v>48</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
@@ -8372,8 +8574,8 @@
       <c r="J8" s="16"/>
     </row>
     <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="227" t="s">
-        <v>176</v>
+      <c r="A9" s="171" t="s">
+        <v>161</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>67</v>
@@ -8388,952 +8590,952 @@
       <c r="J9" s="16"/>
     </row>
     <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="228" t="s">
-        <v>183</v>
-      </c>
-      <c r="B11" s="223"/>
-      <c r="C11" s="223"/>
-      <c r="D11" s="223"/>
-      <c r="E11" s="223"/>
-      <c r="F11" s="223"/>
-      <c r="G11" s="223"/>
-      <c r="H11" s="223"/>
-      <c r="I11" s="223"/>
+      <c r="A11" s="172" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="167"/>
+      <c r="C11" s="167"/>
+      <c r="D11" s="167"/>
+      <c r="E11" s="167"/>
+      <c r="F11" s="167"/>
+      <c r="G11" s="167"/>
+      <c r="H11" s="167"/>
+      <c r="I11" s="167"/>
     </row>
     <row r="12" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="223"/>
-      <c r="B12" s="223"/>
-      <c r="C12" s="223"/>
-      <c r="D12" s="223"/>
-      <c r="E12" s="223"/>
-      <c r="F12" s="223"/>
-      <c r="G12" s="223"/>
-      <c r="H12" s="223"/>
-      <c r="I12" s="223"/>
+      <c r="A12" s="167"/>
+      <c r="B12" s="167"/>
+      <c r="C12" s="167"/>
+      <c r="D12" s="167"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="167"/>
+      <c r="G12" s="167"/>
+      <c r="H12" s="167"/>
+      <c r="I12" s="167"/>
     </row>
     <row r="13" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="229" t="s">
+      <c r="A13" s="173" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="167"/>
+      <c r="C13" s="167"/>
+      <c r="D13" s="167"/>
+      <c r="E13" s="167"/>
+      <c r="F13" s="173" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" s="167"/>
+      <c r="H13" s="167"/>
+      <c r="I13" s="167"/>
+    </row>
+    <row r="14" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="167"/>
+      <c r="B14" s="167"/>
+      <c r="C14" s="167"/>
+      <c r="D14" s="167"/>
+      <c r="E14" s="167"/>
+      <c r="F14" s="167"/>
+      <c r="G14" s="167"/>
+      <c r="H14" s="167"/>
+      <c r="I14" s="167"/>
+    </row>
+    <row r="15" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="176" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="223"/>
-      <c r="C13" s="223"/>
-      <c r="D13" s="223"/>
-      <c r="E13" s="223"/>
-      <c r="F13" s="229" t="s">
+      <c r="B15" s="167"/>
+      <c r="C15" s="167"/>
+      <c r="D15" s="167"/>
+      <c r="E15" s="167"/>
+      <c r="F15" s="174"/>
+      <c r="G15" s="167"/>
+      <c r="H15" s="167"/>
+      <c r="I15" s="167"/>
+    </row>
+    <row r="16" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="176" t="s">
         <v>109</v>
       </c>
-      <c r="G13" s="223"/>
-      <c r="H13" s="223"/>
-      <c r="I13" s="223"/>
-    </row>
-    <row r="14" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="223"/>
-      <c r="B14" s="223"/>
-      <c r="C14" s="223"/>
-      <c r="D14" s="223"/>
-      <c r="E14" s="223"/>
-      <c r="F14" s="223"/>
-      <c r="G14" s="223"/>
-      <c r="H14" s="223"/>
-      <c r="I14" s="223"/>
-    </row>
-    <row r="15" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="232" t="s">
-        <v>112</v>
-      </c>
-      <c r="B15" s="223"/>
-      <c r="C15" s="223"/>
-      <c r="D15" s="223"/>
-      <c r="E15" s="223"/>
-      <c r="F15" s="230"/>
-      <c r="G15" s="223"/>
-      <c r="H15" s="223"/>
-      <c r="I15" s="223"/>
-    </row>
-    <row r="16" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="232" t="s">
-        <v>113</v>
-      </c>
-      <c r="B16" s="223"/>
-      <c r="C16" s="223"/>
-      <c r="D16" s="223"/>
-      <c r="E16" s="223"/>
-      <c r="F16" s="223"/>
-      <c r="G16" s="223"/>
-      <c r="H16" s="223"/>
-      <c r="I16" s="223"/>
+      <c r="B16" s="167"/>
+      <c r="C16" s="167"/>
+      <c r="D16" s="167"/>
+      <c r="E16" s="167"/>
+      <c r="F16" s="167"/>
+      <c r="G16" s="167"/>
+      <c r="H16" s="167"/>
+      <c r="I16" s="167"/>
     </row>
     <row r="17" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="232" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17" s="223"/>
-      <c r="C17" s="223"/>
-      <c r="D17" s="223"/>
-      <c r="E17" s="223"/>
-      <c r="F17" s="223"/>
-      <c r="G17" s="223"/>
-      <c r="H17" s="223"/>
-      <c r="I17" s="223"/>
+      <c r="A17" s="176" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="167"/>
+      <c r="C17" s="167"/>
+      <c r="D17" s="167"/>
+      <c r="E17" s="167"/>
+      <c r="F17" s="167"/>
+      <c r="G17" s="167"/>
+      <c r="H17" s="167"/>
+      <c r="I17" s="167"/>
     </row>
     <row r="18" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="223"/>
-      <c r="B18" s="223"/>
-      <c r="C18" s="223"/>
-      <c r="D18" s="231"/>
-      <c r="E18" s="223"/>
-      <c r="F18" s="223"/>
-      <c r="G18" s="223"/>
-      <c r="H18" s="223"/>
-      <c r="I18" s="223"/>
+      <c r="A18" s="167"/>
+      <c r="B18" s="167"/>
+      <c r="C18" s="167"/>
+      <c r="D18" s="175"/>
+      <c r="E18" s="167"/>
+      <c r="F18" s="167"/>
+      <c r="G18" s="167"/>
+      <c r="H18" s="167"/>
+      <c r="I18" s="167"/>
     </row>
     <row r="19" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="229" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="223"/>
-      <c r="C19" s="223"/>
-      <c r="D19" s="223"/>
-      <c r="E19" s="223"/>
-      <c r="F19" s="223"/>
-      <c r="G19" s="223"/>
-      <c r="H19" s="223"/>
-      <c r="I19" s="223"/>
+      <c r="A19" s="173" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="167"/>
+      <c r="C19" s="167"/>
+      <c r="D19" s="167"/>
+      <c r="E19" s="167"/>
+      <c r="F19" s="167"/>
+      <c r="G19" s="167"/>
+      <c r="H19" s="167"/>
+      <c r="I19" s="167"/>
     </row>
     <row r="20" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="223"/>
-      <c r="B20" s="223"/>
-      <c r="C20" s="223"/>
-      <c r="D20" s="223"/>
-      <c r="E20" s="223"/>
-      <c r="F20" s="230"/>
-      <c r="G20" s="223"/>
-      <c r="H20" s="223"/>
-      <c r="I20" s="223"/>
+      <c r="A20" s="167"/>
+      <c r="B20" s="167"/>
+      <c r="C20" s="167"/>
+      <c r="D20" s="167"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="174"/>
+      <c r="G20" s="167"/>
+      <c r="H20" s="167"/>
+      <c r="I20" s="167"/>
     </row>
     <row r="21" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="232" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" s="223"/>
-      <c r="C21" s="223"/>
-      <c r="D21" s="223"/>
-      <c r="E21" s="223"/>
-      <c r="F21" s="223"/>
-      <c r="G21" s="223"/>
-      <c r="H21" s="223"/>
-      <c r="I21" s="223"/>
+      <c r="A21" s="176" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="167"/>
+      <c r="C21" s="167"/>
+      <c r="D21" s="167"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="167"/>
+      <c r="G21" s="167"/>
+      <c r="H21" s="167"/>
+      <c r="I21" s="167"/>
     </row>
     <row r="22" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="223"/>
-      <c r="B22" s="223"/>
-      <c r="C22" s="223"/>
-      <c r="D22" s="223"/>
-      <c r="E22" s="223"/>
-      <c r="F22" s="223"/>
-      <c r="G22" s="223"/>
-      <c r="H22" s="223"/>
-      <c r="I22" s="223"/>
+      <c r="A22" s="167"/>
+      <c r="B22" s="167"/>
+      <c r="C22" s="167"/>
+      <c r="D22" s="167"/>
+      <c r="E22" s="167"/>
+      <c r="F22" s="167"/>
+      <c r="G22" s="167"/>
+      <c r="H22" s="167"/>
+      <c r="I22" s="167"/>
     </row>
     <row r="23" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="228" t="s">
-        <v>111</v>
-      </c>
-      <c r="B23" s="223"/>
-      <c r="C23" s="223"/>
-      <c r="D23" s="223"/>
-      <c r="E23" s="223"/>
-      <c r="F23" s="223"/>
-      <c r="G23" s="223"/>
-      <c r="H23" s="223"/>
-      <c r="I23" s="223"/>
+      <c r="A23" s="172" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="167"/>
+      <c r="C23" s="167"/>
+      <c r="D23" s="167"/>
+      <c r="E23" s="167"/>
+      <c r="F23" s="167"/>
+      <c r="G23" s="167"/>
+      <c r="H23" s="167"/>
+      <c r="I23" s="167"/>
     </row>
     <row r="24" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="223"/>
-      <c r="B24" s="223"/>
-      <c r="C24" s="223"/>
-      <c r="D24" s="223"/>
-      <c r="E24" s="223"/>
-      <c r="F24" s="223"/>
-      <c r="G24" s="223"/>
-      <c r="H24" s="223"/>
-      <c r="I24" s="223"/>
+      <c r="A24" s="167"/>
+      <c r="B24" s="167"/>
+      <c r="C24" s="167"/>
+      <c r="D24" s="167"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="167"/>
+      <c r="G24" s="167"/>
+      <c r="H24" s="167"/>
+      <c r="I24" s="167"/>
     </row>
     <row r="25" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:24" ht="54.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F29" s="135"/>
-      <c r="H29" s="135"/>
-      <c r="I29" s="135"/>
-      <c r="L29" s="222"/>
-      <c r="M29" s="223"/>
-      <c r="N29" s="223"/>
-      <c r="O29" s="223"/>
-      <c r="P29" s="223"/>
-      <c r="Q29" s="223"/>
-      <c r="R29" s="223"/>
-      <c r="S29" s="223"/>
-      <c r="T29" s="223"/>
-      <c r="U29" s="223"/>
+      <c r="F29" s="91"/>
+      <c r="H29" s="91"/>
+      <c r="I29" s="91"/>
+      <c r="L29" s="166"/>
+      <c r="M29" s="167"/>
+      <c r="N29" s="167"/>
+      <c r="O29" s="167"/>
+      <c r="P29" s="167"/>
+      <c r="Q29" s="167"/>
+      <c r="R29" s="167"/>
+      <c r="S29" s="167"/>
+      <c r="T29" s="167"/>
+      <c r="U29" s="167"/>
     </row>
     <row r="30" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L30" s="222"/>
-      <c r="M30" s="223"/>
-      <c r="N30" s="223"/>
-      <c r="O30" s="223"/>
-      <c r="P30" s="223"/>
-      <c r="Q30" s="223"/>
-      <c r="R30" s="223"/>
-      <c r="S30" s="223"/>
-      <c r="T30" s="223"/>
-      <c r="U30" s="223"/>
+      <c r="L30" s="166"/>
+      <c r="M30" s="167"/>
+      <c r="N30" s="167"/>
+      <c r="O30" s="167"/>
+      <c r="P30" s="167"/>
+      <c r="Q30" s="167"/>
+      <c r="R30" s="167"/>
+      <c r="S30" s="167"/>
+      <c r="T30" s="167"/>
+      <c r="U30" s="167"/>
     </row>
     <row r="31" spans="1:24" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L31" s="224"/>
-      <c r="M31" s="224"/>
-      <c r="N31" s="224"/>
-      <c r="O31" s="224"/>
-      <c r="P31" s="224"/>
-      <c r="Q31" s="224"/>
-      <c r="R31" s="224"/>
-      <c r="S31" s="224"/>
-      <c r="T31" s="224"/>
-      <c r="U31" s="224"/>
+      <c r="L31" s="168"/>
+      <c r="M31" s="168"/>
+      <c r="N31" s="168"/>
+      <c r="O31" s="168"/>
+      <c r="P31" s="168"/>
+      <c r="Q31" s="168"/>
+      <c r="R31" s="168"/>
+      <c r="S31" s="168"/>
+      <c r="T31" s="168"/>
+      <c r="U31" s="168"/>
     </row>
     <row r="32" spans="1:24" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="183" t="s">
+      <c r="A32" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="184" t="s">
+      <c r="B32" s="140" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="185" t="s">
+      <c r="C32" s="141" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="185" t="s">
+      <c r="D32" s="141" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="185" t="s">
+      <c r="E32" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="185" t="s">
+      <c r="F32" s="141" t="s">
         <v>42</v>
       </c>
-      <c r="G32" s="185" t="s">
+      <c r="G32" s="141" t="s">
         <v>41</v>
       </c>
-      <c r="H32" s="186" t="s">
+      <c r="H32" s="142" t="s">
         <v>40</v>
       </c>
-      <c r="I32" s="183" t="s">
+      <c r="I32" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="J32" s="184" t="s">
+      <c r="J32" s="140" t="s">
         <v>46</v>
       </c>
-      <c r="K32" s="185" t="s">
+      <c r="K32" s="141" t="s">
         <v>45</v>
       </c>
-      <c r="L32" s="185" t="s">
+      <c r="L32" s="141" t="s">
         <v>44</v>
       </c>
-      <c r="M32" s="185" t="s">
+      <c r="M32" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="N32" s="185" t="s">
+      <c r="N32" s="141" t="s">
         <v>42</v>
       </c>
-      <c r="O32" s="185" t="s">
+      <c r="O32" s="141" t="s">
         <v>41</v>
       </c>
-      <c r="P32" s="186" t="s">
+      <c r="P32" s="142" t="s">
         <v>40</v>
       </c>
-      <c r="Q32" s="183" t="s">
+      <c r="Q32" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="R32" s="184" t="s">
+      <c r="R32" s="140" t="s">
         <v>46</v>
       </c>
-      <c r="S32" s="185" t="s">
+      <c r="S32" s="141" t="s">
         <v>45</v>
       </c>
-      <c r="T32" s="185" t="s">
+      <c r="T32" s="141" t="s">
         <v>44</v>
       </c>
-      <c r="U32" s="185" t="s">
+      <c r="U32" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="V32" s="185" t="s">
+      <c r="V32" s="141" t="s">
         <v>42</v>
       </c>
-      <c r="W32" s="185" t="s">
+      <c r="W32" s="141" t="s">
         <v>41</v>
       </c>
-      <c r="X32" s="186" t="s">
+      <c r="X32" s="142" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="170" t="s">
+      <c r="A33" s="126" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="171" t="e">
+      <c r="B33" s="127" t="e">
         <f>ROUNDUP((B36/B34*100),0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C33" s="156"/>
-      <c r="D33" s="156"/>
-      <c r="E33" s="156"/>
-      <c r="F33" s="156"/>
-      <c r="G33" s="156"/>
-      <c r="H33" s="172"/>
-      <c r="I33" s="170" t="s">
+      <c r="C33" s="112"/>
+      <c r="D33" s="112"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="112"/>
+      <c r="H33" s="128"/>
+      <c r="I33" s="126" t="s">
         <v>59</v>
       </c>
-      <c r="J33" s="171" t="e">
+      <c r="J33" s="127" t="e">
         <f>ROUNDUP((J36/J34*100),0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K33" s="156"/>
-      <c r="L33" s="156"/>
-      <c r="M33" s="156"/>
-      <c r="N33" s="156"/>
-      <c r="O33" s="156"/>
-      <c r="P33" s="172"/>
-      <c r="Q33" s="170" t="s">
+      <c r="K33" s="112"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="128"/>
+      <c r="Q33" s="126" t="s">
         <v>59</v>
       </c>
-      <c r="R33" s="171" t="e">
+      <c r="R33" s="127" t="e">
         <f>ROUNDUP((R36/R34*100),0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S33" s="156"/>
-      <c r="T33" s="156"/>
-      <c r="U33" s="156"/>
-      <c r="V33" s="156"/>
-      <c r="W33" s="156"/>
-      <c r="X33" s="172"/>
+      <c r="S33" s="112"/>
+      <c r="T33" s="112"/>
+      <c r="U33" s="112"/>
+      <c r="V33" s="112"/>
+      <c r="W33" s="112"/>
+      <c r="X33" s="128"/>
     </row>
     <row r="34" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="166" t="s">
+      <c r="A34" s="122" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="205">
+      <c r="B34" s="153">
         <f>+Balanza!C4</f>
         <v>0</v>
       </c>
-      <c r="C34" s="161"/>
-      <c r="D34" s="162" t="s">
+      <c r="C34" s="117"/>
+      <c r="D34" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="E34" s="163" t="s">
+      <c r="E34" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="F34" s="164">
+      <c r="F34" s="120">
         <f>+F35</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="G34" s="165" t="e">
+      <c r="G34" s="121" t="e">
         <f>(B36/POWER(B34,2))*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H34" s="167" t="e">
+      <c r="H34" s="123" t="e">
         <f>ABS(G34*F34)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I34" s="166" t="s">
+      <c r="I34" s="122" t="s">
         <v>64</v>
       </c>
-      <c r="J34" s="205">
+      <c r="J34" s="153">
         <f>+Balanza!D4</f>
         <v>0</v>
       </c>
-      <c r="K34" s="161"/>
-      <c r="L34" s="162" t="s">
+      <c r="K34" s="117"/>
+      <c r="L34" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="M34" s="163" t="s">
+      <c r="M34" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="N34" s="164">
+      <c r="N34" s="120">
         <f>+N35</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="O34" s="165" t="e">
+      <c r="O34" s="121" t="e">
         <f>(J36/POWER(J34,2))*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P34" s="167" t="e">
+      <c r="P34" s="123" t="e">
         <f>ABS(O34*N34)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q34" s="166" t="s">
+      <c r="Q34" s="122" t="s">
         <v>64</v>
       </c>
-      <c r="R34" s="205">
+      <c r="R34" s="153">
         <f>+Balanza!E4</f>
         <v>0</v>
       </c>
-      <c r="S34" s="161"/>
-      <c r="T34" s="162" t="s">
+      <c r="S34" s="117"/>
+      <c r="T34" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="U34" s="163" t="s">
+      <c r="U34" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="V34" s="164">
+      <c r="V34" s="120">
         <f>+V35</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="W34" s="165" t="e">
+      <c r="W34" s="121" t="e">
         <f>(R36/POWER(R34,2))*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X34" s="167" t="e">
+      <c r="X34" s="123" t="e">
         <f>ABS(W34*V34)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="35" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="168" t="s">
+      <c r="A35" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="206"/>
-      <c r="C35" s="140">
+      <c r="B35" s="154"/>
+      <c r="C35" s="96">
         <f>Balanza!$C$18</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="D35" s="141" t="s">
+      <c r="D35" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="E35" s="160" t="s">
+      <c r="E35" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="F35" s="142">
+      <c r="F35" s="98">
         <f>+C35</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="G35" s="157" t="s">
+      <c r="G35" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="H35" s="169" t="s">
+      <c r="H35" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="I35" s="168" t="s">
+      <c r="I35" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="J35" s="206"/>
-      <c r="K35" s="140">
+      <c r="J35" s="154"/>
+      <c r="K35" s="96">
         <f>Balanza!$C$18</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="L35" s="141" t="s">
+      <c r="L35" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="M35" s="160" t="s">
+      <c r="M35" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="N35" s="142">
+      <c r="N35" s="98">
         <f>+K35</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="O35" s="157" t="s">
+      <c r="O35" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="P35" s="169" t="s">
+      <c r="P35" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="Q35" s="168" t="s">
+      <c r="Q35" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="R35" s="206"/>
-      <c r="S35" s="140">
+      <c r="R35" s="154"/>
+      <c r="S35" s="96">
         <f>Balanza!$C$18</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="T35" s="141" t="s">
+      <c r="T35" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="U35" s="160" t="s">
+      <c r="U35" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="V35" s="142">
+      <c r="V35" s="98">
         <f>+S35</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="W35" s="157" t="s">
+      <c r="W35" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="X35" s="169" t="s">
+      <c r="X35" s="125" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="166" t="s">
+      <c r="A36" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="205">
+      <c r="B36" s="153">
         <f>+Balanza!C5</f>
         <v>0</v>
       </c>
-      <c r="C36" s="161"/>
-      <c r="D36" s="162" t="s">
+      <c r="C36" s="117"/>
+      <c r="D36" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="E36" s="163" t="s">
+      <c r="E36" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="F36" s="164">
+      <c r="F36" s="120">
         <f>+F37</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="G36" s="165" t="e">
+      <c r="G36" s="121" t="e">
         <f>(1/B34)*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H36" s="167" t="e">
+      <c r="H36" s="123" t="e">
         <f>ABS(G36*F36)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I36" s="166" t="s">
+      <c r="I36" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="J36" s="205">
+      <c r="J36" s="153">
         <f>+Balanza!D5</f>
         <v>0</v>
       </c>
-      <c r="K36" s="161"/>
-      <c r="L36" s="162" t="s">
+      <c r="K36" s="117"/>
+      <c r="L36" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="M36" s="163" t="s">
+      <c r="M36" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="N36" s="164">
+      <c r="N36" s="120">
         <f>+N37</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="O36" s="165" t="e">
+      <c r="O36" s="121" t="e">
         <f>(1/J34)*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P36" s="167" t="e">
+      <c r="P36" s="123" t="e">
         <f>ABS(O36*N36)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q36" s="166" t="s">
+      <c r="Q36" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="R36" s="205">
+      <c r="R36" s="153">
         <f>+Balanza!E5</f>
         <v>0</v>
       </c>
-      <c r="S36" s="161"/>
-      <c r="T36" s="162" t="s">
+      <c r="S36" s="117"/>
+      <c r="T36" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="U36" s="163" t="s">
+      <c r="U36" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="V36" s="164">
+      <c r="V36" s="120">
         <f>+V37</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="W36" s="165" t="e">
+      <c r="W36" s="121" t="e">
         <f>(1/R34)*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X36" s="167" t="e">
+      <c r="X36" s="123" t="e">
         <f>ABS(W36*V36)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="37" spans="1:24" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="168" t="s">
+      <c r="A37" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="B37" s="159"/>
-      <c r="C37" s="140">
+      <c r="B37" s="115"/>
+      <c r="C37" s="96">
         <f>Balanza!$C$18</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="D37" s="141" t="s">
+      <c r="D37" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="E37" s="160" t="s">
+      <c r="E37" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="F37" s="142">
+      <c r="F37" s="98">
         <f>+C37</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="G37" s="157" t="s">
+      <c r="G37" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="H37" s="169" t="s">
+      <c r="H37" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="I37" s="168" t="s">
+      <c r="I37" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="J37" s="159"/>
-      <c r="K37" s="140">
+      <c r="J37" s="115"/>
+      <c r="K37" s="96">
         <f>Balanza!$C$18</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="L37" s="141" t="s">
+      <c r="L37" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="M37" s="160" t="s">
+      <c r="M37" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="N37" s="142">
+      <c r="N37" s="98">
         <f>+K37</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="O37" s="157" t="s">
+      <c r="O37" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="P37" s="169" t="s">
+      <c r="P37" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="Q37" s="168" t="s">
+      <c r="Q37" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="R37" s="159"/>
-      <c r="S37" s="140">
+      <c r="R37" s="115"/>
+      <c r="S37" s="96">
         <f>Balanza!$C$18</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="T37" s="141" t="s">
+      <c r="T37" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="U37" s="160" t="s">
+      <c r="U37" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="V37" s="142">
+      <c r="V37" s="98">
         <f>+S37</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="W37" s="157" t="s">
+      <c r="W37" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="X37" s="169" t="s">
+      <c r="X37" s="125" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="143" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="173" t="s">
+    <row r="38" spans="1:24" s="99" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="174">
+      <c r="B38" s="130">
         <f>+Precision!B8</f>
         <v>0.9775252199076786</v>
       </c>
-      <c r="C38" s="175"/>
-      <c r="D38" s="176" t="s">
+      <c r="C38" s="131"/>
+      <c r="D38" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="E38" s="177" t="s">
+      <c r="E38" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="F38" s="178">
+      <c r="F38" s="134">
         <f>+B38</f>
         <v>0.9775252199076786</v>
       </c>
-      <c r="G38" s="179">
+      <c r="G38" s="135">
         <v>1</v>
       </c>
-      <c r="H38" s="180">
+      <c r="H38" s="136">
         <f>ABS(G38*F38)</f>
         <v>0.9775252199076786</v>
       </c>
-      <c r="I38" s="173" t="s">
+      <c r="I38" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="J38" s="174">
+      <c r="J38" s="130">
         <f>+B38</f>
         <v>0.9775252199076786</v>
       </c>
-      <c r="K38" s="175"/>
-      <c r="L38" s="176" t="s">
+      <c r="K38" s="131"/>
+      <c r="L38" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="M38" s="177" t="s">
+      <c r="M38" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="N38" s="178">
+      <c r="N38" s="134">
         <f>+J38</f>
         <v>0.9775252199076786</v>
       </c>
-      <c r="O38" s="179">
+      <c r="O38" s="135">
         <v>1</v>
       </c>
-      <c r="P38" s="180">
+      <c r="P38" s="136">
         <f>ABS(O38*N38)</f>
         <v>0.9775252199076786</v>
       </c>
-      <c r="Q38" s="173" t="s">
+      <c r="Q38" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="R38" s="174">
+      <c r="R38" s="130">
         <f>+J38</f>
         <v>0.9775252199076786</v>
       </c>
-      <c r="S38" s="175"/>
-      <c r="T38" s="176" t="s">
+      <c r="S38" s="131"/>
+      <c r="T38" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="U38" s="177" t="s">
+      <c r="U38" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="V38" s="178">
+      <c r="V38" s="134">
         <f>+R38</f>
         <v>0.9775252199076786</v>
       </c>
-      <c r="W38" s="179">
+      <c r="W38" s="135">
         <v>1</v>
       </c>
-      <c r="X38" s="180">
+      <c r="X38" s="136">
         <f>ABS(W38*V38)</f>
         <v>0.9775252199076786</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="143" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="187" t="s">
+    <row r="39" spans="1:24" s="99" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="143" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="188"/>
-      <c r="C39" s="188"/>
-      <c r="D39" s="189"/>
-      <c r="E39" s="188"/>
-      <c r="F39" s="190"/>
-      <c r="G39" s="188"/>
-      <c r="H39" s="191" t="e">
+      <c r="B39" s="144"/>
+      <c r="C39" s="144"/>
+      <c r="D39" s="145"/>
+      <c r="E39" s="144"/>
+      <c r="F39" s="146"/>
+      <c r="G39" s="144"/>
+      <c r="H39" s="147" t="e">
         <f>SQRT((H34*H34)+(H38*H38)+(H36*H36))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I39" s="187"/>
-      <c r="J39" s="188"/>
-      <c r="K39" s="188"/>
-      <c r="L39" s="189"/>
-      <c r="M39" s="188"/>
-      <c r="N39" s="190"/>
-      <c r="O39" s="188"/>
-      <c r="P39" s="191" t="e">
+      <c r="I39" s="143"/>
+      <c r="J39" s="144"/>
+      <c r="K39" s="144"/>
+      <c r="L39" s="145"/>
+      <c r="M39" s="144"/>
+      <c r="N39" s="146"/>
+      <c r="O39" s="144"/>
+      <c r="P39" s="147" t="e">
         <f>SQRT((P34*P34)+(P38*P38)+(P36*P36))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q39" s="187"/>
-      <c r="R39" s="188"/>
-      <c r="S39" s="188"/>
-      <c r="T39" s="189"/>
-      <c r="U39" s="188"/>
-      <c r="V39" s="190"/>
-      <c r="W39" s="188"/>
-      <c r="X39" s="191" t="e">
+      <c r="Q39" s="143"/>
+      <c r="R39" s="144"/>
+      <c r="S39" s="144"/>
+      <c r="T39" s="145"/>
+      <c r="U39" s="144"/>
+      <c r="V39" s="146"/>
+      <c r="W39" s="144"/>
+      <c r="X39" s="147" t="e">
         <f>SQRT((X34*X34)+(X38*X38)+(X36*X36))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="143" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="187" t="s">
+    <row r="40" spans="1:24" s="99" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="143" t="s">
         <v>63</v>
       </c>
-      <c r="B40" s="188"/>
-      <c r="C40" s="188"/>
-      <c r="D40" s="189"/>
-      <c r="E40" s="188"/>
-      <c r="F40" s="190"/>
-      <c r="G40" s="188"/>
-      <c r="H40" s="225" t="e">
+      <c r="B40" s="144"/>
+      <c r="C40" s="144"/>
+      <c r="D40" s="145"/>
+      <c r="E40" s="144"/>
+      <c r="F40" s="146"/>
+      <c r="G40" s="144"/>
+      <c r="H40" s="169" t="e">
         <f>ROUNDUP((MAX(H39:X39)*2),0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="181"/>
-      <c r="J40" s="181"/>
-      <c r="K40" s="181"/>
-      <c r="L40" s="182"/>
-      <c r="M40" s="181"/>
-      <c r="O40" s="181"/>
-      <c r="P40" s="181"/>
-      <c r="Q40" s="181"/>
-      <c r="R40" s="181"/>
-      <c r="S40" s="181"/>
-      <c r="T40" s="182"/>
-      <c r="U40" s="181"/>
-      <c r="W40" s="181"/>
-      <c r="X40" s="181"/>
+      <c r="I40" s="137"/>
+      <c r="J40" s="137"/>
+      <c r="K40" s="137"/>
+      <c r="L40" s="138"/>
+      <c r="M40" s="137"/>
+      <c r="O40" s="137"/>
+      <c r="P40" s="137"/>
+      <c r="Q40" s="137"/>
+      <c r="R40" s="137"/>
+      <c r="S40" s="137"/>
+      <c r="T40" s="138"/>
+      <c r="U40" s="137"/>
+      <c r="W40" s="137"/>
+      <c r="X40" s="137"/>
     </row>
     <row r="41" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="155"/>
-      <c r="D41" s="155"/>
-      <c r="E41" s="155"/>
-      <c r="F41" s="155"/>
-      <c r="G41" s="155"/>
-      <c r="H41" s="155"/>
-      <c r="I41" s="155"/>
-      <c r="J41" s="155"/>
+      <c r="A41" s="111"/>
+      <c r="D41" s="111"/>
+      <c r="E41" s="111"/>
+      <c r="F41" s="111"/>
+      <c r="G41" s="111"/>
+      <c r="H41" s="111"/>
+      <c r="I41" s="111"/>
+      <c r="J41" s="111"/>
     </row>
     <row r="42" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="155"/>
+      <c r="A42" s="111"/>
       <c r="B42" s="14"/>
       <c r="C42" s="13"/>
-      <c r="D42" s="158"/>
-      <c r="E42" s="155"/>
-      <c r="F42" s="155"/>
-      <c r="G42" s="155"/>
-      <c r="H42" s="155"/>
-      <c r="I42" s="155"/>
-      <c r="J42" s="155"/>
+      <c r="D42" s="114"/>
+      <c r="E42" s="111"/>
+      <c r="F42" s="111"/>
+      <c r="G42" s="111"/>
+      <c r="H42" s="111"/>
+      <c r="I42" s="111"/>
+      <c r="J42" s="111"/>
     </row>
     <row r="43" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="192"/>
-      <c r="B43" s="196" t="str">
+      <c r="A43" s="148"/>
+      <c r="B43" s="152" t="str">
         <f>A34</f>
         <v>Lecturas de Medida - Arcilla</v>
       </c>
-      <c r="C43" s="193" t="e">
+      <c r="C43" s="149" t="e">
         <f>H34</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D43" s="194" t="e">
+      <c r="D43" s="150" t="e">
         <f>+C43/$C$46</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E43" s="155"/>
-      <c r="F43" s="155"/>
-      <c r="G43" s="155"/>
-      <c r="H43" s="155"/>
-      <c r="I43" s="155"/>
-      <c r="J43" s="155"/>
+      <c r="E43" s="111"/>
+      <c r="F43" s="111"/>
+      <c r="G43" s="111"/>
+      <c r="H43" s="111"/>
+      <c r="I43" s="111"/>
+      <c r="J43" s="111"/>
     </row>
     <row r="44" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="192"/>
-      <c r="B44" s="196" t="str">
+      <c r="A44" s="148"/>
+      <c r="B44" s="152" t="str">
         <f>A36</f>
         <v>Lecturas de Medida . Arena</v>
       </c>
-      <c r="C44" s="193" t="e">
+      <c r="C44" s="149" t="e">
         <f>H36</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D44" s="194" t="e">
+      <c r="D44" s="150" t="e">
         <f>+C44/$C$46</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E44" s="155"/>
-      <c r="F44" s="155"/>
-      <c r="G44" s="155"/>
-      <c r="H44" s="155"/>
-      <c r="I44" s="155"/>
-      <c r="J44" s="155"/>
+      <c r="E44" s="111"/>
+      <c r="F44" s="111"/>
+      <c r="G44" s="111"/>
+      <c r="H44" s="111"/>
+      <c r="I44" s="111"/>
+      <c r="J44" s="111"/>
     </row>
     <row r="45" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="196" t="str">
+      <c r="B45" s="152" t="str">
         <f>A38</f>
         <v>factor de presición</v>
       </c>
-      <c r="C45" s="193">
+      <c r="C45" s="149">
         <f>H38</f>
         <v>0.9775252199076786</v>
       </c>
-      <c r="D45" s="194" t="e">
+      <c r="D45" s="150" t="e">
         <f>+C45/$C$46</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E45" s="155"/>
-      <c r="F45" s="155"/>
-      <c r="G45" s="155"/>
-      <c r="H45" s="155"/>
-      <c r="I45" s="155"/>
-      <c r="J45" s="155"/>
+      <c r="E45" s="111"/>
+      <c r="F45" s="111"/>
+      <c r="G45" s="111"/>
+      <c r="H45" s="111"/>
+      <c r="I45" s="111"/>
+      <c r="J45" s="111"/>
     </row>
     <row r="46" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="441"/>
-      <c r="B46" s="442"/>
-      <c r="C46" s="195" t="e">
+      <c r="A46" s="505"/>
+      <c r="B46" s="506"/>
+      <c r="C46" s="151" t="e">
         <f>SUM(C43:C45)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D46" s="192"/>
-      <c r="E46" s="155"/>
-      <c r="F46" s="155"/>
-      <c r="G46" s="155"/>
-      <c r="H46" s="155"/>
-      <c r="I46" s="155"/>
-      <c r="J46" s="155"/>
+      <c r="D46" s="148"/>
+      <c r="E46" s="111"/>
+      <c r="F46" s="111"/>
+      <c r="G46" s="111"/>
+      <c r="H46" s="111"/>
+      <c r="I46" s="111"/>
+      <c r="J46" s="111"/>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A47" s="155"/>
-      <c r="B47" s="155"/>
-      <c r="C47" s="155"/>
-      <c r="D47" s="155"/>
-      <c r="E47" s="155"/>
-      <c r="F47" s="155"/>
-      <c r="G47" s="155"/>
-      <c r="H47" s="155"/>
-      <c r="I47" s="155"/>
-      <c r="J47" s="155"/>
+      <c r="A47" s="111"/>
+      <c r="B47" s="111"/>
+      <c r="C47" s="111"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="111"/>
+      <c r="F47" s="111"/>
+      <c r="G47" s="111"/>
+      <c r="H47" s="111"/>
+      <c r="I47" s="111"/>
+      <c r="J47" s="111"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="361" t="s">
-        <v>177</v>
-      </c>
-      <c r="B55" s="453" t="s">
-        <v>178</v>
-      </c>
-      <c r="C55" s="454"/>
-      <c r="D55" s="362"/>
-      <c r="E55" s="455" t="s">
-        <v>179</v>
-      </c>
-      <c r="F55" s="455"/>
-      <c r="G55" s="456" t="s">
-        <v>180</v>
-      </c>
-      <c r="H55" s="457"/>
+      <c r="A55" s="290" t="s">
+        <v>162</v>
+      </c>
+      <c r="B55" s="517" t="s">
+        <v>163</v>
+      </c>
+      <c r="C55" s="518"/>
+      <c r="D55" s="291"/>
+      <c r="E55" s="519" t="s">
+        <v>164</v>
+      </c>
+      <c r="F55" s="519"/>
+      <c r="G55" s="520" t="s">
+        <v>165</v>
+      </c>
+      <c r="H55" s="521"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="223"/>
-      <c r="B56" s="223"/>
-      <c r="C56" s="223"/>
-      <c r="D56" s="223"/>
-      <c r="E56" s="223"/>
-      <c r="F56" s="223"/>
-      <c r="G56" s="223"/>
-      <c r="H56" s="223"/>
+      <c r="A56" s="167"/>
+      <c r="B56" s="167"/>
+      <c r="C56" s="167"/>
+      <c r="D56" s="167"/>
+      <c r="E56" s="167"/>
+      <c r="F56" s="167"/>
+      <c r="G56" s="167"/>
+      <c r="H56" s="167"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="358" t="s">
-        <v>181</v>
-      </c>
-      <c r="B57" s="438">
+      <c r="A57" s="287" t="s">
+        <v>166</v>
+      </c>
+      <c r="B57" s="502">
         <v>44869</v>
       </c>
-      <c r="C57" s="439"/>
-      <c r="D57" s="223"/>
-      <c r="E57" s="440" t="s">
-        <v>182</v>
-      </c>
-      <c r="F57" s="440"/>
-      <c r="G57" s="438">
+      <c r="C57" s="503"/>
+      <c r="D57" s="167"/>
+      <c r="E57" s="504" t="s">
+        <v>167</v>
+      </c>
+      <c r="F57" s="504"/>
+      <c r="G57" s="502">
         <v>44870</v>
       </c>
-      <c r="H57" s="439"/>
+      <c r="H57" s="503"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="223"/>
-      <c r="B58" s="223"/>
-      <c r="C58" s="223"/>
-      <c r="D58" s="223"/>
-      <c r="E58" s="223"/>
-      <c r="F58" s="223"/>
-      <c r="G58" s="223"/>
-      <c r="H58" s="223"/>
+      <c r="A58" s="167"/>
+      <c r="B58" s="167"/>
+      <c r="C58" s="167"/>
+      <c r="D58" s="167"/>
+      <c r="E58" s="167"/>
+      <c r="F58" s="167"/>
+      <c r="G58" s="167"/>
+      <c r="H58" s="167"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="vsvUK0TloRFKoo8uRc/wzbXs05dwbRMXzNWsarKAjr7XVAo4s0iftn6aIkvgTJjHeS7c0oLFhaZaqoMtHd6kRg==" saltValue="m8e4RTM6eBEkVjZOCJAAeQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
@@ -9373,53 +9575,53 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="144" t="s">
-        <v>99</v>
+      <c r="A2" s="100" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="145" t="str">
+      <c r="B4" s="101" t="str">
         <f>+Datos!B13</f>
         <v>Lectura de la arcilla</v>
       </c>
-      <c r="C4" s="121">
+      <c r="C4" s="77">
         <f>+Datos!G13</f>
         <v>0</v>
       </c>
-      <c r="D4" s="121">
+      <c r="D4" s="77">
         <f>+Datos!H13</f>
         <v>0</v>
       </c>
-      <c r="E4" s="121">
+      <c r="E4" s="77">
         <f>+Datos!I13</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="145" t="str">
+      <c r="B5" s="101" t="str">
         <f>+Datos!B14</f>
         <v>Lectura de la arena</v>
       </c>
-      <c r="C5" s="121">
+      <c r="C5" s="77">
         <f>+Datos!G14</f>
         <v>0</v>
       </c>
-      <c r="D5" s="121">
+      <c r="D5" s="77">
         <f>+Datos!H14</f>
         <v>0</v>
       </c>
-      <c r="E5" s="121">
+      <c r="E5" s="77">
         <f>+Datos!I14</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="459" t="s">
+      <c r="A9" s="523" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="460"/>
-      <c r="C9" s="460"/>
-      <c r="D9" s="460"/>
+      <c r="B9" s="524"/>
+      <c r="C9" s="524"/>
+      <c r="D9" s="524"/>
       <c r="E9" s="26"/>
       <c r="F9" s="26"/>
     </row>
@@ -9428,97 +9630,97 @@
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
       <c r="E10" s="27"/>
-      <c r="F10" s="138"/>
+      <c r="F10" s="94"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="146" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="135"/>
-      <c r="F11" s="138"/>
-      <c r="G11" s="138"/>
+      <c r="A11" s="102" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="91"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="147"/>
-      <c r="B12" s="135"/>
-      <c r="F12" s="138"/>
-      <c r="G12" s="138"/>
+      <c r="A12" s="103"/>
+      <c r="B12" s="91"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="148">
+      <c r="A13" s="104">
         <v>1</v>
       </c>
-      <c r="B13" s="149">
+      <c r="B13" s="105">
         <v>381.5</v>
       </c>
-      <c r="C13" s="149">
+      <c r="C13" s="105">
         <v>381.6</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="148">
+      <c r="A14" s="104">
         <v>2</v>
       </c>
-      <c r="B14" s="149">
+      <c r="B14" s="105">
         <v>381.4</v>
       </c>
-      <c r="C14" s="149">
+      <c r="C14" s="105">
         <v>381.5</v>
       </c>
-      <c r="E14" s="150"/>
-      <c r="F14" s="139"/>
-      <c r="G14" s="139"/>
+      <c r="E14" s="106"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="148">
+      <c r="A15" s="104">
         <v>3</v>
       </c>
-      <c r="B15" s="149">
+      <c r="B15" s="105">
         <v>381.5</v>
       </c>
-      <c r="C15" s="149">
+      <c r="C15" s="105">
         <v>381.6</v>
       </c>
-      <c r="E15" s="150"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
+      <c r="E15" s="106"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="148">
+      <c r="A16" s="104">
         <v>4</v>
       </c>
-      <c r="B16" s="149"/>
-      <c r="C16" s="149"/>
-      <c r="F16" s="139"/>
-      <c r="G16" s="139"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="105"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="461" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" s="461"/>
-      <c r="C17" s="151">
+      <c r="A17" s="525" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="525"/>
+      <c r="C17" s="107">
         <f>COUNT(B13:C16)</f>
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="461"/>
-      <c r="B18" s="461"/>
-      <c r="C18" s="152">
+      <c r="A18" s="525"/>
+      <c r="B18" s="525"/>
+      <c r="C18" s="108">
         <f>STDEV(B13:C16)/SQRT($C$17)</f>
         <v>3.0731814857649951E-2</v>
       </c>
-      <c r="F18" s="139"/>
-      <c r="G18" s="139"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="20"/>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
       <c r="D19" s="21"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="139"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B20" s="21"/>
@@ -9526,49 +9728,49 @@
       <c r="D20" s="21"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="440"/>
+      <c r="A21" s="504"/>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
       <c r="D21" s="21"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="440"/>
+      <c r="A22" s="504"/>
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="440"/>
+      <c r="A23" s="504"/>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
       <c r="D23" s="21"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="440"/>
+      <c r="A24" s="504"/>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
       <c r="D24" s="21"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="458"/>
+      <c r="A25" s="522"/>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
       <c r="D25" s="21"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="458"/>
+      <c r="A26" s="522"/>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
       <c r="D26" s="21"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="458"/>
+      <c r="A27" s="522"/>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
       <c r="D27" s="21"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="458"/>
+      <c r="A28" s="522"/>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
       <c r="D28" s="21"/>
@@ -9601,68 +9803,68 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" style="256" customWidth="1"/>
-    <col min="2" max="16384" width="11.5546875" style="256"/>
+    <col min="1" max="1" width="39.6640625" style="186" customWidth="1"/>
+    <col min="2" max="16384" width="11.5546875" style="186"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="257"/>
+      <c r="A2" s="187"/>
     </row>
     <row r="3" spans="1:11" ht="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="363" t="s">
-        <v>184</v>
+      <c r="A4" s="292" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="137"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="462"/>
-      <c r="J5" s="462"/>
-      <c r="K5" s="462"/>
+      <c r="A5" s="93"/>
+      <c r="H5" s="188"/>
+      <c r="I5" s="526"/>
+      <c r="J5" s="526"/>
+      <c r="K5" s="526"/>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="137" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="259">
+      <c r="A6" s="93" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="189">
         <v>46072</v>
       </c>
-      <c r="H6" s="260"/>
-      <c r="I6" s="261"/>
-      <c r="J6" s="261"/>
-      <c r="K6" s="261"/>
+      <c r="H6" s="190"/>
+      <c r="I6" s="191"/>
+      <c r="J6" s="191"/>
+      <c r="K6" s="191"/>
     </row>
     <row r="7" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="137"/>
-      <c r="B7" s="262"/>
-      <c r="H7" s="359"/>
-      <c r="I7" s="261"/>
-      <c r="J7" s="261"/>
-      <c r="K7" s="261"/>
+      <c r="A7" s="93"/>
+      <c r="B7" s="192"/>
+      <c r="H7" s="288"/>
+      <c r="I7" s="191"/>
+      <c r="J7" s="191"/>
+      <c r="K7" s="191"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="263" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8" s="463">
+      <c r="A8" s="193" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="527">
         <v>0.9775252199076786</v>
       </c>
-      <c r="C8" s="463"/>
-      <c r="D8" s="463"/>
-      <c r="E8" s="136"/>
+      <c r="C8" s="527"/>
+      <c r="D8" s="527"/>
+      <c r="E8" s="92"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="263" t="s">
-        <v>128</v>
-      </c>
-      <c r="B9" s="463">
+      <c r="A9" s="193" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="527">
         <v>0.99721835344343934</v>
       </c>
-      <c r="C9" s="463"/>
-      <c r="D9" s="463"/>
-      <c r="E9" s="136"/>
+      <c r="C9" s="527"/>
+      <c r="D9" s="527"/>
+      <c r="E9" s="92"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="OkxfL873VX6h1beCqCeo5CWhdmsYtZeJUGnlHk/nS/YqLv8qapXvv0MN5g4ZSfjBe+iGRl3N+MfhQIBFE0aJRg==" saltValue="VW/tFKgcT4KIVyQcdgKucQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -9692,10 +9894,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="464" t="s">
+      <c r="A2" s="528" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="464"/>
+      <c r="B2" s="528"/>
       <c r="C2" s="5" t="s">
         <v>12</v>
       </c>

--- a/app/templates/informes/EquiArena/Template_EquiArena.xlsx
+++ b/app/templates/informes/EquiArena/Template_EquiArena.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\6.1 JUNIO INICIA 15-06-25\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\EquiArena\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5491EC75-F5BF-4341-9F34-FB11E3A17F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6764323F-BEE7-442D-9469-7EE07C96DA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="556" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -842,10 +842,10 @@
     <t>- De conformidad con lo dispuesto por el artículo 1321 del Código Civil, queda establecido que en ningún caso la responsabilidad de GEOFAL S.A.C. será mayor al valor del servicio prestado.</t>
   </si>
   <si>
-    <t>Versión: 08 (15-06-2026)</t>
-  </si>
-  <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Versión: 08 (11-06-2026)</t>
   </si>
 </sst>
 </file>
@@ -2945,6 +2945,115 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="44" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="44" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="44" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="1"/>
@@ -2981,114 +3090,72 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="44" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="44" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="44" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3131,73 +3198,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3596,7 +3596,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="119672192"/>
@@ -3633,7 +3633,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="119670272"/>
@@ -3672,7 +3672,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4648,7 +4648,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -4707,7 +4707,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -4826,7 +4826,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -4877,7 +4877,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -4961,7 +4961,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -5773,36 +5773,36 @@
       <c r="N6" s="283"/>
     </row>
     <row r="7" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="409" t="s">
+      <c r="A7" s="437" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="409"/>
-      <c r="C7" s="409"/>
-      <c r="D7" s="409"/>
-      <c r="E7" s="409"/>
-      <c r="F7" s="409"/>
-      <c r="G7" s="409"/>
-      <c r="H7" s="409"/>
-      <c r="I7" s="409"/>
-      <c r="J7" s="409"/>
+      <c r="B7" s="437"/>
+      <c r="C7" s="437"/>
+      <c r="D7" s="437"/>
+      <c r="E7" s="437"/>
+      <c r="F7" s="437"/>
+      <c r="G7" s="437"/>
+      <c r="H7" s="437"/>
+      <c r="I7" s="437"/>
+      <c r="J7" s="437"/>
       <c r="M7" s="279" t="s">
         <v>119</v>
       </c>
       <c r="N7" s="283"/>
     </row>
     <row r="8" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="410" t="s">
+      <c r="A8" s="438" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="410"/>
-      <c r="C8" s="410"/>
-      <c r="D8" s="410"/>
-      <c r="E8" s="410"/>
-      <c r="F8" s="410"/>
-      <c r="G8" s="410"/>
-      <c r="H8" s="410"/>
-      <c r="I8" s="410"/>
-      <c r="J8" s="410"/>
+      <c r="B8" s="438"/>
+      <c r="C8" s="438"/>
+      <c r="D8" s="438"/>
+      <c r="E8" s="438"/>
+      <c r="F8" s="438"/>
+      <c r="G8" s="438"/>
+      <c r="H8" s="438"/>
+      <c r="I8" s="438"/>
+      <c r="J8" s="438"/>
       <c r="M8" s="279" t="s">
         <v>157</v>
       </c>
@@ -5825,22 +5825,22 @@
       <c r="N9" s="283"/>
     </row>
     <row r="10" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="411" t="s">
+      <c r="B10" s="439" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="411"/>
-      <c r="D10" s="411" t="s">
+      <c r="C10" s="439"/>
+      <c r="D10" s="439" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="411"/>
-      <c r="F10" s="411" t="s">
+      <c r="E10" s="439"/>
+      <c r="F10" s="439" t="s">
         <v>125</v>
       </c>
-      <c r="G10" s="411"/>
-      <c r="H10" s="411" t="s">
+      <c r="G10" s="439"/>
+      <c r="H10" s="439" t="s">
         <v>126</v>
       </c>
-      <c r="I10" s="411"/>
+      <c r="I10" s="439"/>
       <c r="J10" s="209"/>
       <c r="K10" s="210"/>
       <c r="L10" s="210"/>
@@ -5849,14 +5849,14 @@
     </row>
     <row r="11" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="211"/>
-      <c r="B11" s="411"/>
-      <c r="C11" s="411"/>
-      <c r="D11" s="411"/>
-      <c r="E11" s="411"/>
-      <c r="F11" s="411"/>
-      <c r="G11" s="411"/>
-      <c r="H11" s="411"/>
-      <c r="I11" s="411"/>
+      <c r="B11" s="439"/>
+      <c r="C11" s="439"/>
+      <c r="D11" s="439"/>
+      <c r="E11" s="439"/>
+      <c r="F11" s="439"/>
+      <c r="G11" s="439"/>
+      <c r="H11" s="439"/>
+      <c r="I11" s="439"/>
       <c r="J11" s="212"/>
       <c r="K11" s="210"/>
       <c r="L11" s="210"/>
@@ -5884,18 +5884,18 @@
       <c r="N12" s="284"/>
     </row>
     <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="412" t="s">
+      <c r="A13" s="440" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="413"/>
-      <c r="C13" s="413"/>
-      <c r="D13" s="413"/>
-      <c r="E13" s="413"/>
-      <c r="F13" s="413"/>
-      <c r="G13" s="413"/>
-      <c r="H13" s="413"/>
-      <c r="I13" s="413"/>
-      <c r="J13" s="414"/>
+      <c r="B13" s="441"/>
+      <c r="C13" s="441"/>
+      <c r="D13" s="441"/>
+      <c r="E13" s="441"/>
+      <c r="F13" s="441"/>
+      <c r="G13" s="441"/>
+      <c r="H13" s="441"/>
+      <c r="I13" s="441"/>
+      <c r="J13" s="442"/>
       <c r="K13" s="210"/>
       <c r="L13" s="210"/>
       <c r="M13" s="279" t="s">
@@ -5904,18 +5904,18 @@
       <c r="N13" s="284"/>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="406" t="s">
+      <c r="A14" s="434" t="s">
         <v>117</v>
       </c>
-      <c r="B14" s="407"/>
-      <c r="C14" s="407"/>
-      <c r="D14" s="407"/>
-      <c r="E14" s="407"/>
-      <c r="F14" s="407"/>
-      <c r="G14" s="407"/>
-      <c r="H14" s="407"/>
-      <c r="I14" s="407"/>
-      <c r="J14" s="408"/>
+      <c r="B14" s="435"/>
+      <c r="C14" s="435"/>
+      <c r="D14" s="435"/>
+      <c r="E14" s="435"/>
+      <c r="F14" s="435"/>
+      <c r="G14" s="435"/>
+      <c r="H14" s="435"/>
+      <c r="I14" s="435"/>
+      <c r="J14" s="436"/>
       <c r="K14" s="210"/>
       <c r="L14" s="210"/>
       <c r="M14" s="282"/>
@@ -5941,21 +5941,21 @@
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="221"/>
-      <c r="B16" s="415" t="s">
+      <c r="B16" s="426" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="415"/>
-      <c r="D16" s="415"/>
+      <c r="C16" s="426"/>
+      <c r="D16" s="426"/>
       <c r="E16" s="222"/>
-      <c r="F16" s="416" t="s">
+      <c r="F16" s="427" t="s">
         <v>127</v>
       </c>
-      <c r="G16" s="416"/>
+      <c r="G16" s="427"/>
       <c r="H16" s="222"/>
-      <c r="I16" s="417" t="s">
+      <c r="I16" s="428" t="s">
         <v>128</v>
       </c>
-      <c r="J16" s="420"/>
+      <c r="J16" s="431"/>
       <c r="K16" s="210"/>
       <c r="L16" s="210"/>
       <c r="M16" s="279" t="s">
@@ -5965,15 +5965,15 @@
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="221"/>
-      <c r="B17" s="423"/>
-      <c r="C17" s="424"/>
-      <c r="D17" s="425"/>
+      <c r="B17" s="417"/>
+      <c r="C17" s="418"/>
+      <c r="D17" s="419"/>
       <c r="E17" s="223"/>
-      <c r="F17" s="423"/>
-      <c r="G17" s="425"/>
+      <c r="F17" s="417"/>
+      <c r="G17" s="419"/>
       <c r="H17" s="222"/>
-      <c r="I17" s="418"/>
-      <c r="J17" s="421"/>
+      <c r="I17" s="429"/>
+      <c r="J17" s="432"/>
       <c r="K17" s="210"/>
       <c r="L17" s="210"/>
       <c r="M17" s="279" t="s">
@@ -5986,8 +5986,8 @@
       <c r="F18" s="223"/>
       <c r="G18" s="223"/>
       <c r="H18" s="222"/>
-      <c r="I18" s="419"/>
-      <c r="J18" s="422"/>
+      <c r="I18" s="430"/>
+      <c r="J18" s="433"/>
       <c r="L18" s="210"/>
       <c r="M18" s="224"/>
     </row>
@@ -6007,11 +6007,11 @@
     </row>
     <row r="20" spans="1:14" s="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="227"/>
-      <c r="B20" s="426" t="s">
+      <c r="B20" s="413" t="s">
         <v>129</v>
       </c>
-      <c r="C20" s="426"/>
-      <c r="D20" s="428"/>
+      <c r="C20" s="413"/>
+      <c r="D20" s="415"/>
       <c r="F20" s="229" t="s">
         <v>130</v>
       </c>
@@ -6024,12 +6024,12 @@
     </row>
     <row r="21" spans="1:14" s="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="232"/>
-      <c r="B21" s="427"/>
-      <c r="C21" s="427"/>
-      <c r="D21" s="429"/>
-      <c r="F21" s="423"/>
-      <c r="G21" s="424"/>
-      <c r="H21" s="425"/>
+      <c r="B21" s="414"/>
+      <c r="C21" s="414"/>
+      <c r="D21" s="416"/>
+      <c r="F21" s="417"/>
+      <c r="G21" s="418"/>
+      <c r="H21" s="419"/>
       <c r="I21" s="230"/>
       <c r="J21" s="226"/>
       <c r="L21" s="231"/>
@@ -6303,11 +6303,11 @@
       <c r="G36" s="250" t="s">
         <v>1</v>
       </c>
-      <c r="H36" s="430">
+      <c r="H36" s="420">
         <v>31</v>
       </c>
-      <c r="I36" s="431"/>
-      <c r="J36" s="432"/>
+      <c r="I36" s="421"/>
+      <c r="J36" s="422"/>
       <c r="K36" s="210"/>
       <c r="L36" s="210"/>
     </row>
@@ -6326,15 +6326,15 @@
       <c r="L37" s="210"/>
     </row>
     <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="433" t="s">
+      <c r="A38" s="423" t="s">
         <v>146</v>
       </c>
-      <c r="B38" s="434"/>
-      <c r="C38" s="435"/>
-      <c r="D38" s="433" t="s">
+      <c r="B38" s="424"/>
+      <c r="C38" s="425"/>
+      <c r="D38" s="423" t="s">
         <v>147</v>
       </c>
-      <c r="E38" s="435"/>
+      <c r="E38" s="425"/>
       <c r="F38" s="271" t="s">
         <v>100</v>
       </c>
@@ -6346,13 +6346,13 @@
       <c r="L38" s="210"/>
     </row>
     <row r="39" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="436" t="s">
+      <c r="A39" s="406" t="s">
         <v>148</v>
       </c>
-      <c r="B39" s="437"/>
-      <c r="C39" s="438"/>
-      <c r="D39" s="436"/>
-      <c r="E39" s="438"/>
+      <c r="B39" s="407"/>
+      <c r="C39" s="408"/>
+      <c r="D39" s="406"/>
+      <c r="E39" s="408"/>
       <c r="F39" s="233"/>
       <c r="G39" s="234"/>
       <c r="H39" s="234"/>
@@ -6362,13 +6362,13 @@
       <c r="L39" s="210"/>
     </row>
     <row r="40" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="436" t="s">
+      <c r="A40" s="406" t="s">
         <v>149</v>
       </c>
-      <c r="B40" s="437"/>
-      <c r="C40" s="438"/>
-      <c r="D40" s="436"/>
-      <c r="E40" s="438"/>
+      <c r="B40" s="407"/>
+      <c r="C40" s="408"/>
+      <c r="D40" s="406"/>
+      <c r="E40" s="408"/>
       <c r="F40" s="274"/>
       <c r="G40" s="272"/>
       <c r="H40" s="272"/>
@@ -6378,61 +6378,61 @@
       <c r="L40" s="210"/>
     </row>
     <row r="41" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="436" t="s">
+      <c r="A41" s="406" t="s">
         <v>150</v>
       </c>
-      <c r="B41" s="437"/>
-      <c r="C41" s="438"/>
-      <c r="D41" s="436"/>
-      <c r="E41" s="438"/>
+      <c r="B41" s="407"/>
+      <c r="C41" s="408"/>
+      <c r="D41" s="406"/>
+      <c r="E41" s="408"/>
       <c r="F41" s="221"/>
       <c r="K41" s="210"/>
       <c r="L41" s="210"/>
     </row>
     <row r="42" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="440" t="s">
+      <c r="A42" s="410" t="s">
         <v>151</v>
       </c>
-      <c r="B42" s="441"/>
-      <c r="C42" s="442"/>
-      <c r="D42" s="436"/>
-      <c r="E42" s="438"/>
+      <c r="B42" s="411"/>
+      <c r="C42" s="412"/>
+      <c r="D42" s="406"/>
+      <c r="E42" s="408"/>
       <c r="F42" s="221"/>
       <c r="K42" s="210"/>
       <c r="L42" s="210"/>
     </row>
     <row r="43" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="440" t="s">
+      <c r="A43" s="410" t="s">
         <v>152</v>
       </c>
-      <c r="B43" s="441"/>
-      <c r="C43" s="442"/>
-      <c r="D43" s="436"/>
-      <c r="E43" s="438"/>
+      <c r="B43" s="411"/>
+      <c r="C43" s="412"/>
+      <c r="D43" s="406"/>
+      <c r="E43" s="408"/>
       <c r="F43" s="221"/>
       <c r="K43" s="210"/>
       <c r="L43" s="210"/>
     </row>
     <row r="44" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="436" t="s">
+      <c r="A44" s="406" t="s">
         <v>153</v>
       </c>
-      <c r="B44" s="437"/>
-      <c r="C44" s="438"/>
-      <c r="D44" s="436"/>
-      <c r="E44" s="438"/>
+      <c r="B44" s="407"/>
+      <c r="C44" s="408"/>
+      <c r="D44" s="406"/>
+      <c r="E44" s="408"/>
       <c r="F44" s="221"/>
       <c r="K44" s="210"/>
       <c r="L44" s="210"/>
     </row>
     <row r="45" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="436" t="s">
+      <c r="A45" s="406" t="s">
         <v>154</v>
       </c>
-      <c r="B45" s="437"/>
-      <c r="C45" s="438"/>
-      <c r="D45" s="436"/>
-      <c r="E45" s="438"/>
+      <c r="B45" s="407"/>
+      <c r="C45" s="408"/>
+      <c r="D45" s="406"/>
+      <c r="E45" s="408"/>
       <c r="F45" s="221"/>
       <c r="K45" s="210"/>
       <c r="L45" s="210"/>
@@ -6525,18 +6525,18 @@
     </row>
     <row r="53" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="439" t="s">
+      <c r="A54" s="409" t="s">
         <v>170</v>
       </c>
-      <c r="B54" s="439"/>
-      <c r="C54" s="439"/>
-      <c r="D54" s="439"/>
-      <c r="E54" s="439"/>
-      <c r="F54" s="439"/>
-      <c r="G54" s="439"/>
-      <c r="H54" s="439"/>
-      <c r="I54" s="439"/>
-      <c r="J54" s="439"/>
+      <c r="B54" s="409"/>
+      <c r="C54" s="409"/>
+      <c r="D54" s="409"/>
+      <c r="E54" s="409"/>
+      <c r="F54" s="409"/>
+      <c r="G54" s="409"/>
+      <c r="H54" s="409"/>
+      <c r="I54" s="409"/>
+      <c r="J54" s="409"/>
     </row>
     <row r="55" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6548,33 +6548,6 @@
     <protectedRange sqref="H31:J31" name="Rango8_1"/>
   </protectedRanges>
   <mergeCells count="39">
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="A54:J54"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="F17:G17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A8:J8"/>
@@ -6587,6 +6560,33 @@
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="A13:J13"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:E44"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0.39370078740157483" top="0" bottom="0" header="0" footer="0"/>
@@ -6637,38 +6637,38 @@
       <c r="M1" s="295"/>
     </row>
     <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="443" t="s">
+      <c r="A2" s="464" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="443"/>
-      <c r="C2" s="443"/>
-      <c r="D2" s="443"/>
-      <c r="E2" s="443"/>
-      <c r="F2" s="443"/>
-      <c r="G2" s="443"/>
-      <c r="H2" s="443"/>
-      <c r="I2" s="443"/>
-      <c r="J2" s="443"/>
-      <c r="K2" s="443"/>
-      <c r="L2" s="443"/>
-      <c r="M2" s="443"/>
+      <c r="B2" s="464"/>
+      <c r="C2" s="464"/>
+      <c r="D2" s="464"/>
+      <c r="E2" s="464"/>
+      <c r="F2" s="464"/>
+      <c r="G2" s="464"/>
+      <c r="H2" s="464"/>
+      <c r="I2" s="464"/>
+      <c r="J2" s="464"/>
+      <c r="K2" s="464"/>
+      <c r="L2" s="464"/>
+      <c r="M2" s="464"/>
     </row>
     <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="444">
+      <c r="A3" s="465">
         <v>0</v>
       </c>
-      <c r="B3" s="444"/>
-      <c r="C3" s="444"/>
-      <c r="D3" s="444"/>
-      <c r="E3" s="444"/>
-      <c r="F3" s="444"/>
-      <c r="G3" s="444"/>
-      <c r="H3" s="444"/>
-      <c r="I3" s="444"/>
-      <c r="J3" s="444"/>
-      <c r="K3" s="444"/>
-      <c r="L3" s="444"/>
-      <c r="M3" s="444"/>
+      <c r="B3" s="465"/>
+      <c r="C3" s="465"/>
+      <c r="D3" s="465"/>
+      <c r="E3" s="465"/>
+      <c r="F3" s="465"/>
+      <c r="G3" s="465"/>
+      <c r="H3" s="465"/>
+      <c r="I3" s="465"/>
+      <c r="J3" s="465"/>
+      <c r="K3" s="465"/>
+      <c r="L3" s="465"/>
+      <c r="M3" s="465"/>
     </row>
     <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6678,17 +6678,17 @@
       <c r="B5" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="455">
+      <c r="C5" s="476">
         <f>+FORMATO!N2</f>
         <v>0</v>
       </c>
-      <c r="D5" s="455"/>
-      <c r="E5" s="455"/>
-      <c r="F5" s="455"/>
-      <c r="G5" s="455"/>
-      <c r="H5" s="455"/>
-      <c r="I5" s="455"/>
-      <c r="J5" s="455"/>
+      <c r="D5" s="476"/>
+      <c r="E5" s="476"/>
+      <c r="F5" s="476"/>
+      <c r="G5" s="476"/>
+      <c r="H5" s="476"/>
+      <c r="I5" s="476"/>
+      <c r="J5" s="476"/>
       <c r="K5" s="299" t="s">
         <v>20</v>
       </c>
@@ -6706,17 +6706,17 @@
       <c r="B6" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="455">
+      <c r="C6" s="476">
         <f>+FORMATO!N3</f>
         <v>0</v>
       </c>
-      <c r="D6" s="455"/>
-      <c r="E6" s="455"/>
-      <c r="F6" s="455"/>
-      <c r="G6" s="455"/>
-      <c r="H6" s="455"/>
-      <c r="I6" s="455"/>
-      <c r="J6" s="455"/>
+      <c r="D6" s="476"/>
+      <c r="E6" s="476"/>
+      <c r="F6" s="476"/>
+      <c r="G6" s="476"/>
+      <c r="H6" s="476"/>
+      <c r="I6" s="476"/>
+      <c r="J6" s="476"/>
       <c r="K6" s="279" t="s">
         <v>119</v>
       </c>
@@ -6738,17 +6738,17 @@
       <c r="B7" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="455">
+      <c r="C7" s="476">
         <f>+FORMATO!N4</f>
         <v>0</v>
       </c>
-      <c r="D7" s="455"/>
-      <c r="E7" s="455"/>
-      <c r="F7" s="455"/>
-      <c r="G7" s="455"/>
-      <c r="H7" s="455"/>
-      <c r="I7" s="455"/>
-      <c r="J7" s="455"/>
+      <c r="D7" s="476"/>
+      <c r="E7" s="476"/>
+      <c r="F7" s="476"/>
+      <c r="G7" s="476"/>
+      <c r="H7" s="476"/>
+      <c r="I7" s="476"/>
+      <c r="J7" s="476"/>
       <c r="K7" s="279" t="s">
         <v>158</v>
       </c>
@@ -6770,17 +6770,17 @@
       <c r="B8" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="455">
+      <c r="C8" s="476">
         <f>+FORMATO!N5</f>
         <v>0</v>
       </c>
-      <c r="D8" s="455"/>
-      <c r="E8" s="455"/>
-      <c r="F8" s="455"/>
-      <c r="G8" s="455"/>
-      <c r="H8" s="455"/>
-      <c r="I8" s="455"/>
-      <c r="J8" s="455"/>
+      <c r="D8" s="476"/>
+      <c r="E8" s="476"/>
+      <c r="F8" s="476"/>
+      <c r="G8" s="476"/>
+      <c r="H8" s="476"/>
+      <c r="I8" s="476"/>
+      <c r="J8" s="476"/>
       <c r="K8" s="304" t="s">
         <v>36</v>
       </c>
@@ -6816,41 +6816,41 @@
       <c r="P9" s="303"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="447" t="s">
+      <c r="A10" s="468" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="448"/>
-      <c r="C10" s="448"/>
-      <c r="D10" s="448"/>
-      <c r="E10" s="448"/>
-      <c r="F10" s="448"/>
-      <c r="G10" s="448"/>
-      <c r="H10" s="448"/>
-      <c r="I10" s="448"/>
-      <c r="J10" s="448"/>
-      <c r="K10" s="448"/>
-      <c r="L10" s="448"/>
-      <c r="M10" s="449"/>
+      <c r="B10" s="469"/>
+      <c r="C10" s="469"/>
+      <c r="D10" s="469"/>
+      <c r="E10" s="469"/>
+      <c r="F10" s="469"/>
+      <c r="G10" s="469"/>
+      <c r="H10" s="469"/>
+      <c r="I10" s="469"/>
+      <c r="J10" s="469"/>
+      <c r="K10" s="469"/>
+      <c r="L10" s="469"/>
+      <c r="M10" s="470"/>
       <c r="N10" s="303"/>
       <c r="O10" s="303"/>
       <c r="P10" s="303"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="450" t="s">
+      <c r="A11" s="471" t="s">
         <v>117</v>
       </c>
-      <c r="B11" s="451"/>
-      <c r="C11" s="451"/>
-      <c r="D11" s="451"/>
-      <c r="E11" s="451"/>
-      <c r="F11" s="451"/>
-      <c r="G11" s="451"/>
-      <c r="H11" s="451"/>
-      <c r="I11" s="451"/>
-      <c r="J11" s="451"/>
-      <c r="K11" s="451"/>
-      <c r="L11" s="451"/>
-      <c r="M11" s="452"/>
+      <c r="B11" s="472"/>
+      <c r="C11" s="472"/>
+      <c r="D11" s="472"/>
+      <c r="E11" s="472"/>
+      <c r="F11" s="472"/>
+      <c r="G11" s="472"/>
+      <c r="H11" s="472"/>
+      <c r="I11" s="472"/>
+      <c r="J11" s="472"/>
+      <c r="K11" s="472"/>
+      <c r="L11" s="472"/>
+      <c r="M11" s="473"/>
       <c r="N11" s="303"/>
       <c r="O11" s="303"/>
       <c r="P11" s="303"/>
@@ -6874,13 +6874,13 @@
       <c r="P12" s="303"/>
     </row>
     <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="453" t="s">
+      <c r="A13" s="474" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="454"/>
-      <c r="C13" s="454"/>
-      <c r="D13" s="454"/>
-      <c r="E13" s="454"/>
+      <c r="B13" s="475"/>
+      <c r="C13" s="475"/>
+      <c r="D13" s="475"/>
+      <c r="E13" s="475"/>
       <c r="F13" s="318"/>
       <c r="G13" s="318"/>
       <c r="H13" s="318"/>
@@ -7011,15 +7011,15 @@
       <c r="A18" s="341"/>
       <c r="B18" s="342"/>
       <c r="C18" s="342"/>
-      <c r="D18" s="445"/>
-      <c r="E18" s="445"/>
+      <c r="D18" s="466"/>
+      <c r="E18" s="466"/>
       <c r="F18" s="342"/>
       <c r="G18" s="342"/>
       <c r="H18" s="342"/>
       <c r="I18" s="343"/>
       <c r="J18" s="343"/>
-      <c r="K18" s="446"/>
-      <c r="L18" s="446"/>
+      <c r="K18" s="467"/>
+      <c r="L18" s="467"/>
       <c r="M18" s="344"/>
       <c r="N18" s="303"/>
       <c r="O18" s="345"/>
@@ -7029,18 +7029,18 @@
       <c r="A19" s="346"/>
       <c r="B19" s="347"/>
       <c r="C19" s="347"/>
-      <c r="D19" s="456" t="s">
+      <c r="D19" s="443" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="457"/>
-      <c r="F19" s="457"/>
-      <c r="G19" s="457"/>
-      <c r="H19" s="458"/>
-      <c r="I19" s="474" t="s">
+      <c r="E19" s="444"/>
+      <c r="F19" s="444"/>
+      <c r="G19" s="444"/>
+      <c r="H19" s="445"/>
+      <c r="I19" s="461" t="s">
         <v>72</v>
       </c>
-      <c r="J19" s="474"/>
-      <c r="K19" s="475"/>
+      <c r="J19" s="461"/>
+      <c r="K19" s="462"/>
       <c r="L19" s="348"/>
       <c r="M19" s="349"/>
       <c r="N19" s="303"/>
@@ -7051,11 +7051,11 @@
       <c r="A20" s="350"/>
       <c r="B20" s="295"/>
       <c r="C20" s="295"/>
-      <c r="D20" s="459"/>
-      <c r="E20" s="460"/>
-      <c r="F20" s="460"/>
-      <c r="G20" s="460"/>
-      <c r="H20" s="461"/>
+      <c r="D20" s="446"/>
+      <c r="E20" s="447"/>
+      <c r="F20" s="447"/>
+      <c r="G20" s="447"/>
+      <c r="H20" s="448"/>
       <c r="I20" s="351">
         <v>1</v>
       </c>
@@ -7127,8 +7127,8 @@
         <f>+Datos!I14</f>
         <v>0</v>
       </c>
-      <c r="L22" s="468"/>
-      <c r="M22" s="467"/>
+      <c r="L22" s="455"/>
+      <c r="M22" s="454"/>
       <c r="N22" s="303"/>
       <c r="O22" s="364"/>
       <c r="P22" s="303"/>
@@ -7158,8 +7158,8 @@
         <f>+Datos!I15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L23" s="466"/>
-      <c r="M23" s="467"/>
+      <c r="L23" s="453"/>
+      <c r="M23" s="454"/>
       <c r="N23" s="303"/>
       <c r="O23" s="303"/>
       <c r="P23" s="364"/>
@@ -7177,12 +7177,12 @@
       <c r="H24" s="360" t="s">
         <v>1</v>
       </c>
-      <c r="I24" s="469" t="e">
+      <c r="I24" s="456" t="e">
         <f>+Datos!G16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J24" s="470"/>
-      <c r="K24" s="471"/>
+      <c r="J24" s="457"/>
+      <c r="K24" s="458"/>
       <c r="L24" s="369"/>
       <c r="M24" s="362"/>
       <c r="N24" s="303"/>
@@ -7244,10 +7244,10 @@
       <c r="C28" s="386"/>
       <c r="D28" s="367"/>
       <c r="E28" s="369"/>
-      <c r="F28" s="472" t="s">
-        <v>177</v>
-      </c>
-      <c r="G28" s="473"/>
+      <c r="F28" s="459" t="s">
+        <v>176</v>
+      </c>
+      <c r="G28" s="460"/>
       <c r="M28" s="384"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -7270,11 +7270,11 @@
       <c r="C30" s="386"/>
       <c r="D30" s="367"/>
       <c r="E30" s="369"/>
-      <c r="F30" s="462">
+      <c r="F30" s="449">
         <f>+Datos!E25</f>
         <v>0</v>
       </c>
-      <c r="G30" s="463"/>
+      <c r="G30" s="450"/>
       <c r="M30" s="384"/>
     </row>
     <row r="31" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7285,11 +7285,11 @@
       <c r="C31" s="386"/>
       <c r="D31" s="367"/>
       <c r="E31" s="369"/>
-      <c r="F31" s="462">
+      <c r="F31" s="449">
         <f>+Datos!E26</f>
         <v>0</v>
       </c>
-      <c r="G31" s="463"/>
+      <c r="G31" s="450"/>
       <c r="M31" s="384"/>
     </row>
     <row r="32" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7326,95 +7326,95 @@
       <c r="M34" s="393"/>
     </row>
     <row r="35" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="476" t="s">
+      <c r="A35" s="463" t="s">
         <v>171</v>
       </c>
-      <c r="B35" s="476"/>
-      <c r="C35" s="476"/>
-      <c r="D35" s="476"/>
-      <c r="E35" s="476"/>
-      <c r="F35" s="476"/>
-      <c r="G35" s="476"/>
-      <c r="H35" s="476"/>
-      <c r="I35" s="476"/>
-      <c r="J35" s="476"/>
-      <c r="K35" s="476"/>
-      <c r="L35" s="476"/>
-      <c r="M35" s="476"/>
+      <c r="B35" s="463"/>
+      <c r="C35" s="463"/>
+      <c r="D35" s="463"/>
+      <c r="E35" s="463"/>
+      <c r="F35" s="463"/>
+      <c r="G35" s="463"/>
+      <c r="H35" s="463"/>
+      <c r="I35" s="463"/>
+      <c r="J35" s="463"/>
+      <c r="K35" s="463"/>
+      <c r="L35" s="463"/>
+      <c r="M35" s="463"/>
     </row>
     <row r="36" spans="1:16" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="465" t="s">
+      <c r="A36" s="452" t="s">
         <v>172</v>
       </c>
-      <c r="B36" s="465"/>
-      <c r="C36" s="465"/>
-      <c r="D36" s="465"/>
-      <c r="E36" s="465"/>
-      <c r="F36" s="465"/>
-      <c r="G36" s="465"/>
-      <c r="H36" s="465"/>
-      <c r="I36" s="465"/>
-      <c r="J36" s="465"/>
-      <c r="K36" s="465"/>
-      <c r="L36" s="465"/>
-      <c r="M36" s="465"/>
+      <c r="B36" s="452"/>
+      <c r="C36" s="452"/>
+      <c r="D36" s="452"/>
+      <c r="E36" s="452"/>
+      <c r="F36" s="452"/>
+      <c r="G36" s="452"/>
+      <c r="H36" s="452"/>
+      <c r="I36" s="452"/>
+      <c r="J36" s="452"/>
+      <c r="K36" s="452"/>
+      <c r="L36" s="452"/>
+      <c r="M36" s="452"/>
     </row>
     <row r="37" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="465" t="s">
+      <c r="A37" s="452" t="s">
         <v>173</v>
       </c>
-      <c r="B37" s="465"/>
-      <c r="C37" s="465"/>
-      <c r="D37" s="465"/>
-      <c r="E37" s="465"/>
-      <c r="F37" s="465"/>
-      <c r="G37" s="465"/>
-      <c r="H37" s="465"/>
-      <c r="I37" s="465"/>
-      <c r="J37" s="465"/>
-      <c r="K37" s="465"/>
-      <c r="L37" s="465"/>
-      <c r="M37" s="465"/>
+      <c r="B37" s="452"/>
+      <c r="C37" s="452"/>
+      <c r="D37" s="452"/>
+      <c r="E37" s="452"/>
+      <c r="F37" s="452"/>
+      <c r="G37" s="452"/>
+      <c r="H37" s="452"/>
+      <c r="I37" s="452"/>
+      <c r="J37" s="452"/>
+      <c r="K37" s="452"/>
+      <c r="L37" s="452"/>
+      <c r="M37" s="452"/>
       <c r="N37" s="303"/>
       <c r="O37" s="303"/>
       <c r="P37" s="303"/>
     </row>
     <row r="38" spans="1:16" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="465" t="s">
+      <c r="A38" s="452" t="s">
         <v>174</v>
       </c>
-      <c r="B38" s="465"/>
-      <c r="C38" s="465"/>
-      <c r="D38" s="465"/>
-      <c r="E38" s="465"/>
-      <c r="F38" s="465"/>
-      <c r="G38" s="465"/>
-      <c r="H38" s="465"/>
-      <c r="I38" s="465"/>
-      <c r="J38" s="465"/>
-      <c r="K38" s="465"/>
-      <c r="L38" s="465"/>
-      <c r="M38" s="465"/>
+      <c r="B38" s="452"/>
+      <c r="C38" s="452"/>
+      <c r="D38" s="452"/>
+      <c r="E38" s="452"/>
+      <c r="F38" s="452"/>
+      <c r="G38" s="452"/>
+      <c r="H38" s="452"/>
+      <c r="I38" s="452"/>
+      <c r="J38" s="452"/>
+      <c r="K38" s="452"/>
+      <c r="L38" s="452"/>
+      <c r="M38" s="452"/>
       <c r="N38" s="303"/>
       <c r="O38" s="303"/>
       <c r="P38" s="303"/>
     </row>
     <row r="39" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="464" t="s">
+      <c r="A39" s="451" t="s">
         <v>175</v>
       </c>
-      <c r="B39" s="464"/>
-      <c r="C39" s="464"/>
-      <c r="D39" s="464"/>
-      <c r="E39" s="464"/>
-      <c r="F39" s="464"/>
-      <c r="G39" s="464"/>
-      <c r="H39" s="464"/>
-      <c r="I39" s="464"/>
-      <c r="J39" s="464"/>
-      <c r="K39" s="464"/>
-      <c r="L39" s="464"/>
-      <c r="M39" s="464"/>
+      <c r="B39" s="451"/>
+      <c r="C39" s="451"/>
+      <c r="D39" s="451"/>
+      <c r="E39" s="451"/>
+      <c r="F39" s="451"/>
+      <c r="G39" s="451"/>
+      <c r="H39" s="451"/>
+      <c r="I39" s="451"/>
+      <c r="J39" s="451"/>
+      <c r="K39" s="451"/>
+      <c r="L39" s="451"/>
+      <c r="M39" s="451"/>
       <c r="N39" s="303"/>
       <c r="O39" s="303"/>
       <c r="P39" s="303"/>
@@ -7542,7 +7542,7 @@
     </row>
     <row r="47" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="403" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B47" s="403"/>
       <c r="C47" s="403"/>
@@ -7612,13 +7612,24 @@
     </row>
     <row r="51" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="M9pFxN1vCZ6AssimQy9CSjlzNMYwxkYAI/oYy7gjk/sW0GpV64Tmh24pQaoksmla/+3jmuHbJXffSgoAOfB+NQ==" saltValue="aZQAvccvHvYOr/L9Ag76PA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="E12" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="E7:E9 C7:D8" name="Rango3_3_1_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="C5:E6" name="Rango3_3_1_1_1_1_1_2_1_1"/>
   </protectedRanges>
   <mergeCells count="24">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="C5:J5"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="C8:J8"/>
     <mergeCell ref="D19:H20"/>
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
@@ -7632,17 +7643,6 @@
     <mergeCell ref="A35:M35"/>
     <mergeCell ref="A36:M36"/>
     <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C5:J5"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="C8:J8"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F28:G28" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/app/templates/informes/EquiArena/Template_EquiArena.xlsx
+++ b/app/templates/informes/EquiArena/Template_EquiArena.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\EquiArena\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6764323F-BEE7-442D-9469-7EE07C96DA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AD288C-7B05-4AC5-9176-5DA14C381A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="556" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -845,7 +845,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Versión: 08 (11-06-2026)</t>
+    <t>Versión: 08 (12-06-2026)</t>
   </si>
 </sst>
 </file>
@@ -2945,6 +2945,123 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="44" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="44" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="44" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="1"/>
@@ -2973,121 +3090,46 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="44" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="44" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="44" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3156,48 +3198,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5773,36 +5773,36 @@
       <c r="N6" s="283"/>
     </row>
     <row r="7" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="437" t="s">
+      <c r="A7" s="409" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="437"/>
-      <c r="C7" s="437"/>
-      <c r="D7" s="437"/>
-      <c r="E7" s="437"/>
-      <c r="F7" s="437"/>
-      <c r="G7" s="437"/>
-      <c r="H7" s="437"/>
-      <c r="I7" s="437"/>
-      <c r="J7" s="437"/>
+      <c r="B7" s="409"/>
+      <c r="C7" s="409"/>
+      <c r="D7" s="409"/>
+      <c r="E7" s="409"/>
+      <c r="F7" s="409"/>
+      <c r="G7" s="409"/>
+      <c r="H7" s="409"/>
+      <c r="I7" s="409"/>
+      <c r="J7" s="409"/>
       <c r="M7" s="279" t="s">
         <v>119</v>
       </c>
       <c r="N7" s="283"/>
     </row>
     <row r="8" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="438" t="s">
+      <c r="A8" s="410" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="438"/>
-      <c r="C8" s="438"/>
-      <c r="D8" s="438"/>
-      <c r="E8" s="438"/>
-      <c r="F8" s="438"/>
-      <c r="G8" s="438"/>
-      <c r="H8" s="438"/>
-      <c r="I8" s="438"/>
-      <c r="J8" s="438"/>
+      <c r="B8" s="410"/>
+      <c r="C8" s="410"/>
+      <c r="D8" s="410"/>
+      <c r="E8" s="410"/>
+      <c r="F8" s="410"/>
+      <c r="G8" s="410"/>
+      <c r="H8" s="410"/>
+      <c r="I8" s="410"/>
+      <c r="J8" s="410"/>
       <c r="M8" s="279" t="s">
         <v>157</v>
       </c>
@@ -5825,22 +5825,22 @@
       <c r="N9" s="283"/>
     </row>
     <row r="10" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="439" t="s">
+      <c r="B10" s="411" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="439"/>
-      <c r="D10" s="439" t="s">
+      <c r="C10" s="411"/>
+      <c r="D10" s="411" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="439"/>
-      <c r="F10" s="439" t="s">
+      <c r="E10" s="411"/>
+      <c r="F10" s="411" t="s">
         <v>125</v>
       </c>
-      <c r="G10" s="439"/>
-      <c r="H10" s="439" t="s">
+      <c r="G10" s="411"/>
+      <c r="H10" s="411" t="s">
         <v>126</v>
       </c>
-      <c r="I10" s="439"/>
+      <c r="I10" s="411"/>
       <c r="J10" s="209"/>
       <c r="K10" s="210"/>
       <c r="L10" s="210"/>
@@ -5849,14 +5849,14 @@
     </row>
     <row r="11" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="211"/>
-      <c r="B11" s="439"/>
-      <c r="C11" s="439"/>
-      <c r="D11" s="439"/>
-      <c r="E11" s="439"/>
-      <c r="F11" s="439"/>
-      <c r="G11" s="439"/>
-      <c r="H11" s="439"/>
-      <c r="I11" s="439"/>
+      <c r="B11" s="411"/>
+      <c r="C11" s="411"/>
+      <c r="D11" s="411"/>
+      <c r="E11" s="411"/>
+      <c r="F11" s="411"/>
+      <c r="G11" s="411"/>
+      <c r="H11" s="411"/>
+      <c r="I11" s="411"/>
       <c r="J11" s="212"/>
       <c r="K11" s="210"/>
       <c r="L11" s="210"/>
@@ -5884,18 +5884,18 @@
       <c r="N12" s="284"/>
     </row>
     <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="440" t="s">
+      <c r="A13" s="412" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="441"/>
-      <c r="C13" s="441"/>
-      <c r="D13" s="441"/>
-      <c r="E13" s="441"/>
-      <c r="F13" s="441"/>
-      <c r="G13" s="441"/>
-      <c r="H13" s="441"/>
-      <c r="I13" s="441"/>
-      <c r="J13" s="442"/>
+      <c r="B13" s="413"/>
+      <c r="C13" s="413"/>
+      <c r="D13" s="413"/>
+      <c r="E13" s="413"/>
+      <c r="F13" s="413"/>
+      <c r="G13" s="413"/>
+      <c r="H13" s="413"/>
+      <c r="I13" s="413"/>
+      <c r="J13" s="414"/>
       <c r="K13" s="210"/>
       <c r="L13" s="210"/>
       <c r="M13" s="279" t="s">
@@ -5904,18 +5904,18 @@
       <c r="N13" s="284"/>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="434" t="s">
+      <c r="A14" s="406" t="s">
         <v>117</v>
       </c>
-      <c r="B14" s="435"/>
-      <c r="C14" s="435"/>
-      <c r="D14" s="435"/>
-      <c r="E14" s="435"/>
-      <c r="F14" s="435"/>
-      <c r="G14" s="435"/>
-      <c r="H14" s="435"/>
-      <c r="I14" s="435"/>
-      <c r="J14" s="436"/>
+      <c r="B14" s="407"/>
+      <c r="C14" s="407"/>
+      <c r="D14" s="407"/>
+      <c r="E14" s="407"/>
+      <c r="F14" s="407"/>
+      <c r="G14" s="407"/>
+      <c r="H14" s="407"/>
+      <c r="I14" s="407"/>
+      <c r="J14" s="408"/>
       <c r="K14" s="210"/>
       <c r="L14" s="210"/>
       <c r="M14" s="282"/>
@@ -5941,21 +5941,21 @@
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="221"/>
-      <c r="B16" s="426" t="s">
+      <c r="B16" s="415" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="426"/>
-      <c r="D16" s="426"/>
+      <c r="C16" s="415"/>
+      <c r="D16" s="415"/>
       <c r="E16" s="222"/>
-      <c r="F16" s="427" t="s">
+      <c r="F16" s="416" t="s">
         <v>127</v>
       </c>
-      <c r="G16" s="427"/>
+      <c r="G16" s="416"/>
       <c r="H16" s="222"/>
-      <c r="I16" s="428" t="s">
+      <c r="I16" s="417" t="s">
         <v>128</v>
       </c>
-      <c r="J16" s="431"/>
+      <c r="J16" s="420"/>
       <c r="K16" s="210"/>
       <c r="L16" s="210"/>
       <c r="M16" s="279" t="s">
@@ -5965,15 +5965,15 @@
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="221"/>
-      <c r="B17" s="417"/>
-      <c r="C17" s="418"/>
-      <c r="D17" s="419"/>
+      <c r="B17" s="423"/>
+      <c r="C17" s="424"/>
+      <c r="D17" s="425"/>
       <c r="E17" s="223"/>
-      <c r="F17" s="417"/>
-      <c r="G17" s="419"/>
+      <c r="F17" s="423"/>
+      <c r="G17" s="425"/>
       <c r="H17" s="222"/>
-      <c r="I17" s="429"/>
-      <c r="J17" s="432"/>
+      <c r="I17" s="418"/>
+      <c r="J17" s="421"/>
       <c r="K17" s="210"/>
       <c r="L17" s="210"/>
       <c r="M17" s="279" t="s">
@@ -5986,8 +5986,8 @@
       <c r="F18" s="223"/>
       <c r="G18" s="223"/>
       <c r="H18" s="222"/>
-      <c r="I18" s="430"/>
-      <c r="J18" s="433"/>
+      <c r="I18" s="419"/>
+      <c r="J18" s="422"/>
       <c r="L18" s="210"/>
       <c r="M18" s="224"/>
     </row>
@@ -6007,11 +6007,11 @@
     </row>
     <row r="20" spans="1:14" s="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="227"/>
-      <c r="B20" s="413" t="s">
+      <c r="B20" s="426" t="s">
         <v>129</v>
       </c>
-      <c r="C20" s="413"/>
-      <c r="D20" s="415"/>
+      <c r="C20" s="426"/>
+      <c r="D20" s="428"/>
       <c r="F20" s="229" t="s">
         <v>130</v>
       </c>
@@ -6024,12 +6024,12 @@
     </row>
     <row r="21" spans="1:14" s="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="232"/>
-      <c r="B21" s="414"/>
-      <c r="C21" s="414"/>
-      <c r="D21" s="416"/>
-      <c r="F21" s="417"/>
-      <c r="G21" s="418"/>
-      <c r="H21" s="419"/>
+      <c r="B21" s="427"/>
+      <c r="C21" s="427"/>
+      <c r="D21" s="429"/>
+      <c r="F21" s="423"/>
+      <c r="G21" s="424"/>
+      <c r="H21" s="425"/>
       <c r="I21" s="230"/>
       <c r="J21" s="226"/>
       <c r="L21" s="231"/>
@@ -6303,11 +6303,11 @@
       <c r="G36" s="250" t="s">
         <v>1</v>
       </c>
-      <c r="H36" s="420">
+      <c r="H36" s="430">
         <v>31</v>
       </c>
-      <c r="I36" s="421"/>
-      <c r="J36" s="422"/>
+      <c r="I36" s="431"/>
+      <c r="J36" s="432"/>
       <c r="K36" s="210"/>
       <c r="L36" s="210"/>
     </row>
@@ -6326,15 +6326,15 @@
       <c r="L37" s="210"/>
     </row>
     <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="423" t="s">
+      <c r="A38" s="433" t="s">
         <v>146</v>
       </c>
-      <c r="B38" s="424"/>
-      <c r="C38" s="425"/>
-      <c r="D38" s="423" t="s">
+      <c r="B38" s="434"/>
+      <c r="C38" s="435"/>
+      <c r="D38" s="433" t="s">
         <v>147</v>
       </c>
-      <c r="E38" s="425"/>
+      <c r="E38" s="435"/>
       <c r="F38" s="271" t="s">
         <v>100</v>
       </c>
@@ -6346,13 +6346,13 @@
       <c r="L38" s="210"/>
     </row>
     <row r="39" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="406" t="s">
+      <c r="A39" s="436" t="s">
         <v>148</v>
       </c>
-      <c r="B39" s="407"/>
-      <c r="C39" s="408"/>
-      <c r="D39" s="406"/>
-      <c r="E39" s="408"/>
+      <c r="B39" s="437"/>
+      <c r="C39" s="438"/>
+      <c r="D39" s="436"/>
+      <c r="E39" s="438"/>
       <c r="F39" s="233"/>
       <c r="G39" s="234"/>
       <c r="H39" s="234"/>
@@ -6362,13 +6362,13 @@
       <c r="L39" s="210"/>
     </row>
     <row r="40" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="406" t="s">
+      <c r="A40" s="436" t="s">
         <v>149</v>
       </c>
-      <c r="B40" s="407"/>
-      <c r="C40" s="408"/>
-      <c r="D40" s="406"/>
-      <c r="E40" s="408"/>
+      <c r="B40" s="437"/>
+      <c r="C40" s="438"/>
+      <c r="D40" s="436"/>
+      <c r="E40" s="438"/>
       <c r="F40" s="274"/>
       <c r="G40" s="272"/>
       <c r="H40" s="272"/>
@@ -6378,61 +6378,61 @@
       <c r="L40" s="210"/>
     </row>
     <row r="41" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="406" t="s">
+      <c r="A41" s="436" t="s">
         <v>150</v>
       </c>
-      <c r="B41" s="407"/>
-      <c r="C41" s="408"/>
-      <c r="D41" s="406"/>
-      <c r="E41" s="408"/>
+      <c r="B41" s="437"/>
+      <c r="C41" s="438"/>
+      <c r="D41" s="436"/>
+      <c r="E41" s="438"/>
       <c r="F41" s="221"/>
       <c r="K41" s="210"/>
       <c r="L41" s="210"/>
     </row>
     <row r="42" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="410" t="s">
+      <c r="A42" s="440" t="s">
         <v>151</v>
       </c>
-      <c r="B42" s="411"/>
-      <c r="C42" s="412"/>
-      <c r="D42" s="406"/>
-      <c r="E42" s="408"/>
+      <c r="B42" s="441"/>
+      <c r="C42" s="442"/>
+      <c r="D42" s="436"/>
+      <c r="E42" s="438"/>
       <c r="F42" s="221"/>
       <c r="K42" s="210"/>
       <c r="L42" s="210"/>
     </row>
     <row r="43" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="410" t="s">
+      <c r="A43" s="440" t="s">
         <v>152</v>
       </c>
-      <c r="B43" s="411"/>
-      <c r="C43" s="412"/>
-      <c r="D43" s="406"/>
-      <c r="E43" s="408"/>
+      <c r="B43" s="441"/>
+      <c r="C43" s="442"/>
+      <c r="D43" s="436"/>
+      <c r="E43" s="438"/>
       <c r="F43" s="221"/>
       <c r="K43" s="210"/>
       <c r="L43" s="210"/>
     </row>
     <row r="44" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="406" t="s">
+      <c r="A44" s="436" t="s">
         <v>153</v>
       </c>
-      <c r="B44" s="407"/>
-      <c r="C44" s="408"/>
-      <c r="D44" s="406"/>
-      <c r="E44" s="408"/>
+      <c r="B44" s="437"/>
+      <c r="C44" s="438"/>
+      <c r="D44" s="436"/>
+      <c r="E44" s="438"/>
       <c r="F44" s="221"/>
       <c r="K44" s="210"/>
       <c r="L44" s="210"/>
     </row>
     <row r="45" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="406" t="s">
+      <c r="A45" s="436" t="s">
         <v>154</v>
       </c>
-      <c r="B45" s="407"/>
-      <c r="C45" s="408"/>
-      <c r="D45" s="406"/>
-      <c r="E45" s="408"/>
+      <c r="B45" s="437"/>
+      <c r="C45" s="438"/>
+      <c r="D45" s="436"/>
+      <c r="E45" s="438"/>
       <c r="F45" s="221"/>
       <c r="K45" s="210"/>
       <c r="L45" s="210"/>
@@ -6525,18 +6525,18 @@
     </row>
     <row r="53" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="409" t="s">
+      <c r="A54" s="439" t="s">
         <v>170</v>
       </c>
-      <c r="B54" s="409"/>
-      <c r="C54" s="409"/>
-      <c r="D54" s="409"/>
-      <c r="E54" s="409"/>
-      <c r="F54" s="409"/>
-      <c r="G54" s="409"/>
-      <c r="H54" s="409"/>
-      <c r="I54" s="409"/>
-      <c r="J54" s="409"/>
+      <c r="B54" s="439"/>
+      <c r="C54" s="439"/>
+      <c r="D54" s="439"/>
+      <c r="E54" s="439"/>
+      <c r="F54" s="439"/>
+      <c r="G54" s="439"/>
+      <c r="H54" s="439"/>
+      <c r="I54" s="439"/>
+      <c r="J54" s="439"/>
     </row>
     <row r="55" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6548,6 +6548,33 @@
     <protectedRange sqref="H31:J31" name="Rango8_1"/>
   </protectedRanges>
   <mergeCells count="39">
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="F17:G17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A8:J8"/>
@@ -6560,33 +6587,6 @@
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="A13:J13"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="A54:J54"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="D44:E44"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0.39370078740157483" top="0" bottom="0" header="0" footer="0"/>
@@ -6637,38 +6637,38 @@
       <c r="M1" s="295"/>
     </row>
     <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="464" t="s">
+      <c r="A2" s="443" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="464"/>
-      <c r="C2" s="464"/>
-      <c r="D2" s="464"/>
-      <c r="E2" s="464"/>
-      <c r="F2" s="464"/>
-      <c r="G2" s="464"/>
-      <c r="H2" s="464"/>
-      <c r="I2" s="464"/>
-      <c r="J2" s="464"/>
-      <c r="K2" s="464"/>
-      <c r="L2" s="464"/>
-      <c r="M2" s="464"/>
+      <c r="B2" s="443"/>
+      <c r="C2" s="443"/>
+      <c r="D2" s="443"/>
+      <c r="E2" s="443"/>
+      <c r="F2" s="443"/>
+      <c r="G2" s="443"/>
+      <c r="H2" s="443"/>
+      <c r="I2" s="443"/>
+      <c r="J2" s="443"/>
+      <c r="K2" s="443"/>
+      <c r="L2" s="443"/>
+      <c r="M2" s="443"/>
     </row>
     <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="465">
+      <c r="A3" s="444">
         <v>0</v>
       </c>
-      <c r="B3" s="465"/>
-      <c r="C3" s="465"/>
-      <c r="D3" s="465"/>
-      <c r="E3" s="465"/>
-      <c r="F3" s="465"/>
-      <c r="G3" s="465"/>
-      <c r="H3" s="465"/>
-      <c r="I3" s="465"/>
-      <c r="J3" s="465"/>
-      <c r="K3" s="465"/>
-      <c r="L3" s="465"/>
-      <c r="M3" s="465"/>
+      <c r="B3" s="444"/>
+      <c r="C3" s="444"/>
+      <c r="D3" s="444"/>
+      <c r="E3" s="444"/>
+      <c r="F3" s="444"/>
+      <c r="G3" s="444"/>
+      <c r="H3" s="444"/>
+      <c r="I3" s="444"/>
+      <c r="J3" s="444"/>
+      <c r="K3" s="444"/>
+      <c r="L3" s="444"/>
+      <c r="M3" s="444"/>
     </row>
     <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6678,17 +6678,17 @@
       <c r="B5" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="476">
+      <c r="C5" s="455">
         <f>+FORMATO!N2</f>
         <v>0</v>
       </c>
-      <c r="D5" s="476"/>
-      <c r="E5" s="476"/>
-      <c r="F5" s="476"/>
-      <c r="G5" s="476"/>
-      <c r="H5" s="476"/>
-      <c r="I5" s="476"/>
-      <c r="J5" s="476"/>
+      <c r="D5" s="455"/>
+      <c r="E5" s="455"/>
+      <c r="F5" s="455"/>
+      <c r="G5" s="455"/>
+      <c r="H5" s="455"/>
+      <c r="I5" s="455"/>
+      <c r="J5" s="455"/>
       <c r="K5" s="299" t="s">
         <v>20</v>
       </c>
@@ -6706,17 +6706,17 @@
       <c r="B6" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="476">
+      <c r="C6" s="455">
         <f>+FORMATO!N3</f>
         <v>0</v>
       </c>
-      <c r="D6" s="476"/>
-      <c r="E6" s="476"/>
-      <c r="F6" s="476"/>
-      <c r="G6" s="476"/>
-      <c r="H6" s="476"/>
-      <c r="I6" s="476"/>
-      <c r="J6" s="476"/>
+      <c r="D6" s="455"/>
+      <c r="E6" s="455"/>
+      <c r="F6" s="455"/>
+      <c r="G6" s="455"/>
+      <c r="H6" s="455"/>
+      <c r="I6" s="455"/>
+      <c r="J6" s="455"/>
       <c r="K6" s="279" t="s">
         <v>119</v>
       </c>
@@ -6738,17 +6738,17 @@
       <c r="B7" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="476">
+      <c r="C7" s="455">
         <f>+FORMATO!N4</f>
         <v>0</v>
       </c>
-      <c r="D7" s="476"/>
-      <c r="E7" s="476"/>
-      <c r="F7" s="476"/>
-      <c r="G7" s="476"/>
-      <c r="H7" s="476"/>
-      <c r="I7" s="476"/>
-      <c r="J7" s="476"/>
+      <c r="D7" s="455"/>
+      <c r="E7" s="455"/>
+      <c r="F7" s="455"/>
+      <c r="G7" s="455"/>
+      <c r="H7" s="455"/>
+      <c r="I7" s="455"/>
+      <c r="J7" s="455"/>
       <c r="K7" s="279" t="s">
         <v>158</v>
       </c>
@@ -6770,17 +6770,17 @@
       <c r="B8" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="476">
+      <c r="C8" s="455">
         <f>+FORMATO!N5</f>
         <v>0</v>
       </c>
-      <c r="D8" s="476"/>
-      <c r="E8" s="476"/>
-      <c r="F8" s="476"/>
-      <c r="G8" s="476"/>
-      <c r="H8" s="476"/>
-      <c r="I8" s="476"/>
-      <c r="J8" s="476"/>
+      <c r="D8" s="455"/>
+      <c r="E8" s="455"/>
+      <c r="F8" s="455"/>
+      <c r="G8" s="455"/>
+      <c r="H8" s="455"/>
+      <c r="I8" s="455"/>
+      <c r="J8" s="455"/>
       <c r="K8" s="304" t="s">
         <v>36</v>
       </c>
@@ -6816,41 +6816,41 @@
       <c r="P9" s="303"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="468" t="s">
+      <c r="A10" s="447" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="469"/>
-      <c r="C10" s="469"/>
-      <c r="D10" s="469"/>
-      <c r="E10" s="469"/>
-      <c r="F10" s="469"/>
-      <c r="G10" s="469"/>
-      <c r="H10" s="469"/>
-      <c r="I10" s="469"/>
-      <c r="J10" s="469"/>
-      <c r="K10" s="469"/>
-      <c r="L10" s="469"/>
-      <c r="M10" s="470"/>
+      <c r="B10" s="448"/>
+      <c r="C10" s="448"/>
+      <c r="D10" s="448"/>
+      <c r="E10" s="448"/>
+      <c r="F10" s="448"/>
+      <c r="G10" s="448"/>
+      <c r="H10" s="448"/>
+      <c r="I10" s="448"/>
+      <c r="J10" s="448"/>
+      <c r="K10" s="448"/>
+      <c r="L10" s="448"/>
+      <c r="M10" s="449"/>
       <c r="N10" s="303"/>
       <c r="O10" s="303"/>
       <c r="P10" s="303"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="471" t="s">
+      <c r="A11" s="450" t="s">
         <v>117</v>
       </c>
-      <c r="B11" s="472"/>
-      <c r="C11" s="472"/>
-      <c r="D11" s="472"/>
-      <c r="E11" s="472"/>
-      <c r="F11" s="472"/>
-      <c r="G11" s="472"/>
-      <c r="H11" s="472"/>
-      <c r="I11" s="472"/>
-      <c r="J11" s="472"/>
-      <c r="K11" s="472"/>
-      <c r="L11" s="472"/>
-      <c r="M11" s="473"/>
+      <c r="B11" s="451"/>
+      <c r="C11" s="451"/>
+      <c r="D11" s="451"/>
+      <c r="E11" s="451"/>
+      <c r="F11" s="451"/>
+      <c r="G11" s="451"/>
+      <c r="H11" s="451"/>
+      <c r="I11" s="451"/>
+      <c r="J11" s="451"/>
+      <c r="K11" s="451"/>
+      <c r="L11" s="451"/>
+      <c r="M11" s="452"/>
       <c r="N11" s="303"/>
       <c r="O11" s="303"/>
       <c r="P11" s="303"/>
@@ -6874,13 +6874,13 @@
       <c r="P12" s="303"/>
     </row>
     <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="474" t="s">
+      <c r="A13" s="453" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="475"/>
-      <c r="C13" s="475"/>
-      <c r="D13" s="475"/>
-      <c r="E13" s="475"/>
+      <c r="B13" s="454"/>
+      <c r="C13" s="454"/>
+      <c r="D13" s="454"/>
+      <c r="E13" s="454"/>
       <c r="F13" s="318"/>
       <c r="G13" s="318"/>
       <c r="H13" s="318"/>
@@ -7011,15 +7011,15 @@
       <c r="A18" s="341"/>
       <c r="B18" s="342"/>
       <c r="C18" s="342"/>
-      <c r="D18" s="466"/>
-      <c r="E18" s="466"/>
+      <c r="D18" s="445"/>
+      <c r="E18" s="445"/>
       <c r="F18" s="342"/>
       <c r="G18" s="342"/>
       <c r="H18" s="342"/>
       <c r="I18" s="343"/>
       <c r="J18" s="343"/>
-      <c r="K18" s="467"/>
-      <c r="L18" s="467"/>
+      <c r="K18" s="446"/>
+      <c r="L18" s="446"/>
       <c r="M18" s="344"/>
       <c r="N18" s="303"/>
       <c r="O18" s="345"/>
@@ -7029,18 +7029,18 @@
       <c r="A19" s="346"/>
       <c r="B19" s="347"/>
       <c r="C19" s="347"/>
-      <c r="D19" s="443" t="s">
+      <c r="D19" s="456" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="444"/>
-      <c r="F19" s="444"/>
-      <c r="G19" s="444"/>
-      <c r="H19" s="445"/>
-      <c r="I19" s="461" t="s">
+      <c r="E19" s="457"/>
+      <c r="F19" s="457"/>
+      <c r="G19" s="457"/>
+      <c r="H19" s="458"/>
+      <c r="I19" s="474" t="s">
         <v>72</v>
       </c>
-      <c r="J19" s="461"/>
-      <c r="K19" s="462"/>
+      <c r="J19" s="474"/>
+      <c r="K19" s="475"/>
       <c r="L19" s="348"/>
       <c r="M19" s="349"/>
       <c r="N19" s="303"/>
@@ -7051,11 +7051,11 @@
       <c r="A20" s="350"/>
       <c r="B20" s="295"/>
       <c r="C20" s="295"/>
-      <c r="D20" s="446"/>
-      <c r="E20" s="447"/>
-      <c r="F20" s="447"/>
-      <c r="G20" s="447"/>
-      <c r="H20" s="448"/>
+      <c r="D20" s="459"/>
+      <c r="E20" s="460"/>
+      <c r="F20" s="460"/>
+      <c r="G20" s="460"/>
+      <c r="H20" s="461"/>
       <c r="I20" s="351">
         <v>1</v>
       </c>
@@ -7127,8 +7127,8 @@
         <f>+Datos!I14</f>
         <v>0</v>
       </c>
-      <c r="L22" s="455"/>
-      <c r="M22" s="454"/>
+      <c r="L22" s="468"/>
+      <c r="M22" s="467"/>
       <c r="N22" s="303"/>
       <c r="O22" s="364"/>
       <c r="P22" s="303"/>
@@ -7158,8 +7158,8 @@
         <f>+Datos!I15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L23" s="453"/>
-      <c r="M23" s="454"/>
+      <c r="L23" s="466"/>
+      <c r="M23" s="467"/>
       <c r="N23" s="303"/>
       <c r="O23" s="303"/>
       <c r="P23" s="364"/>
@@ -7177,12 +7177,12 @@
       <c r="H24" s="360" t="s">
         <v>1</v>
       </c>
-      <c r="I24" s="456" t="e">
+      <c r="I24" s="469" t="e">
         <f>+Datos!G16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J24" s="457"/>
-      <c r="K24" s="458"/>
+      <c r="J24" s="470"/>
+      <c r="K24" s="471"/>
       <c r="L24" s="369"/>
       <c r="M24" s="362"/>
       <c r="N24" s="303"/>
@@ -7244,10 +7244,10 @@
       <c r="C28" s="386"/>
       <c r="D28" s="367"/>
       <c r="E28" s="369"/>
-      <c r="F28" s="459" t="s">
+      <c r="F28" s="472" t="s">
         <v>176</v>
       </c>
-      <c r="G28" s="460"/>
+      <c r="G28" s="473"/>
       <c r="M28" s="384"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -7270,11 +7270,11 @@
       <c r="C30" s="386"/>
       <c r="D30" s="367"/>
       <c r="E30" s="369"/>
-      <c r="F30" s="449">
+      <c r="F30" s="462">
         <f>+Datos!E25</f>
         <v>0</v>
       </c>
-      <c r="G30" s="450"/>
+      <c r="G30" s="463"/>
       <c r="M30" s="384"/>
     </row>
     <row r="31" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7285,11 +7285,11 @@
       <c r="C31" s="386"/>
       <c r="D31" s="367"/>
       <c r="E31" s="369"/>
-      <c r="F31" s="449">
+      <c r="F31" s="462">
         <f>+Datos!E26</f>
         <v>0</v>
       </c>
-      <c r="G31" s="450"/>
+      <c r="G31" s="463"/>
       <c r="M31" s="384"/>
     </row>
     <row r="32" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7326,95 +7326,95 @@
       <c r="M34" s="393"/>
     </row>
     <row r="35" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="463" t="s">
+      <c r="A35" s="476" t="s">
         <v>171</v>
       </c>
-      <c r="B35" s="463"/>
-      <c r="C35" s="463"/>
-      <c r="D35" s="463"/>
-      <c r="E35" s="463"/>
-      <c r="F35" s="463"/>
-      <c r="G35" s="463"/>
-      <c r="H35" s="463"/>
-      <c r="I35" s="463"/>
-      <c r="J35" s="463"/>
-      <c r="K35" s="463"/>
-      <c r="L35" s="463"/>
-      <c r="M35" s="463"/>
+      <c r="B35" s="476"/>
+      <c r="C35" s="476"/>
+      <c r="D35" s="476"/>
+      <c r="E35" s="476"/>
+      <c r="F35" s="476"/>
+      <c r="G35" s="476"/>
+      <c r="H35" s="476"/>
+      <c r="I35" s="476"/>
+      <c r="J35" s="476"/>
+      <c r="K35" s="476"/>
+      <c r="L35" s="476"/>
+      <c r="M35" s="476"/>
     </row>
     <row r="36" spans="1:16" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="452" t="s">
+      <c r="A36" s="465" t="s">
         <v>172</v>
       </c>
-      <c r="B36" s="452"/>
-      <c r="C36" s="452"/>
-      <c r="D36" s="452"/>
-      <c r="E36" s="452"/>
-      <c r="F36" s="452"/>
-      <c r="G36" s="452"/>
-      <c r="H36" s="452"/>
-      <c r="I36" s="452"/>
-      <c r="J36" s="452"/>
-      <c r="K36" s="452"/>
-      <c r="L36" s="452"/>
-      <c r="M36" s="452"/>
+      <c r="B36" s="465"/>
+      <c r="C36" s="465"/>
+      <c r="D36" s="465"/>
+      <c r="E36" s="465"/>
+      <c r="F36" s="465"/>
+      <c r="G36" s="465"/>
+      <c r="H36" s="465"/>
+      <c r="I36" s="465"/>
+      <c r="J36" s="465"/>
+      <c r="K36" s="465"/>
+      <c r="L36" s="465"/>
+      <c r="M36" s="465"/>
     </row>
     <row r="37" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="452" t="s">
+      <c r="A37" s="465" t="s">
         <v>173</v>
       </c>
-      <c r="B37" s="452"/>
-      <c r="C37" s="452"/>
-      <c r="D37" s="452"/>
-      <c r="E37" s="452"/>
-      <c r="F37" s="452"/>
-      <c r="G37" s="452"/>
-      <c r="H37" s="452"/>
-      <c r="I37" s="452"/>
-      <c r="J37" s="452"/>
-      <c r="K37" s="452"/>
-      <c r="L37" s="452"/>
-      <c r="M37" s="452"/>
+      <c r="B37" s="465"/>
+      <c r="C37" s="465"/>
+      <c r="D37" s="465"/>
+      <c r="E37" s="465"/>
+      <c r="F37" s="465"/>
+      <c r="G37" s="465"/>
+      <c r="H37" s="465"/>
+      <c r="I37" s="465"/>
+      <c r="J37" s="465"/>
+      <c r="K37" s="465"/>
+      <c r="L37" s="465"/>
+      <c r="M37" s="465"/>
       <c r="N37" s="303"/>
       <c r="O37" s="303"/>
       <c r="P37" s="303"/>
     </row>
     <row r="38" spans="1:16" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="452" t="s">
+      <c r="A38" s="465" t="s">
         <v>174</v>
       </c>
-      <c r="B38" s="452"/>
-      <c r="C38" s="452"/>
-      <c r="D38" s="452"/>
-      <c r="E38" s="452"/>
-      <c r="F38" s="452"/>
-      <c r="G38" s="452"/>
-      <c r="H38" s="452"/>
-      <c r="I38" s="452"/>
-      <c r="J38" s="452"/>
-      <c r="K38" s="452"/>
-      <c r="L38" s="452"/>
-      <c r="M38" s="452"/>
+      <c r="B38" s="465"/>
+      <c r="C38" s="465"/>
+      <c r="D38" s="465"/>
+      <c r="E38" s="465"/>
+      <c r="F38" s="465"/>
+      <c r="G38" s="465"/>
+      <c r="H38" s="465"/>
+      <c r="I38" s="465"/>
+      <c r="J38" s="465"/>
+      <c r="K38" s="465"/>
+      <c r="L38" s="465"/>
+      <c r="M38" s="465"/>
       <c r="N38" s="303"/>
       <c r="O38" s="303"/>
       <c r="P38" s="303"/>
     </row>
     <row r="39" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="451" t="s">
+      <c r="A39" s="464" t="s">
         <v>175</v>
       </c>
-      <c r="B39" s="451"/>
-      <c r="C39" s="451"/>
-      <c r="D39" s="451"/>
-      <c r="E39" s="451"/>
-      <c r="F39" s="451"/>
-      <c r="G39" s="451"/>
-      <c r="H39" s="451"/>
-      <c r="I39" s="451"/>
-      <c r="J39" s="451"/>
-      <c r="K39" s="451"/>
-      <c r="L39" s="451"/>
-      <c r="M39" s="451"/>
+      <c r="B39" s="464"/>
+      <c r="C39" s="464"/>
+      <c r="D39" s="464"/>
+      <c r="E39" s="464"/>
+      <c r="F39" s="464"/>
+      <c r="G39" s="464"/>
+      <c r="H39" s="464"/>
+      <c r="I39" s="464"/>
+      <c r="J39" s="464"/>
+      <c r="K39" s="464"/>
+      <c r="L39" s="464"/>
+      <c r="M39" s="464"/>
       <c r="N39" s="303"/>
       <c r="O39" s="303"/>
       <c r="P39" s="303"/>
@@ -7619,17 +7619,6 @@
     <protectedRange sqref="C5:E6" name="Rango3_3_1_1_1_1_1_2_1_1"/>
   </protectedRanges>
   <mergeCells count="24">
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C5:J5"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="C8:J8"/>
     <mergeCell ref="D19:H20"/>
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
@@ -7643,6 +7632,17 @@
     <mergeCell ref="A35:M35"/>
     <mergeCell ref="A36:M36"/>
     <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="C5:J5"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="C8:J8"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F28:G28" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/app/templates/informes/EquiArena/Template_EquiArena.xlsx
+++ b/app/templates/informes/EquiArena/Template_EquiArena.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\EquiArena\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\6.1 JUNIO INICIA 15-06-25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AD288C-7B05-4AC5-9176-5DA14C381A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539911C6-48A8-4690-B9CD-F42F5202E243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="556" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2945,6 +2945,115 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="44" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="44" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="44" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="1"/>
@@ -2981,114 +3090,72 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="44" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="44" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="44" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3131,73 +3198,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="4" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3596,7 +3596,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="119672192"/>
@@ -3633,7 +3633,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="119670272"/>
@@ -3672,7 +3672,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4648,7 +4648,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -4707,7 +4707,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -4826,7 +4826,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -4877,7 +4877,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -4929,7 +4929,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -4961,7 +4961,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -5773,36 +5773,36 @@
       <c r="N6" s="283"/>
     </row>
     <row r="7" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="409" t="s">
+      <c r="A7" s="437" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="409"/>
-      <c r="C7" s="409"/>
-      <c r="D7" s="409"/>
-      <c r="E7" s="409"/>
-      <c r="F7" s="409"/>
-      <c r="G7" s="409"/>
-      <c r="H7" s="409"/>
-      <c r="I7" s="409"/>
-      <c r="J7" s="409"/>
+      <c r="B7" s="437"/>
+      <c r="C7" s="437"/>
+      <c r="D7" s="437"/>
+      <c r="E7" s="437"/>
+      <c r="F7" s="437"/>
+      <c r="G7" s="437"/>
+      <c r="H7" s="437"/>
+      <c r="I7" s="437"/>
+      <c r="J7" s="437"/>
       <c r="M7" s="279" t="s">
         <v>119</v>
       </c>
       <c r="N7" s="283"/>
     </row>
     <row r="8" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="410" t="s">
+      <c r="A8" s="438" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="410"/>
-      <c r="C8" s="410"/>
-      <c r="D8" s="410"/>
-      <c r="E8" s="410"/>
-      <c r="F8" s="410"/>
-      <c r="G8" s="410"/>
-      <c r="H8" s="410"/>
-      <c r="I8" s="410"/>
-      <c r="J8" s="410"/>
+      <c r="B8" s="438"/>
+      <c r="C8" s="438"/>
+      <c r="D8" s="438"/>
+      <c r="E8" s="438"/>
+      <c r="F8" s="438"/>
+      <c r="G8" s="438"/>
+      <c r="H8" s="438"/>
+      <c r="I8" s="438"/>
+      <c r="J8" s="438"/>
       <c r="M8" s="279" t="s">
         <v>157</v>
       </c>
@@ -5825,22 +5825,22 @@
       <c r="N9" s="283"/>
     </row>
     <row r="10" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="411" t="s">
+      <c r="B10" s="439" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="411"/>
-      <c r="D10" s="411" t="s">
+      <c r="C10" s="439"/>
+      <c r="D10" s="439" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="411"/>
-      <c r="F10" s="411" t="s">
+      <c r="E10" s="439"/>
+      <c r="F10" s="439" t="s">
         <v>125</v>
       </c>
-      <c r="G10" s="411"/>
-      <c r="H10" s="411" t="s">
+      <c r="G10" s="439"/>
+      <c r="H10" s="439" t="s">
         <v>126</v>
       </c>
-      <c r="I10" s="411"/>
+      <c r="I10" s="439"/>
       <c r="J10" s="209"/>
       <c r="K10" s="210"/>
       <c r="L10" s="210"/>
@@ -5849,14 +5849,14 @@
     </row>
     <row r="11" spans="1:14" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="211"/>
-      <c r="B11" s="411"/>
-      <c r="C11" s="411"/>
-      <c r="D11" s="411"/>
-      <c r="E11" s="411"/>
-      <c r="F11" s="411"/>
-      <c r="G11" s="411"/>
-      <c r="H11" s="411"/>
-      <c r="I11" s="411"/>
+      <c r="B11" s="439"/>
+      <c r="C11" s="439"/>
+      <c r="D11" s="439"/>
+      <c r="E11" s="439"/>
+      <c r="F11" s="439"/>
+      <c r="G11" s="439"/>
+      <c r="H11" s="439"/>
+      <c r="I11" s="439"/>
       <c r="J11" s="212"/>
       <c r="K11" s="210"/>
       <c r="L11" s="210"/>
@@ -5884,18 +5884,18 @@
       <c r="N12" s="284"/>
     </row>
     <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="412" t="s">
+      <c r="A13" s="440" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="413"/>
-      <c r="C13" s="413"/>
-      <c r="D13" s="413"/>
-      <c r="E13" s="413"/>
-      <c r="F13" s="413"/>
-      <c r="G13" s="413"/>
-      <c r="H13" s="413"/>
-      <c r="I13" s="413"/>
-      <c r="J13" s="414"/>
+      <c r="B13" s="441"/>
+      <c r="C13" s="441"/>
+      <c r="D13" s="441"/>
+      <c r="E13" s="441"/>
+      <c r="F13" s="441"/>
+      <c r="G13" s="441"/>
+      <c r="H13" s="441"/>
+      <c r="I13" s="441"/>
+      <c r="J13" s="442"/>
       <c r="K13" s="210"/>
       <c r="L13" s="210"/>
       <c r="M13" s="279" t="s">
@@ -5904,18 +5904,18 @@
       <c r="N13" s="284"/>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="406" t="s">
+      <c r="A14" s="434" t="s">
         <v>117</v>
       </c>
-      <c r="B14" s="407"/>
-      <c r="C14" s="407"/>
-      <c r="D14" s="407"/>
-      <c r="E14" s="407"/>
-      <c r="F14" s="407"/>
-      <c r="G14" s="407"/>
-      <c r="H14" s="407"/>
-      <c r="I14" s="407"/>
-      <c r="J14" s="408"/>
+      <c r="B14" s="435"/>
+      <c r="C14" s="435"/>
+      <c r="D14" s="435"/>
+      <c r="E14" s="435"/>
+      <c r="F14" s="435"/>
+      <c r="G14" s="435"/>
+      <c r="H14" s="435"/>
+      <c r="I14" s="435"/>
+      <c r="J14" s="436"/>
       <c r="K14" s="210"/>
       <c r="L14" s="210"/>
       <c r="M14" s="282"/>
@@ -5941,21 +5941,21 @@
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="221"/>
-      <c r="B16" s="415" t="s">
+      <c r="B16" s="426" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="415"/>
-      <c r="D16" s="415"/>
+      <c r="C16" s="426"/>
+      <c r="D16" s="426"/>
       <c r="E16" s="222"/>
-      <c r="F16" s="416" t="s">
+      <c r="F16" s="427" t="s">
         <v>127</v>
       </c>
-      <c r="G16" s="416"/>
+      <c r="G16" s="427"/>
       <c r="H16" s="222"/>
-      <c r="I16" s="417" t="s">
+      <c r="I16" s="428" t="s">
         <v>128</v>
       </c>
-      <c r="J16" s="420"/>
+      <c r="J16" s="431"/>
       <c r="K16" s="210"/>
       <c r="L16" s="210"/>
       <c r="M16" s="279" t="s">
@@ -5965,15 +5965,15 @@
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="221"/>
-      <c r="B17" s="423"/>
-      <c r="C17" s="424"/>
-      <c r="D17" s="425"/>
+      <c r="B17" s="417"/>
+      <c r="C17" s="418"/>
+      <c r="D17" s="419"/>
       <c r="E17" s="223"/>
-      <c r="F17" s="423"/>
-      <c r="G17" s="425"/>
+      <c r="F17" s="417"/>
+      <c r="G17" s="419"/>
       <c r="H17" s="222"/>
-      <c r="I17" s="418"/>
-      <c r="J17" s="421"/>
+      <c r="I17" s="429"/>
+      <c r="J17" s="432"/>
       <c r="K17" s="210"/>
       <c r="L17" s="210"/>
       <c r="M17" s="279" t="s">
@@ -5986,8 +5986,8 @@
       <c r="F18" s="223"/>
       <c r="G18" s="223"/>
       <c r="H18" s="222"/>
-      <c r="I18" s="419"/>
-      <c r="J18" s="422"/>
+      <c r="I18" s="430"/>
+      <c r="J18" s="433"/>
       <c r="L18" s="210"/>
       <c r="M18" s="224"/>
     </row>
@@ -6007,11 +6007,11 @@
     </row>
     <row r="20" spans="1:14" s="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="227"/>
-      <c r="B20" s="426" t="s">
+      <c r="B20" s="413" t="s">
         <v>129</v>
       </c>
-      <c r="C20" s="426"/>
-      <c r="D20" s="428"/>
+      <c r="C20" s="413"/>
+      <c r="D20" s="415"/>
       <c r="F20" s="229" t="s">
         <v>130</v>
       </c>
@@ -6024,12 +6024,12 @@
     </row>
     <row r="21" spans="1:14" s="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="232"/>
-      <c r="B21" s="427"/>
-      <c r="C21" s="427"/>
-      <c r="D21" s="429"/>
-      <c r="F21" s="423"/>
-      <c r="G21" s="424"/>
-      <c r="H21" s="425"/>
+      <c r="B21" s="414"/>
+      <c r="C21" s="414"/>
+      <c r="D21" s="416"/>
+      <c r="F21" s="417"/>
+      <c r="G21" s="418"/>
+      <c r="H21" s="419"/>
       <c r="I21" s="230"/>
       <c r="J21" s="226"/>
       <c r="L21" s="231"/>
@@ -6303,11 +6303,11 @@
       <c r="G36" s="250" t="s">
         <v>1</v>
       </c>
-      <c r="H36" s="430">
+      <c r="H36" s="420">
         <v>31</v>
       </c>
-      <c r="I36" s="431"/>
-      <c r="J36" s="432"/>
+      <c r="I36" s="421"/>
+      <c r="J36" s="422"/>
       <c r="K36" s="210"/>
       <c r="L36" s="210"/>
     </row>
@@ -6326,15 +6326,15 @@
       <c r="L37" s="210"/>
     </row>
     <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="433" t="s">
+      <c r="A38" s="423" t="s">
         <v>146</v>
       </c>
-      <c r="B38" s="434"/>
-      <c r="C38" s="435"/>
-      <c r="D38" s="433" t="s">
+      <c r="B38" s="424"/>
+      <c r="C38" s="425"/>
+      <c r="D38" s="423" t="s">
         <v>147</v>
       </c>
-      <c r="E38" s="435"/>
+      <c r="E38" s="425"/>
       <c r="F38" s="271" t="s">
         <v>100</v>
       </c>
@@ -6346,13 +6346,13 @@
       <c r="L38" s="210"/>
     </row>
     <row r="39" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="436" t="s">
+      <c r="A39" s="406" t="s">
         <v>148</v>
       </c>
-      <c r="B39" s="437"/>
-      <c r="C39" s="438"/>
-      <c r="D39" s="436"/>
-      <c r="E39" s="438"/>
+      <c r="B39" s="407"/>
+      <c r="C39" s="408"/>
+      <c r="D39" s="406"/>
+      <c r="E39" s="408"/>
       <c r="F39" s="233"/>
       <c r="G39" s="234"/>
       <c r="H39" s="234"/>
@@ -6362,13 +6362,13 @@
       <c r="L39" s="210"/>
     </row>
     <row r="40" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="436" t="s">
+      <c r="A40" s="406" t="s">
         <v>149</v>
       </c>
-      <c r="B40" s="437"/>
-      <c r="C40" s="438"/>
-      <c r="D40" s="436"/>
-      <c r="E40" s="438"/>
+      <c r="B40" s="407"/>
+      <c r="C40" s="408"/>
+      <c r="D40" s="406"/>
+      <c r="E40" s="408"/>
       <c r="F40" s="274"/>
       <c r="G40" s="272"/>
       <c r="H40" s="272"/>
@@ -6378,61 +6378,61 @@
       <c r="L40" s="210"/>
     </row>
     <row r="41" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="436" t="s">
+      <c r="A41" s="406" t="s">
         <v>150</v>
       </c>
-      <c r="B41" s="437"/>
-      <c r="C41" s="438"/>
-      <c r="D41" s="436"/>
-      <c r="E41" s="438"/>
+      <c r="B41" s="407"/>
+      <c r="C41" s="408"/>
+      <c r="D41" s="406"/>
+      <c r="E41" s="408"/>
       <c r="F41" s="221"/>
       <c r="K41" s="210"/>
       <c r="L41" s="210"/>
     </row>
     <row r="42" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="440" t="s">
+      <c r="A42" s="410" t="s">
         <v>151</v>
       </c>
-      <c r="B42" s="441"/>
-      <c r="C42" s="442"/>
-      <c r="D42" s="436"/>
-      <c r="E42" s="438"/>
+      <c r="B42" s="411"/>
+      <c r="C42" s="412"/>
+      <c r="D42" s="406"/>
+      <c r="E42" s="408"/>
       <c r="F42" s="221"/>
       <c r="K42" s="210"/>
       <c r="L42" s="210"/>
     </row>
     <row r="43" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="440" t="s">
+      <c r="A43" s="410" t="s">
         <v>152</v>
       </c>
-      <c r="B43" s="441"/>
-      <c r="C43" s="442"/>
-      <c r="D43" s="436"/>
-      <c r="E43" s="438"/>
+      <c r="B43" s="411"/>
+      <c r="C43" s="412"/>
+      <c r="D43" s="406"/>
+      <c r="E43" s="408"/>
       <c r="F43" s="221"/>
       <c r="K43" s="210"/>
       <c r="L43" s="210"/>
     </row>
     <row r="44" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="436" t="s">
+      <c r="A44" s="406" t="s">
         <v>153</v>
       </c>
-      <c r="B44" s="437"/>
-      <c r="C44" s="438"/>
-      <c r="D44" s="436"/>
-      <c r="E44" s="438"/>
+      <c r="B44" s="407"/>
+      <c r="C44" s="408"/>
+      <c r="D44" s="406"/>
+      <c r="E44" s="408"/>
       <c r="F44" s="221"/>
       <c r="K44" s="210"/>
       <c r="L44" s="210"/>
     </row>
     <row r="45" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="436" t="s">
+      <c r="A45" s="406" t="s">
         <v>154</v>
       </c>
-      <c r="B45" s="437"/>
-      <c r="C45" s="438"/>
-      <c r="D45" s="436"/>
-      <c r="E45" s="438"/>
+      <c r="B45" s="407"/>
+      <c r="C45" s="408"/>
+      <c r="D45" s="406"/>
+      <c r="E45" s="408"/>
       <c r="F45" s="221"/>
       <c r="K45" s="210"/>
       <c r="L45" s="210"/>
@@ -6525,18 +6525,18 @@
     </row>
     <row r="53" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="439" t="s">
+      <c r="A54" s="409" t="s">
         <v>170</v>
       </c>
-      <c r="B54" s="439"/>
-      <c r="C54" s="439"/>
-      <c r="D54" s="439"/>
-      <c r="E54" s="439"/>
-      <c r="F54" s="439"/>
-      <c r="G54" s="439"/>
-      <c r="H54" s="439"/>
-      <c r="I54" s="439"/>
-      <c r="J54" s="439"/>
+      <c r="B54" s="409"/>
+      <c r="C54" s="409"/>
+      <c r="D54" s="409"/>
+      <c r="E54" s="409"/>
+      <c r="F54" s="409"/>
+      <c r="G54" s="409"/>
+      <c r="H54" s="409"/>
+      <c r="I54" s="409"/>
+      <c r="J54" s="409"/>
     </row>
     <row r="55" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="1:12" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6548,33 +6548,6 @@
     <protectedRange sqref="H31:J31" name="Rango8_1"/>
   </protectedRanges>
   <mergeCells count="39">
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="A54:J54"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="F17:G17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A8:J8"/>
@@ -6587,6 +6560,33 @@
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="A13:J13"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:E44"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0.39370078740157483" top="0" bottom="0" header="0" footer="0"/>
@@ -6637,38 +6637,38 @@
       <c r="M1" s="295"/>
     </row>
     <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="443" t="s">
+      <c r="A2" s="464" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="443"/>
-      <c r="C2" s="443"/>
-      <c r="D2" s="443"/>
-      <c r="E2" s="443"/>
-      <c r="F2" s="443"/>
-      <c r="G2" s="443"/>
-      <c r="H2" s="443"/>
-      <c r="I2" s="443"/>
-      <c r="J2" s="443"/>
-      <c r="K2" s="443"/>
-      <c r="L2" s="443"/>
-      <c r="M2" s="443"/>
+      <c r="B2" s="464"/>
+      <c r="C2" s="464"/>
+      <c r="D2" s="464"/>
+      <c r="E2" s="464"/>
+      <c r="F2" s="464"/>
+      <c r="G2" s="464"/>
+      <c r="H2" s="464"/>
+      <c r="I2" s="464"/>
+      <c r="J2" s="464"/>
+      <c r="K2" s="464"/>
+      <c r="L2" s="464"/>
+      <c r="M2" s="464"/>
     </row>
     <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="444">
+      <c r="A3" s="465">
         <v>0</v>
       </c>
-      <c r="B3" s="444"/>
-      <c r="C3" s="444"/>
-      <c r="D3" s="444"/>
-      <c r="E3" s="444"/>
-      <c r="F3" s="444"/>
-      <c r="G3" s="444"/>
-      <c r="H3" s="444"/>
-      <c r="I3" s="444"/>
-      <c r="J3" s="444"/>
-      <c r="K3" s="444"/>
-      <c r="L3" s="444"/>
-      <c r="M3" s="444"/>
+      <c r="B3" s="465"/>
+      <c r="C3" s="465"/>
+      <c r="D3" s="465"/>
+      <c r="E3" s="465"/>
+      <c r="F3" s="465"/>
+      <c r="G3" s="465"/>
+      <c r="H3" s="465"/>
+      <c r="I3" s="465"/>
+      <c r="J3" s="465"/>
+      <c r="K3" s="465"/>
+      <c r="L3" s="465"/>
+      <c r="M3" s="465"/>
     </row>
     <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6678,17 +6678,17 @@
       <c r="B5" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="455">
+      <c r="C5" s="476">
         <f>+FORMATO!N2</f>
         <v>0</v>
       </c>
-      <c r="D5" s="455"/>
-      <c r="E5" s="455"/>
-      <c r="F5" s="455"/>
-      <c r="G5" s="455"/>
-      <c r="H5" s="455"/>
-      <c r="I5" s="455"/>
-      <c r="J5" s="455"/>
+      <c r="D5" s="476"/>
+      <c r="E5" s="476"/>
+      <c r="F5" s="476"/>
+      <c r="G5" s="476"/>
+      <c r="H5" s="476"/>
+      <c r="I5" s="476"/>
+      <c r="J5" s="476"/>
       <c r="K5" s="299" t="s">
         <v>20</v>
       </c>
@@ -6706,17 +6706,17 @@
       <c r="B6" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="455">
+      <c r="C6" s="476">
         <f>+FORMATO!N3</f>
         <v>0</v>
       </c>
-      <c r="D6" s="455"/>
-      <c r="E6" s="455"/>
-      <c r="F6" s="455"/>
-      <c r="G6" s="455"/>
-      <c r="H6" s="455"/>
-      <c r="I6" s="455"/>
-      <c r="J6" s="455"/>
+      <c r="D6" s="476"/>
+      <c r="E6" s="476"/>
+      <c r="F6" s="476"/>
+      <c r="G6" s="476"/>
+      <c r="H6" s="476"/>
+      <c r="I6" s="476"/>
+      <c r="J6" s="476"/>
       <c r="K6" s="279" t="s">
         <v>119</v>
       </c>
@@ -6738,17 +6738,17 @@
       <c r="B7" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="455">
+      <c r="C7" s="476">
         <f>+FORMATO!N4</f>
         <v>0</v>
       </c>
-      <c r="D7" s="455"/>
-      <c r="E7" s="455"/>
-      <c r="F7" s="455"/>
-      <c r="G7" s="455"/>
-      <c r="H7" s="455"/>
-      <c r="I7" s="455"/>
-      <c r="J7" s="455"/>
+      <c r="D7" s="476"/>
+      <c r="E7" s="476"/>
+      <c r="F7" s="476"/>
+      <c r="G7" s="476"/>
+      <c r="H7" s="476"/>
+      <c r="I7" s="476"/>
+      <c r="J7" s="476"/>
       <c r="K7" s="279" t="s">
         <v>158</v>
       </c>
@@ -6770,17 +6770,17 @@
       <c r="B8" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="455">
+      <c r="C8" s="476">
         <f>+FORMATO!N5</f>
         <v>0</v>
       </c>
-      <c r="D8" s="455"/>
-      <c r="E8" s="455"/>
-      <c r="F8" s="455"/>
-      <c r="G8" s="455"/>
-      <c r="H8" s="455"/>
-      <c r="I8" s="455"/>
-      <c r="J8" s="455"/>
+      <c r="D8" s="476"/>
+      <c r="E8" s="476"/>
+      <c r="F8" s="476"/>
+      <c r="G8" s="476"/>
+      <c r="H8" s="476"/>
+      <c r="I8" s="476"/>
+      <c r="J8" s="476"/>
       <c r="K8" s="304" t="s">
         <v>36</v>
       </c>
@@ -6816,41 +6816,41 @@
       <c r="P9" s="303"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="447" t="s">
+      <c r="A10" s="468" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="448"/>
-      <c r="C10" s="448"/>
-      <c r="D10" s="448"/>
-      <c r="E10" s="448"/>
-      <c r="F10" s="448"/>
-      <c r="G10" s="448"/>
-      <c r="H10" s="448"/>
-      <c r="I10" s="448"/>
-      <c r="J10" s="448"/>
-      <c r="K10" s="448"/>
-      <c r="L10" s="448"/>
-      <c r="M10" s="449"/>
+      <c r="B10" s="469"/>
+      <c r="C10" s="469"/>
+      <c r="D10" s="469"/>
+      <c r="E10" s="469"/>
+      <c r="F10" s="469"/>
+      <c r="G10" s="469"/>
+      <c r="H10" s="469"/>
+      <c r="I10" s="469"/>
+      <c r="J10" s="469"/>
+      <c r="K10" s="469"/>
+      <c r="L10" s="469"/>
+      <c r="M10" s="470"/>
       <c r="N10" s="303"/>
       <c r="O10" s="303"/>
       <c r="P10" s="303"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="450" t="s">
+      <c r="A11" s="471" t="s">
         <v>117</v>
       </c>
-      <c r="B11" s="451"/>
-      <c r="C11" s="451"/>
-      <c r="D11" s="451"/>
-      <c r="E11" s="451"/>
-      <c r="F11" s="451"/>
-      <c r="G11" s="451"/>
-      <c r="H11" s="451"/>
-      <c r="I11" s="451"/>
-      <c r="J11" s="451"/>
-      <c r="K11" s="451"/>
-      <c r="L11" s="451"/>
-      <c r="M11" s="452"/>
+      <c r="B11" s="472"/>
+      <c r="C11" s="472"/>
+      <c r="D11" s="472"/>
+      <c r="E11" s="472"/>
+      <c r="F11" s="472"/>
+      <c r="G11" s="472"/>
+      <c r="H11" s="472"/>
+      <c r="I11" s="472"/>
+      <c r="J11" s="472"/>
+      <c r="K11" s="472"/>
+      <c r="L11" s="472"/>
+      <c r="M11" s="473"/>
       <c r="N11" s="303"/>
       <c r="O11" s="303"/>
       <c r="P11" s="303"/>
@@ -6874,13 +6874,13 @@
       <c r="P12" s="303"/>
     </row>
     <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="453" t="s">
+      <c r="A13" s="474" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="454"/>
-      <c r="C13" s="454"/>
-      <c r="D13" s="454"/>
-      <c r="E13" s="454"/>
+      <c r="B13" s="475"/>
+      <c r="C13" s="475"/>
+      <c r="D13" s="475"/>
+      <c r="E13" s="475"/>
       <c r="F13" s="318"/>
       <c r="G13" s="318"/>
       <c r="H13" s="318"/>
@@ -7011,15 +7011,15 @@
       <c r="A18" s="341"/>
       <c r="B18" s="342"/>
       <c r="C18" s="342"/>
-      <c r="D18" s="445"/>
-      <c r="E18" s="445"/>
+      <c r="D18" s="466"/>
+      <c r="E18" s="466"/>
       <c r="F18" s="342"/>
       <c r="G18" s="342"/>
       <c r="H18" s="342"/>
       <c r="I18" s="343"/>
       <c r="J18" s="343"/>
-      <c r="K18" s="446"/>
-      <c r="L18" s="446"/>
+      <c r="K18" s="467"/>
+      <c r="L18" s="467"/>
       <c r="M18" s="344"/>
       <c r="N18" s="303"/>
       <c r="O18" s="345"/>
@@ -7029,18 +7029,18 @@
       <c r="A19" s="346"/>
       <c r="B19" s="347"/>
       <c r="C19" s="347"/>
-      <c r="D19" s="456" t="s">
+      <c r="D19" s="443" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="457"/>
-      <c r="F19" s="457"/>
-      <c r="G19" s="457"/>
-      <c r="H19" s="458"/>
-      <c r="I19" s="474" t="s">
+      <c r="E19" s="444"/>
+      <c r="F19" s="444"/>
+      <c r="G19" s="444"/>
+      <c r="H19" s="445"/>
+      <c r="I19" s="461" t="s">
         <v>72</v>
       </c>
-      <c r="J19" s="474"/>
-      <c r="K19" s="475"/>
+      <c r="J19" s="461"/>
+      <c r="K19" s="462"/>
       <c r="L19" s="348"/>
       <c r="M19" s="349"/>
       <c r="N19" s="303"/>
@@ -7051,11 +7051,11 @@
       <c r="A20" s="350"/>
       <c r="B20" s="295"/>
       <c r="C20" s="295"/>
-      <c r="D20" s="459"/>
-      <c r="E20" s="460"/>
-      <c r="F20" s="460"/>
-      <c r="G20" s="460"/>
-      <c r="H20" s="461"/>
+      <c r="D20" s="446"/>
+      <c r="E20" s="447"/>
+      <c r="F20" s="447"/>
+      <c r="G20" s="447"/>
+      <c r="H20" s="448"/>
       <c r="I20" s="351">
         <v>1</v>
       </c>
@@ -7127,8 +7127,8 @@
         <f>+Datos!I14</f>
         <v>0</v>
       </c>
-      <c r="L22" s="468"/>
-      <c r="M22" s="467"/>
+      <c r="L22" s="455"/>
+      <c r="M22" s="454"/>
       <c r="N22" s="303"/>
       <c r="O22" s="364"/>
       <c r="P22" s="303"/>
@@ -7158,8 +7158,8 @@
         <f>+Datos!I15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L23" s="466"/>
-      <c r="M23" s="467"/>
+      <c r="L23" s="453"/>
+      <c r="M23" s="454"/>
       <c r="N23" s="303"/>
       <c r="O23" s="303"/>
       <c r="P23" s="364"/>
@@ -7177,12 +7177,12 @@
       <c r="H24" s="360" t="s">
         <v>1</v>
       </c>
-      <c r="I24" s="469" t="e">
+      <c r="I24" s="456" t="e">
         <f>+Datos!G16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J24" s="470"/>
-      <c r="K24" s="471"/>
+      <c r="J24" s="457"/>
+      <c r="K24" s="458"/>
       <c r="L24" s="369"/>
       <c r="M24" s="362"/>
       <c r="N24" s="303"/>
@@ -7244,10 +7244,10 @@
       <c r="C28" s="386"/>
       <c r="D28" s="367"/>
       <c r="E28" s="369"/>
-      <c r="F28" s="472" t="s">
+      <c r="F28" s="459" t="s">
         <v>176</v>
       </c>
-      <c r="G28" s="473"/>
+      <c r="G28" s="460"/>
       <c r="M28" s="384"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -7270,11 +7270,11 @@
       <c r="C30" s="386"/>
       <c r="D30" s="367"/>
       <c r="E30" s="369"/>
-      <c r="F30" s="462">
+      <c r="F30" s="449">
         <f>+Datos!E25</f>
         <v>0</v>
       </c>
-      <c r="G30" s="463"/>
+      <c r="G30" s="450"/>
       <c r="M30" s="384"/>
     </row>
     <row r="31" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7285,11 +7285,11 @@
       <c r="C31" s="386"/>
       <c r="D31" s="367"/>
       <c r="E31" s="369"/>
-      <c r="F31" s="462">
+      <c r="F31" s="449">
         <f>+Datos!E26</f>
         <v>0</v>
       </c>
-      <c r="G31" s="463"/>
+      <c r="G31" s="450"/>
       <c r="M31" s="384"/>
     </row>
     <row r="32" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7326,95 +7326,95 @@
       <c r="M34" s="393"/>
     </row>
     <row r="35" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="476" t="s">
+      <c r="A35" s="463" t="s">
         <v>171</v>
       </c>
-      <c r="B35" s="476"/>
-      <c r="C35" s="476"/>
-      <c r="D35" s="476"/>
-      <c r="E35" s="476"/>
-      <c r="F35" s="476"/>
-      <c r="G35" s="476"/>
-      <c r="H35" s="476"/>
-      <c r="I35" s="476"/>
-      <c r="J35" s="476"/>
-      <c r="K35" s="476"/>
-      <c r="L35" s="476"/>
-      <c r="M35" s="476"/>
+      <c r="B35" s="463"/>
+      <c r="C35" s="463"/>
+      <c r="D35" s="463"/>
+      <c r="E35" s="463"/>
+      <c r="F35" s="463"/>
+      <c r="G35" s="463"/>
+      <c r="H35" s="463"/>
+      <c r="I35" s="463"/>
+      <c r="J35" s="463"/>
+      <c r="K35" s="463"/>
+      <c r="L35" s="463"/>
+      <c r="M35" s="463"/>
     </row>
     <row r="36" spans="1:16" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="465" t="s">
+      <c r="A36" s="452" t="s">
         <v>172</v>
       </c>
-      <c r="B36" s="465"/>
-      <c r="C36" s="465"/>
-      <c r="D36" s="465"/>
-      <c r="E36" s="465"/>
-      <c r="F36" s="465"/>
-      <c r="G36" s="465"/>
-      <c r="H36" s="465"/>
-      <c r="I36" s="465"/>
-      <c r="J36" s="465"/>
-      <c r="K36" s="465"/>
-      <c r="L36" s="465"/>
-      <c r="M36" s="465"/>
+      <c r="B36" s="452"/>
+      <c r="C36" s="452"/>
+      <c r="D36" s="452"/>
+      <c r="E36" s="452"/>
+      <c r="F36" s="452"/>
+      <c r="G36" s="452"/>
+      <c r="H36" s="452"/>
+      <c r="I36" s="452"/>
+      <c r="J36" s="452"/>
+      <c r="K36" s="452"/>
+      <c r="L36" s="452"/>
+      <c r="M36" s="452"/>
     </row>
     <row r="37" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="465" t="s">
+      <c r="A37" s="452" t="s">
         <v>173</v>
       </c>
-      <c r="B37" s="465"/>
-      <c r="C37" s="465"/>
-      <c r="D37" s="465"/>
-      <c r="E37" s="465"/>
-      <c r="F37" s="465"/>
-      <c r="G37" s="465"/>
-      <c r="H37" s="465"/>
-      <c r="I37" s="465"/>
-      <c r="J37" s="465"/>
-      <c r="K37" s="465"/>
-      <c r="L37" s="465"/>
-      <c r="M37" s="465"/>
+      <c r="B37" s="452"/>
+      <c r="C37" s="452"/>
+      <c r="D37" s="452"/>
+      <c r="E37" s="452"/>
+      <c r="F37" s="452"/>
+      <c r="G37" s="452"/>
+      <c r="H37" s="452"/>
+      <c r="I37" s="452"/>
+      <c r="J37" s="452"/>
+      <c r="K37" s="452"/>
+      <c r="L37" s="452"/>
+      <c r="M37" s="452"/>
       <c r="N37" s="303"/>
       <c r="O37" s="303"/>
       <c r="P37" s="303"/>
     </row>
     <row r="38" spans="1:16" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="465" t="s">
+      <c r="A38" s="452" t="s">
         <v>174</v>
       </c>
-      <c r="B38" s="465"/>
-      <c r="C38" s="465"/>
-      <c r="D38" s="465"/>
-      <c r="E38" s="465"/>
-      <c r="F38" s="465"/>
-      <c r="G38" s="465"/>
-      <c r="H38" s="465"/>
-      <c r="I38" s="465"/>
-      <c r="J38" s="465"/>
-      <c r="K38" s="465"/>
-      <c r="L38" s="465"/>
-      <c r="M38" s="465"/>
+      <c r="B38" s="452"/>
+      <c r="C38" s="452"/>
+      <c r="D38" s="452"/>
+      <c r="E38" s="452"/>
+      <c r="F38" s="452"/>
+      <c r="G38" s="452"/>
+      <c r="H38" s="452"/>
+      <c r="I38" s="452"/>
+      <c r="J38" s="452"/>
+      <c r="K38" s="452"/>
+      <c r="L38" s="452"/>
+      <c r="M38" s="452"/>
       <c r="N38" s="303"/>
       <c r="O38" s="303"/>
       <c r="P38" s="303"/>
     </row>
     <row r="39" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="464" t="s">
+      <c r="A39" s="451" t="s">
         <v>175</v>
       </c>
-      <c r="B39" s="464"/>
-      <c r="C39" s="464"/>
-      <c r="D39" s="464"/>
-      <c r="E39" s="464"/>
-      <c r="F39" s="464"/>
-      <c r="G39" s="464"/>
-      <c r="H39" s="464"/>
-      <c r="I39" s="464"/>
-      <c r="J39" s="464"/>
-      <c r="K39" s="464"/>
-      <c r="L39" s="464"/>
-      <c r="M39" s="464"/>
+      <c r="B39" s="451"/>
+      <c r="C39" s="451"/>
+      <c r="D39" s="451"/>
+      <c r="E39" s="451"/>
+      <c r="F39" s="451"/>
+      <c r="G39" s="451"/>
+      <c r="H39" s="451"/>
+      <c r="I39" s="451"/>
+      <c r="J39" s="451"/>
+      <c r="K39" s="451"/>
+      <c r="L39" s="451"/>
+      <c r="M39" s="451"/>
       <c r="N39" s="303"/>
       <c r="O39" s="303"/>
       <c r="P39" s="303"/>
@@ -7612,13 +7612,24 @@
     </row>
     <row r="51" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="8NM1+p6p3LesDUstMxFGHu0zYxm1d4zXGYtLxhJOWwI+xJ9//NVS0q83GcKW2Ki+XgVMpMuspxvNsKuxOQLOxg==" saltValue="QYjBUm0XnOsAQh3sj8wCVA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="E12" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="E7:E9 C7:D8" name="Rango3_3_1_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="C5:E6" name="Rango3_3_1_1_1_1_1_2_1_1"/>
   </protectedRanges>
   <mergeCells count="24">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="C5:J5"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="C8:J8"/>
     <mergeCell ref="D19:H20"/>
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
@@ -7632,19 +7643,8 @@
     <mergeCell ref="A35:M35"/>
     <mergeCell ref="A36:M36"/>
     <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C5:J5"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="C8:J8"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F28:G28" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"-,Procedimiento A,Procedimiento B"</formula1>
     </dataValidation>
@@ -7653,7 +7653,7 @@
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0" right="0" top="1.3779527559055118" bottom="0" header="0.11811023622047245" footer="0"/>
+  <pageMargins left="0" right="0" top="1.3779527559055118" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="274" scale="90" orientation="portrait" r:id="rId1"/>
   <headerFooter scaleWithDoc="0">
     <oddHeader>&amp;C&amp;G</oddHeader>
